--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G19">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G34">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G40">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.84</v>
+        <v>3.44</v>
       </c>
       <c r="O51">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P51">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB51">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.21</v>
+        <v>2.84</v>
       </c>
       <c r="O52">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P52">
-        <v>3.31</v>
+        <v>2.35</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AB52">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.44</v>
+        <v>2.21</v>
       </c>
       <c r="O53">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="P53">
-        <v>2.08</v>
+        <v>3.31</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AB53">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G65">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.49</v>
+        <v>1.31</v>
       </c>
       <c r="O103">
-        <v>3.32</v>
+        <v>5.2</v>
       </c>
       <c r="P103">
-        <v>2.71</v>
+        <v>8.9</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AB103">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.31</v>
+        <v>2.02</v>
       </c>
       <c r="O104">
-        <v>5.2</v>
+        <v>3.46</v>
       </c>
       <c r="P104">
-        <v>8.9</v>
+        <v>3.54</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AB104">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="O105">
-        <v>3.46</v>
+        <v>3.22</v>
       </c>
       <c r="P105">
-        <v>3.54</v>
+        <v>2.94</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="AA105">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AB105">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="O106">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="P106">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB106">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G107">
@@ -17753,10 +17753,10 @@
         <v>2.49</v>
       </c>
       <c r="O107">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P107">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17789,10 +17789,10 @@
         <v>0</v>
       </c>
       <c r="AA107">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AB107">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AC107">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O109">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P109">
-        <v>4.18</v>
+        <v>4.32</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AB109">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="O110">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
-        <v>4.32</v>
+        <v>3.03</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AB110">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.26</v>
+        <v>3.17</v>
       </c>
       <c r="O111">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="P111">
-        <v>3.03</v>
+        <v>2.16</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB111">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.17</v>
+        <v>1.66</v>
       </c>
       <c r="O112">
-        <v>3.46</v>
+        <v>3.88</v>
       </c>
       <c r="P112">
-        <v>2.16</v>
+        <v>4.84</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AB112">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="O113">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="P113">
-        <v>4.84</v>
+        <v>2.98</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AB113">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O114">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P114">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AB114">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="O115">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="P115">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB115">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="O116">
-        <v>3.15</v>
+        <v>3.68</v>
       </c>
       <c r="P116">
-        <v>3.14</v>
+        <v>4.18</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AB116">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G231">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G232">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G236">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G237">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G251">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G252">

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G8">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G19">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G27">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G31">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G41">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G43">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.44</v>
+        <v>2.84</v>
       </c>
       <c r="O51">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P51">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB51">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.84</v>
+        <v>2.21</v>
       </c>
       <c r="O52">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
-        <v>2.35</v>
+        <v>3.31</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AB52">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.21</v>
+        <v>3.44</v>
       </c>
       <c r="O53">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="P53">
-        <v>3.31</v>
+        <v>2.08</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AB53">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G59">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G65">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G73">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.94</v>
+        <v>2.18</v>
       </c>
       <c r="O90">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="P90">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="O91">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="P91">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB91">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.33</v>
+        <v>1.79</v>
       </c>
       <c r="O92">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="P92">
-        <v>2.97</v>
+        <v>4.14</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB92">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="O93">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="P93">
-        <v>3.14</v>
+        <v>2.53</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15507,10 +15507,10 @@
         <v>0</v>
       </c>
       <c r="AA93">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB93">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="O94">
-        <v>3.36</v>
+        <v>3.74</v>
       </c>
       <c r="P94">
-        <v>3.31</v>
+        <v>4.77</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB94">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="O95">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="P95">
-        <v>4.14</v>
+        <v>3.01</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AB95">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.65</v>
+        <v>2.09</v>
       </c>
       <c r="O96">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="P96">
-        <v>2.53</v>
+        <v>3.41</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15999,7 +15999,7 @@
         <v>2</v>
       </c>
       <c r="AB96">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.68</v>
+        <v>2.94</v>
       </c>
       <c r="O97">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="P97">
-        <v>4.77</v>
+        <v>2.34</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB97">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="O98">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="P98">
-        <v>3.01</v>
+        <v>3.55</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB98">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="O99">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P99">
-        <v>3.41</v>
+        <v>2.97</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,14 +16935,14 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="O102">
+        <v>3.46</v>
+      </c>
+      <c r="P102">
         <v>3.54</v>
       </c>
-      <c r="P102">
-        <v>3.22</v>
-      </c>
       <c r="Q102">
         <v>0</v>
       </c>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AB102">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.31</v>
+        <v>2.49</v>
       </c>
       <c r="O103">
-        <v>5.2</v>
+        <v>3.28</v>
       </c>
       <c r="P103">
-        <v>8.9</v>
+        <v>2.74</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AB103">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.02</v>
+        <v>2.49</v>
       </c>
       <c r="O104">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
       <c r="P104">
-        <v>3.54</v>
+        <v>2.71</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB104">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="O105">
-        <v>3.22</v>
+        <v>5.2</v>
       </c>
       <c r="P105">
-        <v>2.94</v>
+        <v>8.9</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="AA105">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AB105">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.49</v>
+        <v>2.14</v>
       </c>
       <c r="O106">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P106">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="AB106">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="O107">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="P107">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17789,10 +17789,10 @@
         <v>0</v>
       </c>
       <c r="AA107">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB107">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AC107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.48</v>
+        <v>1.79</v>
       </c>
       <c r="O108">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P108">
-        <v>2.8</v>
+        <v>4.32</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AB108">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.79</v>
+        <v>3.17</v>
       </c>
       <c r="O109">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P109">
-        <v>4.32</v>
+        <v>2.16</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB109">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="O110">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="P110">
-        <v>3.03</v>
+        <v>4.84</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AB110">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.17</v>
+        <v>1.8</v>
       </c>
       <c r="O111">
-        <v>3.46</v>
+        <v>3.68</v>
       </c>
       <c r="P111">
-        <v>2.16</v>
+        <v>4.18</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB111">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="O112">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="P112">
-        <v>4.84</v>
+        <v>2.98</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AB112">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O113">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P113">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AB113">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="O114">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="P114">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB114">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="O115">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB115">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O116">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P116">
-        <v>4.18</v>
+        <v>3.03</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AB116">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>6.57</v>
+        <v>3.48</v>
       </c>
       <c r="O174">
-        <v>3.38</v>
+        <v>2.82</v>
       </c>
       <c r="P174">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.48</v>
+        <v>6.57</v>
       </c>
       <c r="O175">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="P175">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G194">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="O239">
-        <v>3.79</v>
+        <v>4.11</v>
       </c>
       <c r="P239">
-        <v>3.17</v>
+        <v>3.85</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,16 +39305,16 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB239">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="O240">
-        <v>4.11</v>
+        <v>4.21</v>
       </c>
       <c r="P240">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -39474,10 +39474,10 @@
         <v>0</v>
       </c>
       <c r="AC240">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AD240">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AE240">
         <v>0</v>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O241">
-        <v>4.21</v>
+        <v>3.66</v>
       </c>
       <c r="P241">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -39631,16 +39631,16 @@
         <v>0</v>
       </c>
       <c r="AA241">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB241">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC241">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD241">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE241">
         <v>0</v>
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="O242">
         <v>3.66</v>
       </c>
       <c r="P242">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39794,7 +39794,7 @@
         <v>0</v>
       </c>
       <c r="AA242">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB242">
         <v>2.05</v>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="O243">
-        <v>3.66</v>
+        <v>3.79</v>
       </c>
       <c r="P243">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -39957,10 +39957,10 @@
         <v>0</v>
       </c>
       <c r="AA243">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB243">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC243">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G73">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G88">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="O94">
-        <v>3.74</v>
+        <v>3.32</v>
       </c>
       <c r="P94">
-        <v>4.77</v>
+        <v>3.41</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB94">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.29</v>
+        <v>1.68</v>
       </c>
       <c r="O95">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="P95">
-        <v>3.01</v>
+        <v>4.77</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB95">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.09</v>
+        <v>2.29</v>
       </c>
       <c r="O96">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P96">
-        <v>3.41</v>
+        <v>3.01</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB96">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="O112">
-        <v>3.48</v>
+        <v>3.15</v>
       </c>
       <c r="P112">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AB112">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="O113">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P113">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AB113">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O114">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="P114">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB114">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="P115">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="AB115">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="O116">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P116">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AB116">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G122">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G164">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G170">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O178">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P178">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB178">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,55 +40733,55 @@
         </is>
       </c>
       <c r="N248">
+        <v>1.75</v>
+      </c>
+      <c r="O248">
+        <v>4.09</v>
+      </c>
+      <c r="P248">
+        <v>4.68</v>
+      </c>
+      <c r="Q248">
+        <v>0</v>
+      </c>
+      <c r="R248">
+        <v>0</v>
+      </c>
+      <c r="S248">
+        <v>0</v>
+      </c>
+      <c r="T248">
+        <v>0</v>
+      </c>
+      <c r="U248">
+        <v>0</v>
+      </c>
+      <c r="V248">
+        <v>0</v>
+      </c>
+      <c r="W248">
+        <v>0</v>
+      </c>
+      <c r="X248">
+        <v>0</v>
+      </c>
+      <c r="Y248">
+        <v>0</v>
+      </c>
+      <c r="Z248">
+        <v>0</v>
+      </c>
+      <c r="AA248">
+        <v>1.58</v>
+      </c>
+      <c r="AB248">
         <v>2.2</v>
       </c>
-      <c r="O248">
-        <v>3.95</v>
-      </c>
-      <c r="P248">
-        <v>3.1</v>
-      </c>
-      <c r="Q248">
-        <v>0</v>
-      </c>
-      <c r="R248">
-        <v>0</v>
-      </c>
-      <c r="S248">
-        <v>0</v>
-      </c>
-      <c r="T248">
-        <v>0</v>
-      </c>
-      <c r="U248">
-        <v>0</v>
-      </c>
-      <c r="V248">
-        <v>0</v>
-      </c>
-      <c r="W248">
-        <v>0</v>
-      </c>
-      <c r="X248">
-        <v>0</v>
-      </c>
-      <c r="Y248">
-        <v>0</v>
-      </c>
-      <c r="Z248">
-        <v>0</v>
-      </c>
-      <c r="AA248">
-        <v>0</v>
-      </c>
-      <c r="AB248">
-        <v>0</v>
-      </c>
       <c r="AC248">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD248">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE248">
         <v>0</v>
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O249">
-        <v>4.09</v>
+        <v>3.95</v>
       </c>
       <c r="P249">
-        <v>4.68</v>
+        <v>3.1</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -40935,16 +40935,16 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB249">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC249">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD249">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE249">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G60">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="O98">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P98">
-        <v>3.55</v>
+        <v>2.97</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16325,7 +16325,7 @@
         <v>2</v>
       </c>
       <c r="AB98">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="O99">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="P99">
-        <v>2.97</v>
+        <v>3.55</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16488,7 +16488,7 @@
         <v>2</v>
       </c>
       <c r="AB99">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="O114">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P114">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB114">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="O115">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P115">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AB115">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="P116">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="AB116">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G135">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G144">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G154">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G164">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>0</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="O259">
-        <v>4.84</v>
+        <v>4.16</v>
       </c>
       <c r="P259">
-        <v>5.46</v>
+        <v>4.83</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42571,10 +42571,10 @@
         <v>0</v>
       </c>
       <c r="AC259">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AD259">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AE259">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="O260">
-        <v>4.16</v>
+        <v>4.84</v>
       </c>
       <c r="P260">
-        <v>4.83</v>
+        <v>5.46</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42734,10 +42734,10 @@
         <v>0</v>
       </c>
       <c r="AC260">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AD260">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AE260">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="O83">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P83">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="O86">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P86">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O87">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P87">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="O88">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P88">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G141">

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,14 +5525,14 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="O32">
+        <v>3.6</v>
+      </c>
+      <c r="P32">
         <v>3.38</v>
       </c>
-      <c r="P32">
-        <v>2.91</v>
-      </c>
       <c r="Q32">
         <v>0</v>
       </c>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.9</v>
+        <v>3.32</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>3.38</v>
+        <v>2</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="P34">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="O35">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="P35">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB35">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.94</v>
+        <v>2.33</v>
       </c>
       <c r="O97">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P97">
-        <v>2.34</v>
+        <v>2.97</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB97">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="O98">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="P98">
-        <v>2.97</v>
+        <v>3.55</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16325,7 +16325,7 @@
         <v>2</v>
       </c>
       <c r="AB98">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.02</v>
+        <v>2.94</v>
       </c>
       <c r="O99">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="P99">
-        <v>3.55</v>
+        <v>2.34</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB99">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="O114">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P114">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB114">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O115">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P115">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AB115">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="O116">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P116">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AB116">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O168">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P168">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>0</v>
       </c>
       <c r="AA168">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB168">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC170">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.9</v>
+        <v>3.32</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>3.38</v>
+        <v>2</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="P33">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="O34">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="P34">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,14 +6014,14 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="O35">
+        <v>3.6</v>
+      </c>
+      <c r="P35">
         <v>3.38</v>
       </c>
-      <c r="P35">
-        <v>2.91</v>
-      </c>
       <c r="Q35">
         <v>0</v>
       </c>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC35">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41424,10 +41424,10 @@
         <v>0</v>
       </c>
       <c r="AA252">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB252">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC252">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -42239,10 +42239,10 @@
         <v>0</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC257">
         <v>0</v>
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P258">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q258">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU260"/>
+  <dimension ref="A1:AU264"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O132">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P132">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,22 +22435,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O136">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P136">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22761,22 +22761,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G141">
@@ -23408,27 +23408,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G142">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-08-15 12:30:00</t>
+          <t>2026-08-15 12:00:00</t>
         </is>
       </c>
     </row>
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O147">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P147">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O148">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P148">
-        <v>2.5</v>
+        <v>3.16</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G154">
@@ -25527,12 +25527,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G155">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>2026-08-15 13:00:00</t>
+          <t>2026-08-15 12:30:00</t>
         </is>
       </c>
     </row>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G164">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>6.53</v>
+        <v>0</v>
       </c>
       <c r="O165">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P165">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27320,12 +27320,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>2026-08-15 13:15:00</t>
+          <t>2026-08-15 13:00:00</t>
         </is>
       </c>
     </row>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O167">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P167">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27646,12 +27646,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-08-15 13:30:00</t>
+          <t>2026-08-15 13:15:00</t>
         </is>
       </c>
     </row>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O170">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P170">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB170">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>0</v>
       </c>
       <c r="AA171">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC171">
         <v>0</v>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O172">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P172">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB172">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28629,7 +28629,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O174">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="P174">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>6.57</v>
+        <v>3.48</v>
       </c>
       <c r="O175">
-        <v>3.38</v>
+        <v>2.82</v>
       </c>
       <c r="P175">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.38</v>
+        <v>6.57</v>
       </c>
       <c r="O176">
-        <v>3.68</v>
+        <v>3.38</v>
       </c>
       <c r="P176">
-        <v>2.86</v>
+        <v>1.51</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-15 13:45:00</t>
+          <t>2026-08-15 13:30:00</t>
         </is>
       </c>
     </row>
@@ -29113,27 +29113,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-15 14:00:00</t>
+          <t>2026-08-15 13:45:00</t>
         </is>
       </c>
     </row>
@@ -29281,22 +29281,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O179">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P179">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB179">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -29607,22 +29607,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O181">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="AA181">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB181">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC181">
         <v>0</v>
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O182">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P182">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30091,12 +30091,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G183">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-08-15 14:30:00</t>
+          <t>2026-08-15 14:00:00</t>
         </is>
       </c>
     </row>
@@ -30254,12 +30254,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.99</v>
+        <v>4.37</v>
       </c>
       <c r="O184">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="P184">
-        <v>3.58</v>
+        <v>1.83</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-08-15 14:30:00</t>
+          <t>2026-08-15 14:00:00</t>
         </is>
       </c>
     </row>
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O185">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P185">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-08-15 14:45:00</t>
+          <t>2026-08-15 14:30:00</t>
         </is>
       </c>
     </row>
@@ -30580,12 +30580,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-08-15 15:00:00</t>
+          <t>2026-08-15 14:30:00</t>
         </is>
       </c>
     </row>
@@ -30743,12 +30743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-08-15 15:00:00</t>
+          <t>2026-08-15 14:45:00</t>
         </is>
       </c>
     </row>
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,22 +31237,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,22 +31400,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G191">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G195">
@@ -32215,22 +32215,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G196">
@@ -32378,22 +32378,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O197">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P197">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G198">
@@ -32699,12 +32699,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G199">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:00</t>
+          <t>2026-08-15 15:00:00</t>
         </is>
       </c>
     </row>
@@ -32862,12 +32862,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:00</t>
+          <t>2026-08-15 15:00:00</t>
         </is>
       </c>
     </row>
@@ -33025,12 +33025,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O201">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P201">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:00</t>
+          <t>2026-08-15 15:00:00</t>
         </is>
       </c>
     </row>
@@ -33188,12 +33188,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-15 15:30:00</t>
+          <t>2026-08-15 15:15:00</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G203">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-08-15 15:30:00</t>
+          <t>2026-08-15 15:15:00</t>
         </is>
       </c>
     </row>
@@ -33514,12 +33514,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.17</v>
+        <v>1.56</v>
       </c>
       <c r="O204">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P204">
-        <v>2.99</v>
+        <v>5.15</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>2026-08-15 15:30:00</t>
+          <t>2026-08-15 15:15:00</t>
         </is>
       </c>
     </row>
@@ -33682,7 +33682,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="O207">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P207">
-        <v>2.86</v>
+        <v>2.99</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34166,12 +34166,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="O208">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="P208">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>2026-08-15 15:45:00</t>
+          <t>2026-08-15 15:30:00</t>
         </is>
       </c>
     </row>
@@ -34329,12 +34329,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O209">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="P209">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>2026-08-15 15:45:00</t>
+          <t>2026-08-15 15:30:00</t>
         </is>
       </c>
     </row>
@@ -34492,27 +34492,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>2026-08-15 16:00:00</t>
+          <t>2026-08-15 15:30:00</t>
         </is>
       </c>
     </row>
@@ -34655,27 +34655,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>2026-08-15 16:00:00</t>
+          <t>2026-08-15 15:45:00</t>
         </is>
       </c>
     </row>
@@ -34818,27 +34818,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>2026-08-15 16:00:00</t>
+          <t>2026-08-15 15:45:00</t>
         </is>
       </c>
     </row>
@@ -34986,22 +34986,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G213">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G216">
@@ -35633,27 +35633,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O217">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P217">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>2026-08-15 16:30:00</t>
+          <t>2026-08-15 16:00:00</t>
         </is>
       </c>
     </row>
@@ -35796,12 +35796,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O218">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P218">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35882,10 +35882,10 @@
         <v>0</v>
       </c>
       <c r="AA218">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB218">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC218">
         <v>0</v>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>2026-08-15 16:30:00</t>
+          <t>2026-08-15 16:00:00</t>
         </is>
       </c>
     </row>
@@ -35959,27 +35959,27 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G219">
@@ -36110,7 +36110,7 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>2026-08-15 16:30:00</t>
+          <t>2026-08-15 16:00:00</t>
         </is>
       </c>
     </row>
@@ -36122,27 +36122,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G220">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>2026-08-15 16:30:00</t>
+          <t>2026-08-15 16:00:00</t>
         </is>
       </c>
     </row>
@@ -36285,12 +36285,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>2026-08-15 17:00:00</t>
+          <t>2026-08-15 16:30:00</t>
         </is>
       </c>
     </row>
@@ -36448,27 +36448,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36534,10 +36534,10 @@
         <v>0</v>
       </c>
       <c r="AA222">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB222">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC222">
         <v>0</v>
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2026-08-15 17:00:00</t>
+          <t>2026-08-15 16:30:00</t>
         </is>
       </c>
     </row>
@@ -36611,27 +36611,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G223">
@@ -36762,7 +36762,7 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>2026-08-15 18:00:00</t>
+          <t>2026-08-15 16:30:00</t>
         </is>
       </c>
     </row>
@@ -36774,27 +36774,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G224">
@@ -36925,7 +36925,7 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>2026-08-15 18:00:00</t>
+          <t>2026-08-15 16:30:00</t>
         </is>
       </c>
     </row>
@@ -36937,12 +36937,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O225">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P225">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>2026-08-15 18:30:00</t>
+          <t>2026-08-15 17:00:00</t>
         </is>
       </c>
     </row>
@@ -37100,12 +37100,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G226">
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>2026-08-15 18:30:00</t>
+          <t>2026-08-15 17:00:00</t>
         </is>
       </c>
     </row>
@@ -37263,12 +37263,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G227">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-08-15 18:30:00</t>
+          <t>2026-08-15 18:00:00</t>
         </is>
       </c>
     </row>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G228">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-08-15 18:30:00</t>
+          <t>2026-08-15 18:00:00</t>
         </is>
       </c>
     </row>
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37752,12 +37752,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G230">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-08-15 19:00:00</t>
+          <t>2026-08-15 18:30:00</t>
         </is>
       </c>
     </row>
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G231">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-08-15 19:30:00</t>
+          <t>2026-08-15 18:30:00</t>
         </is>
       </c>
     </row>
@@ -38078,12 +38078,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G232">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>2026-08-15 19:30:00</t>
+          <t>2026-08-15 18:30:00</t>
         </is>
       </c>
     </row>
@@ -38241,12 +38241,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G233">
@@ -38392,7 +38392,7 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>2026-08-15 19:30:00</t>
+          <t>2026-08-15 18:30:00</t>
         </is>
       </c>
     </row>
@@ -38404,12 +38404,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O234">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P234">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>2026-08-15 20:00:00</t>
+          <t>2026-08-15 19:00:00</t>
         </is>
       </c>
     </row>
@@ -38567,12 +38567,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G235">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>2026-08-15 20:00:00</t>
+          <t>2026-08-15 19:30:00</t>
         </is>
       </c>
     </row>
@@ -38730,12 +38730,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G236">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-08-15 20:00:00</t>
+          <t>2026-08-15 19:30:00</t>
         </is>
       </c>
     </row>
@@ -38893,12 +38893,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O237">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P237">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-08-15 20:00:00</t>
+          <t>2026-08-15 19:30:00</t>
         </is>
       </c>
     </row>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="O238">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="P238">
-        <v>4.05</v>
+        <v>5.95</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-08-15 20:30:00</t>
+          <t>2026-08-15 20:00:00</t>
         </is>
       </c>
     </row>
@@ -39219,12 +39219,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O239">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P239">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39311,10 +39311,10 @@
         <v>0</v>
       </c>
       <c r="AC239">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD239">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE239">
         <v>0</v>
@@ -39370,7 +39370,7 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>2026-08-15 20:30:00</t>
+          <t>2026-08-15 20:00:00</t>
         </is>
       </c>
     </row>
@@ -39382,12 +39382,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O240">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="P240">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -39474,10 +39474,10 @@
         <v>0</v>
       </c>
       <c r="AC240">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD240">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE240">
         <v>0</v>
@@ -39533,7 +39533,7 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>2026-08-15 20:30:00</t>
+          <t>2026-08-15 20:00:00</t>
         </is>
       </c>
     </row>
@@ -39545,12 +39545,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G241">
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="O241">
-        <v>3.66</v>
+        <v>3.04</v>
       </c>
       <c r="P241">
-        <v>2.85</v>
+        <v>2.51</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -39631,10 +39631,10 @@
         <v>0</v>
       </c>
       <c r="AA241">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB241">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC241">
         <v>0</v>
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-08-15 20:30:00</t>
+          <t>2026-08-15 20:00:00</t>
         </is>
       </c>
     </row>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>2.32</v>
+        <v>1.69</v>
       </c>
       <c r="O242">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="P242">
-        <v>3.06</v>
+        <v>4.05</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39794,10 +39794,10 @@
         <v>0</v>
       </c>
       <c r="AA242">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB242">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC242">
         <v>0</v>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="O243">
-        <v>3.79</v>
+        <v>4.11</v>
       </c>
       <c r="P243">
-        <v>3.17</v>
+        <v>3.85</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -39957,16 +39957,16 @@
         <v>0</v>
       </c>
       <c r="AA243">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB243">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD243">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE243">
         <v>0</v>
@@ -40034,12 +40034,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40126,10 +40126,10 @@
         <v>0</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE244">
         <v>0</v>
@@ -40185,7 +40185,7 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>2026-08-15 21:00:00</t>
+          <t>2026-08-15 20:30:00</t>
         </is>
       </c>
     </row>
@@ -40197,12 +40197,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.71</v>
+        <v>2.46</v>
       </c>
       <c r="O245">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="P245">
-        <v>5.35</v>
+        <v>2.85</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,11 +40283,11 @@
         <v>0</v>
       </c>
       <c r="AA245">
+        <v>1.65</v>
+      </c>
+      <c r="AB245">
         <v>2.05</v>
       </c>
-      <c r="AB245">
-        <v>1.8</v>
-      </c>
       <c r="AC245">
         <v>0</v>
       </c>
@@ -40348,7 +40348,7 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>2026-08-15 21:00:00</t>
+          <t>2026-08-15 20:30:00</t>
         </is>
       </c>
     </row>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC246">
         <v>0</v>
@@ -40511,7 +40511,7 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>2026-08-15 21:00:00</t>
+          <t>2026-08-15 20:30:00</t>
         </is>
       </c>
     </row>
@@ -40523,12 +40523,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40609,10 +40609,10 @@
         <v>0</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC247">
         <v>0</v>
@@ -40674,7 +40674,7 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>2026-08-15 21:00:00</t>
+          <t>2026-08-15 20:30:00</t>
         </is>
       </c>
     </row>
@@ -40686,12 +40686,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O248">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="P248">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40772,10 +40772,10 @@
         <v>0</v>
       </c>
       <c r="AA248">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB248">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC248">
         <v>0</v>
@@ -40837,7 +40837,7 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>2026-08-15 21:30:00</t>
+          <t>2026-08-15 21:00:00</t>
         </is>
       </c>
     </row>
@@ -40849,12 +40849,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="O249">
-        <v>3.95</v>
+        <v>3.71</v>
       </c>
       <c r="P249">
-        <v>3.1</v>
+        <v>5.35</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -40935,16 +40935,16 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC249">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD249">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE249">
         <v>0</v>
@@ -41000,7 +41000,7 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>2026-08-15 21:30:00</t>
+          <t>2026-08-15 21:00:00</t>
         </is>
       </c>
     </row>
@@ -41012,12 +41012,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G250">
@@ -41163,7 +41163,7 @@
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>2026-08-15 21:45:00</t>
+          <t>2026-08-15 21:00:00</t>
         </is>
       </c>
     </row>
@@ -41175,12 +41175,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O251">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P251">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41326,7 +41326,7 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>2026-08-15 22:00:00</t>
+          <t>2026-08-15 21:00:00</t>
         </is>
       </c>
     </row>
@@ -41338,12 +41338,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="O252">
-        <v>3.25</v>
+        <v>4.09</v>
       </c>
       <c r="P252">
-        <v>3.4</v>
+        <v>4.68</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41424,10 +41424,10 @@
         <v>0</v>
       </c>
       <c r="AA252">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AB252">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC252">
         <v>0</v>
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-08-15 22:00:00</t>
+          <t>2026-08-15 21:30:00</t>
         </is>
       </c>
     </row>
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O253">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="P253">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41587,16 +41587,16 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB253">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE253">
         <v>0</v>
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-08-15 22:30:00</t>
+          <t>2026-08-15 21:30:00</t>
         </is>
       </c>
     </row>
@@ -41664,12 +41664,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O254">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P254">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41750,10 +41750,10 @@
         <v>0</v>
       </c>
       <c r="AA254">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB254">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC254">
         <v>0</v>
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-08-15 22:30:00</t>
+          <t>2026-08-15 21:45:00</t>
         </is>
       </c>
     </row>
@@ -41827,12 +41827,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="O255">
-        <v>5.08</v>
+        <v>4.35</v>
       </c>
       <c r="P255">
-        <v>7.43</v>
+        <v>5.6</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -41919,10 +41919,10 @@
         <v>0</v>
       </c>
       <c r="AC255">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD255">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE255">
         <v>0</v>
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-08-15 22:30:00</t>
+          <t>2026-08-15 22:00:00</t>
         </is>
       </c>
     </row>
@@ -41990,7 +41990,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="O256">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P256">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42076,10 +42076,10 @@
         <v>0</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC256">
         <v>0</v>
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>2026-08-15 23:00:00</t>
+          <t>2026-08-15 22:00:00</t>
         </is>
       </c>
     </row>
@@ -42153,7 +42153,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G257">
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="O257">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P257">
-        <v>1.71</v>
+        <v>2.65</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -42239,10 +42239,10 @@
         <v>0</v>
       </c>
       <c r="AA257">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB257">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC257">
         <v>0</v>
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-08-15 23:00:00</t>
+          <t>2026-08-15 22:30:00</t>
         </is>
       </c>
     </row>
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="O258">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P258">
-        <v>3.35</v>
+        <v>4.58</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -42402,10 +42402,10 @@
         <v>0</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC258">
         <v>0</v>
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-08-15 23:30:00</t>
+          <t>2026-08-15 22:30:00</t>
         </is>
       </c>
     </row>
@@ -42479,7 +42479,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="O259">
-        <v>4.16</v>
+        <v>5.08</v>
       </c>
       <c r="P259">
-        <v>4.83</v>
+        <v>7.43</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42571,10 +42571,10 @@
         <v>0</v>
       </c>
       <c r="AC259">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AD259">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AE259">
         <v>0</v>
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-08-15 23:30:00</t>
+          <t>2026-08-15 22:30:00</t>
         </is>
       </c>
     </row>
@@ -42642,156 +42642,808 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N260">
+        <v>1.7</v>
+      </c>
+      <c r="O260">
+        <v>3.7</v>
+      </c>
+      <c r="P260">
+        <v>4</v>
+      </c>
+      <c r="Q260">
+        <v>0</v>
+      </c>
+      <c r="R260">
+        <v>0</v>
+      </c>
+      <c r="S260">
+        <v>0</v>
+      </c>
+      <c r="T260">
+        <v>0</v>
+      </c>
+      <c r="U260">
+        <v>0</v>
+      </c>
+      <c r="V260">
+        <v>0</v>
+      </c>
+      <c r="W260">
+        <v>0</v>
+      </c>
+      <c r="X260">
+        <v>0</v>
+      </c>
+      <c r="Y260">
+        <v>0</v>
+      </c>
+      <c r="Z260">
+        <v>0</v>
+      </c>
+      <c r="AA260">
+        <v>0</v>
+      </c>
+      <c r="AB260">
+        <v>0</v>
+      </c>
+      <c r="AC260">
+        <v>0</v>
+      </c>
+      <c r="AD260">
+        <v>0</v>
+      </c>
+      <c r="AE260">
+        <v>0</v>
+      </c>
+      <c r="AF260">
+        <v>0</v>
+      </c>
+      <c r="AG260">
+        <v>0</v>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ260">
+        <v>0</v>
+      </c>
+      <c r="AK260">
+        <v>0</v>
+      </c>
+      <c r="AL260">
+        <v>0</v>
+      </c>
+      <c r="AM260">
+        <v>-1</v>
+      </c>
+      <c r="AN260">
+        <v>-1</v>
+      </c>
+      <c r="AO260">
+        <v>-1</v>
+      </c>
+      <c r="AP260">
+        <v>-1</v>
+      </c>
+      <c r="AQ260">
+        <v>0</v>
+      </c>
+      <c r="AR260">
+        <v>0</v>
+      </c>
+      <c r="AS260">
+        <v>0</v>
+      </c>
+      <c r="AT260">
+        <v>0</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Louisville City</t>
+        </is>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>0</v>
+      </c>
+      <c r="L261">
+        <v>0</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N261">
+        <v>4</v>
+      </c>
+      <c r="O261">
+        <v>3.65</v>
+      </c>
+      <c r="P261">
+        <v>1.71</v>
+      </c>
+      <c r="Q261">
+        <v>0</v>
+      </c>
+      <c r="R261">
+        <v>0</v>
+      </c>
+      <c r="S261">
+        <v>0</v>
+      </c>
+      <c r="T261">
+        <v>0</v>
+      </c>
+      <c r="U261">
+        <v>0</v>
+      </c>
+      <c r="V261">
+        <v>0</v>
+      </c>
+      <c r="W261">
+        <v>0</v>
+      </c>
+      <c r="X261">
+        <v>0</v>
+      </c>
+      <c r="Y261">
+        <v>0</v>
+      </c>
+      <c r="Z261">
+        <v>0</v>
+      </c>
+      <c r="AA261">
+        <v>1.75</v>
+      </c>
+      <c r="AB261">
+        <v>1.93</v>
+      </c>
+      <c r="AC261">
+        <v>0</v>
+      </c>
+      <c r="AD261">
+        <v>0</v>
+      </c>
+      <c r="AE261">
+        <v>0</v>
+      </c>
+      <c r="AF261">
+        <v>0</v>
+      </c>
+      <c r="AG261">
+        <v>0</v>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ261">
+        <v>0</v>
+      </c>
+      <c r="AK261">
+        <v>0</v>
+      </c>
+      <c r="AL261">
+        <v>0</v>
+      </c>
+      <c r="AM261">
+        <v>-1</v>
+      </c>
+      <c r="AN261">
+        <v>-1</v>
+      </c>
+      <c r="AO261">
+        <v>-1</v>
+      </c>
+      <c r="AP261">
+        <v>-1</v>
+      </c>
+      <c r="AQ261">
+        <v>0</v>
+      </c>
+      <c r="AR261">
+        <v>0</v>
+      </c>
+      <c r="AS261">
+        <v>0</v>
+      </c>
+      <c r="AT261">
+        <v>0</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="G262">
+        <v>0</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>0</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N262">
+        <v>1.88</v>
+      </c>
+      <c r="O262">
+        <v>3.6</v>
+      </c>
+      <c r="P262">
+        <v>3.35</v>
+      </c>
+      <c r="Q262">
+        <v>0</v>
+      </c>
+      <c r="R262">
+        <v>0</v>
+      </c>
+      <c r="S262">
+        <v>0</v>
+      </c>
+      <c r="T262">
+        <v>0</v>
+      </c>
+      <c r="U262">
+        <v>0</v>
+      </c>
+      <c r="V262">
+        <v>0</v>
+      </c>
+      <c r="W262">
+        <v>0</v>
+      </c>
+      <c r="X262">
+        <v>0</v>
+      </c>
+      <c r="Y262">
+        <v>0</v>
+      </c>
+      <c r="Z262">
+        <v>0</v>
+      </c>
+      <c r="AA262">
+        <v>0</v>
+      </c>
+      <c r="AB262">
+        <v>0</v>
+      </c>
+      <c r="AC262">
+        <v>0</v>
+      </c>
+      <c r="AD262">
+        <v>0</v>
+      </c>
+      <c r="AE262">
+        <v>0</v>
+      </c>
+      <c r="AF262">
+        <v>0</v>
+      </c>
+      <c r="AG262">
+        <v>0</v>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ262">
+        <v>0</v>
+      </c>
+      <c r="AK262">
+        <v>0</v>
+      </c>
+      <c r="AL262">
+        <v>0</v>
+      </c>
+      <c r="AM262">
+        <v>-1</v>
+      </c>
+      <c r="AN262">
+        <v>-1</v>
+      </c>
+      <c r="AO262">
+        <v>-1</v>
+      </c>
+      <c r="AP262">
+        <v>-1</v>
+      </c>
+      <c r="AQ262">
+        <v>0</v>
+      </c>
+      <c r="AR262">
+        <v>0</v>
+      </c>
+      <c r="AS262">
+        <v>0</v>
+      </c>
+      <c r="AT262">
+        <v>0</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="G263">
+        <v>0</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>0</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N263">
+        <v>1.71</v>
+      </c>
+      <c r="O263">
+        <v>4.16</v>
+      </c>
+      <c r="P263">
+        <v>4.83</v>
+      </c>
+      <c r="Q263">
+        <v>0</v>
+      </c>
+      <c r="R263">
+        <v>0</v>
+      </c>
+      <c r="S263">
+        <v>0</v>
+      </c>
+      <c r="T263">
+        <v>0</v>
+      </c>
+      <c r="U263">
+        <v>0</v>
+      </c>
+      <c r="V263">
+        <v>0</v>
+      </c>
+      <c r="W263">
+        <v>0</v>
+      </c>
+      <c r="X263">
+        <v>0</v>
+      </c>
+      <c r="Y263">
+        <v>0</v>
+      </c>
+      <c r="Z263">
+        <v>0</v>
+      </c>
+      <c r="AA263">
+        <v>0</v>
+      </c>
+      <c r="AB263">
+        <v>0</v>
+      </c>
+      <c r="AC263">
+        <v>2.15</v>
+      </c>
+      <c r="AD263">
+        <v>1.6</v>
+      </c>
+      <c r="AE263">
+        <v>0</v>
+      </c>
+      <c r="AF263">
+        <v>0</v>
+      </c>
+      <c r="AG263">
+        <v>0</v>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ263">
+        <v>0</v>
+      </c>
+      <c r="AK263">
+        <v>0</v>
+      </c>
+      <c r="AL263">
+        <v>0</v>
+      </c>
+      <c r="AM263">
+        <v>-1</v>
+      </c>
+      <c r="AN263">
+        <v>-1</v>
+      </c>
+      <c r="AO263">
+        <v>-1</v>
+      </c>
+      <c r="AP263">
+        <v>-1</v>
+      </c>
+      <c r="AQ263">
+        <v>0</v>
+      </c>
+      <c r="AR263">
+        <v>0</v>
+      </c>
+      <c r="AS263">
+        <v>0</v>
+      </c>
+      <c r="AT263">
+        <v>0</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F264" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="G260">
-        <v>0</v>
-      </c>
-      <c r="H260">
-        <v>0</v>
-      </c>
-      <c r="I260">
-        <v>0</v>
-      </c>
-      <c r="J260">
-        <v>0</v>
-      </c>
-      <c r="K260">
-        <v>0</v>
-      </c>
-      <c r="L260">
-        <v>0</v>
-      </c>
-      <c r="M260" t="inlineStr">
+      <c r="G264">
+        <v>0</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>0</v>
+      </c>
+      <c r="L264">
+        <v>0</v>
+      </c>
+      <c r="M264" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N260">
+      <c r="N264">
         <v>1.56</v>
       </c>
-      <c r="O260">
+      <c r="O264">
         <v>4.84</v>
       </c>
-      <c r="P260">
+      <c r="P264">
         <v>5.46</v>
       </c>
-      <c r="Q260">
-        <v>0</v>
-      </c>
-      <c r="R260">
-        <v>0</v>
-      </c>
-      <c r="S260">
-        <v>0</v>
-      </c>
-      <c r="T260">
-        <v>0</v>
-      </c>
-      <c r="U260">
-        <v>0</v>
-      </c>
-      <c r="V260">
-        <v>0</v>
-      </c>
-      <c r="W260">
-        <v>0</v>
-      </c>
-      <c r="X260">
-        <v>0</v>
-      </c>
-      <c r="Y260">
-        <v>0</v>
-      </c>
-      <c r="Z260">
-        <v>0</v>
-      </c>
-      <c r="AA260">
-        <v>0</v>
-      </c>
-      <c r="AB260">
-        <v>0</v>
-      </c>
-      <c r="AC260">
+      <c r="Q264">
+        <v>0</v>
+      </c>
+      <c r="R264">
+        <v>0</v>
+      </c>
+      <c r="S264">
+        <v>0</v>
+      </c>
+      <c r="T264">
+        <v>0</v>
+      </c>
+      <c r="U264">
+        <v>0</v>
+      </c>
+      <c r="V264">
+        <v>0</v>
+      </c>
+      <c r="W264">
+        <v>0</v>
+      </c>
+      <c r="X264">
+        <v>0</v>
+      </c>
+      <c r="Y264">
+        <v>0</v>
+      </c>
+      <c r="Z264">
+        <v>0</v>
+      </c>
+      <c r="AA264">
+        <v>0</v>
+      </c>
+      <c r="AB264">
+        <v>0</v>
+      </c>
+      <c r="AC264">
         <v>1.93</v>
       </c>
-      <c r="AD260">
+      <c r="AD264">
         <v>1.77</v>
       </c>
-      <c r="AE260">
-        <v>0</v>
-      </c>
-      <c r="AF260">
-        <v>0</v>
-      </c>
-      <c r="AG260">
-        <v>0</v>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ260">
-        <v>0</v>
-      </c>
-      <c r="AK260">
-        <v>0</v>
-      </c>
-      <c r="AL260">
-        <v>0</v>
-      </c>
-      <c r="AM260">
-        <v>-1</v>
-      </c>
-      <c r="AN260">
-        <v>-1</v>
-      </c>
-      <c r="AO260">
-        <v>-1</v>
-      </c>
-      <c r="AP260">
-        <v>-1</v>
-      </c>
-      <c r="AQ260">
-        <v>0</v>
-      </c>
-      <c r="AR260">
-        <v>0</v>
-      </c>
-      <c r="AS260">
-        <v>0</v>
-      </c>
-      <c r="AT260">
-        <v>0</v>
-      </c>
-      <c r="AU260" t="inlineStr">
+      <c r="AE264">
+        <v>0</v>
+      </c>
+      <c r="AF264">
+        <v>0</v>
+      </c>
+      <c r="AG264">
+        <v>0</v>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ264">
+        <v>0</v>
+      </c>
+      <c r="AK264">
+        <v>0</v>
+      </c>
+      <c r="AL264">
+        <v>0</v>
+      </c>
+      <c r="AM264">
+        <v>-1</v>
+      </c>
+      <c r="AN264">
+        <v>-1</v>
+      </c>
+      <c r="AO264">
+        <v>-1</v>
+      </c>
+      <c r="AP264">
+        <v>-1</v>
+      </c>
+      <c r="AQ264">
+        <v>0</v>
+      </c>
+      <c r="AR264">
+        <v>0</v>
+      </c>
+      <c r="AS264">
+        <v>0</v>
+      </c>
+      <c r="AT264">
+        <v>0</v>
+      </c>
+      <c r="AU264" t="inlineStr">
         <is>
           <t>2026-08-15 23:30:00</t>
         </is>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21381,10 +21381,10 @@
         <v>0</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE129">
         <v>0</v>
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O218">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35882,10 +35882,10 @@
         <v>0</v>
       </c>
       <c r="AA218">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB218">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC218">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20723,10 +20723,10 @@
         <v>0</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC125">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23005,10 +23005,10 @@
         <v>0</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC139">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23820,10 +23820,10 @@
         <v>0</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC144">
         <v>0</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q158">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.42</v>
+        <v>1.99</v>
       </c>
       <c r="O255">
-        <v>4.35</v>
+        <v>3.25</v>
       </c>
       <c r="P255">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -41913,10 +41913,10 @@
         <v>0</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC255">
         <v>0</v>
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="O256">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="P256">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42076,10 +42076,10 @@
         <v>0</v>
       </c>
       <c r="AA256">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB256">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC256">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33274,10 +33274,10 @@
         <v>0</v>
       </c>
       <c r="AA202">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB202">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC202">
         <v>0</v>
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36208,10 +36208,10 @@
         <v>0</v>
       </c>
       <c r="AA220">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB220">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC220">
         <v>0</v>
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36860,10 +36860,10 @@
         <v>0</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC224">
         <v>0</v>
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -38158,10 +38158,10 @@
         <v>0</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA232">
         <v>0</v>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38321,16 +38321,16 @@
         <v>0</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC233">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="O114">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P114">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB114">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="O115">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P115">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AB115">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="P116">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="AB116">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30020,10 +30020,10 @@
         <v>0</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE182">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31801,10 +31801,10 @@
         <v>0</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA193">
         <v>0</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31964,10 +31964,10 @@
         <v>0</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA194">
         <v>0</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32127,10 +32127,10 @@
         <v>0</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32290,10 +32290,10 @@
         <v>0</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32453,10 +32453,10 @@
         <v>0</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA197">
         <v>0</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35387,10 +35387,10 @@
         <v>0</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA215">
         <v>0</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37349,10 +37349,10 @@
         <v>0</v>
       </c>
       <c r="AA227">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB227">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC227">
         <v>0</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38484,10 +38484,10 @@
         <v>0</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA234">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.87</v>
+        <v>2.18</v>
       </c>
       <c r="O26">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="P26">
-        <v>1.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.18</v>
+        <v>3.87</v>
       </c>
       <c r="O27">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="P27">
-        <v>3.2</v>
+        <v>1.96</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.65</v>
+        <v>2.09</v>
       </c>
       <c r="O93">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="P93">
-        <v>2.53</v>
+        <v>3.41</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15510,7 +15510,7 @@
         <v>2</v>
       </c>
       <c r="AB93">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="O94">
-        <v>3.32</v>
+        <v>3.74</v>
       </c>
       <c r="P94">
-        <v>3.41</v>
+        <v>4.77</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,10 +15670,10 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB94">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AC94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="O95">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="P95">
-        <v>4.77</v>
+        <v>3.01</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB95">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="O96">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P96">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB96">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.33</v>
+        <v>2.94</v>
       </c>
       <c r="O97">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P97">
-        <v>2.97</v>
+        <v>2.34</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB97">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="O99">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P99">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AB99">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O115">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P115">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AB115">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="O116">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P116">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AB116">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G153">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G155">

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O86">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P86">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O88">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P88">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G154">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O244">
-        <v>4.21</v>
+        <v>3.66</v>
       </c>
       <c r="P244">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40120,16 +40120,16 @@
         <v>0</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC244">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD244">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE244">
         <v>0</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="O245">
         <v>3.66</v>
       </c>
       <c r="P245">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB245">
         <v>2.05</v>
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="O246">
-        <v>3.66</v>
+        <v>3.79</v>
       </c>
       <c r="P246">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB246">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC246">
         <v>0</v>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="O247">
-        <v>3.79</v>
+        <v>4.21</v>
       </c>
       <c r="P247">
-        <v>3.17</v>
+        <v>2.68</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40609,16 +40609,16 @@
         <v>0</v>
       </c>
       <c r="AA247">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB247">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC247">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD247">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE247">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
+        <v>2.82</v>
+      </c>
+      <c r="O10">
+        <v>3.3</v>
+      </c>
+      <c r="P10">
+        <v>2.57</v>
+      </c>
+      <c r="Q10">
+        <v>3.2</v>
+      </c>
+      <c r="R10">
+        <v>2.01</v>
+      </c>
+      <c r="S10">
+        <v>1.4</v>
+      </c>
+      <c r="T10">
+        <v>2.87</v>
+      </c>
+      <c r="U10">
+        <v>3.02</v>
+      </c>
+      <c r="V10">
+        <v>1.37</v>
+      </c>
+      <c r="W10">
+        <v>1.08</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.33</v>
+      </c>
+      <c r="Z10">
+        <v>3.37</v>
+      </c>
+      <c r="AA10">
+        <v>2.05</v>
+      </c>
+      <c r="AB10">
+        <v>1.72</v>
+      </c>
+      <c r="AC10">
+        <v>3.3</v>
+      </c>
+      <c r="AD10">
+        <v>1.25</v>
+      </c>
+      <c r="AE10">
+        <v>1.06</v>
+      </c>
+      <c r="AF10">
         <v>1.75</v>
       </c>
-      <c r="O10">
-        <v>3.73</v>
-      </c>
-      <c r="P10">
-        <v>4.81</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>1.97</v>
-      </c>
-      <c r="AB10">
-        <v>1.79</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.82</v>
+        <v>1.75</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.73</v>
       </c>
       <c r="P11">
-        <v>2.57</v>
+        <v>4.81</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>2.92</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>3.15</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G19">
@@ -4067,55 +4067,55 @@
         <v>3.2</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.81</v>
+        <v>2.74</v>
       </c>
       <c r="O24">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="P24">
-        <v>2.07</v>
+        <v>2.66</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.74</v>
+        <v>2.18</v>
       </c>
       <c r="O25">
-        <v>3.26</v>
+        <v>3.62</v>
       </c>
       <c r="P25">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.18</v>
+        <v>3.87</v>
       </c>
       <c r="O26">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="P26">
-        <v>3.2</v>
+        <v>1.96</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="O27">
-        <v>3.61</v>
+        <v>3.33</v>
       </c>
       <c r="P27">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5045,34 +5045,34 @@
         <v>3.84</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA29">
         <v>1.83</v>
@@ -5081,19 +5081,19 @@
         <v>1.89</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>3.19</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>1.91</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.32</v>
+        <v>2.18</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>2.91</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="O33">
+        <v>3.6</v>
+      </c>
+      <c r="P33">
         <v>3.38</v>
       </c>
-      <c r="P33">
-        <v>2.91</v>
-      </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA33">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AB33">
-        <v>1.81</v>
+        <v>2.22</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="P34">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="O35">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="P35">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,40 +6512,40 @@
         <v>3.54</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC38">
         <v>1.94</v>
@@ -6554,13 +6554,13 @@
         <v>1.83</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="O42">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="Q42">
-        <v>2.58</v>
+        <v>3.67</v>
       </c>
       <c r="R42">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U42">
+        <v>2.5</v>
+      </c>
+      <c r="V42">
+        <v>1.54</v>
+      </c>
+      <c r="W42">
+        <v>1.08</v>
+      </c>
+      <c r="X42">
+        <v>1.04</v>
+      </c>
+      <c r="Y42">
+        <v>1.21</v>
+      </c>
+      <c r="Z42">
+        <v>4.1</v>
+      </c>
+      <c r="AA42">
+        <v>1.67</v>
+      </c>
+      <c r="AB42">
+        <v>2.16</v>
+      </c>
+      <c r="AC42">
+        <v>2.7</v>
+      </c>
+      <c r="AD42">
+        <v>1.42</v>
+      </c>
+      <c r="AE42">
+        <v>1.13</v>
+      </c>
+      <c r="AF42">
+        <v>1.53</v>
+      </c>
+      <c r="AG42">
         <v>2.3</v>
       </c>
-      <c r="V42">
-        <v>1.57</v>
-      </c>
-      <c r="W42">
-        <v>1.15</v>
-      </c>
-      <c r="X42">
-        <v>1.03</v>
-      </c>
-      <c r="Y42">
-        <v>1.2</v>
-      </c>
-      <c r="Z42">
-        <v>4.33</v>
-      </c>
-      <c r="AA42">
-        <v>1.62</v>
-      </c>
-      <c r="AB42">
-        <v>2.25</v>
-      </c>
-      <c r="AC42">
-        <v>2.2</v>
-      </c>
-      <c r="AD42">
-        <v>1.6</v>
-      </c>
-      <c r="AE42">
-        <v>1.18</v>
-      </c>
-      <c r="AF42">
-        <v>1.4</v>
-      </c>
-      <c r="AG42">
-        <v>2.45</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AK42">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="Q43">
-        <v>3.67</v>
+        <v>2.58</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V43">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA43">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB43">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC43">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD43">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.59</v>
+        <v>2.36</v>
       </c>
       <c r="O47">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P47">
-        <v>2.55</v>
+        <v>2.91</v>
       </c>
       <c r="Q47">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R47">
         <v>2.1</v>
       </c>
       <c r="S47">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="U47">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V47">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W47">
         <v>1.05</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
         <v>1.33</v>
       </c>
       <c r="Z47">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AA47">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB47">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC47">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AD47">
         <v>1.25</v>
       </c>
       <c r="AE47">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG47">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK47">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="O48">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P48">
-        <v>2.91</v>
+        <v>2.55</v>
       </c>
       <c r="Q48">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R48">
         <v>2.1</v>
       </c>
       <c r="S48">
+        <v>1.4</v>
+      </c>
+      <c r="T48">
+        <v>2.6</v>
+      </c>
+      <c r="U48">
+        <v>2.75</v>
+      </c>
+      <c r="V48">
         <v>1.36</v>
-      </c>
-      <c r="T48">
-        <v>2.59</v>
-      </c>
-      <c r="U48">
-        <v>2.82</v>
-      </c>
-      <c r="V48">
-        <v>1.33</v>
       </c>
       <c r="W48">
         <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
         <v>1.33</v>
       </c>
       <c r="Z48">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA48">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB48">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC48">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AD48">
         <v>1.25</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF48">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>2</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>3.26</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>2.8</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -12054,55 +12054,55 @@
         <v>0</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12217,55 +12217,55 @@
         <v>2.33</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>2.12</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.44</v>
+        <v>6.25</v>
       </c>
       <c r="O79">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="P79">
+        <v>1.39</v>
+      </c>
+      <c r="Q79">
+        <v>4.83</v>
+      </c>
+      <c r="R79">
+        <v>2.25</v>
+      </c>
+      <c r="S79">
+        <v>1.28</v>
+      </c>
+      <c r="T79">
+        <v>3.23</v>
+      </c>
+      <c r="U79">
+        <v>2.48</v>
+      </c>
+      <c r="V79">
+        <v>1.5</v>
+      </c>
+      <c r="W79">
+        <v>1.11</v>
+      </c>
+      <c r="X79">
+        <v>1.02</v>
+      </c>
+      <c r="Y79">
+        <v>1.16</v>
+      </c>
+      <c r="Z79">
+        <v>4.1</v>
+      </c>
+      <c r="AA79">
+        <v>1.65</v>
+      </c>
+      <c r="AB79">
+        <v>2.19</v>
+      </c>
+      <c r="AC79">
         <v>2.52</v>
       </c>
-      <c r="Q79">
-        <v>2.99</v>
-      </c>
-      <c r="R79">
-        <v>2.14</v>
-      </c>
-      <c r="S79">
-        <v>1.33</v>
-      </c>
-      <c r="T79">
-        <v>2.91</v>
-      </c>
-      <c r="U79">
-        <v>2.59</v>
-      </c>
-      <c r="V79">
+      <c r="AD79">
         <v>1.41</v>
       </c>
-      <c r="W79">
-        <v>1.07</v>
-      </c>
-      <c r="X79">
-        <v>1</v>
-      </c>
-      <c r="Y79">
-        <v>1.24</v>
-      </c>
-      <c r="Z79">
-        <v>3.34</v>
-      </c>
-      <c r="AA79">
-        <v>1.82</v>
-      </c>
-      <c r="AB79">
-        <v>1.88</v>
-      </c>
-      <c r="AC79">
-        <v>2.92</v>
-      </c>
-      <c r="AD79">
-        <v>1.31</v>
-      </c>
       <c r="AE79">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF79">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG79">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.24</v>
+        <v>2.01</v>
       </c>
       <c r="AK79">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>6.25</v>
+        <v>2.44</v>
       </c>
       <c r="O80">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="P80">
-        <v>1.39</v>
+        <v>2.52</v>
       </c>
       <c r="Q80">
-        <v>4.83</v>
+        <v>2.99</v>
       </c>
       <c r="R80">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S80">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T80">
-        <v>3.23</v>
+        <v>2.91</v>
       </c>
       <c r="U80">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="V80">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y80">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z80">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA80">
+        <v>1.82</v>
+      </c>
+      <c r="AB80">
+        <v>1.88</v>
+      </c>
+      <c r="AC80">
+        <v>2.92</v>
+      </c>
+      <c r="AD80">
+        <v>1.31</v>
+      </c>
+      <c r="AE80">
+        <v>1.08</v>
+      </c>
+      <c r="AF80">
         <v>1.65</v>
       </c>
-      <c r="AB80">
-        <v>2.19</v>
-      </c>
-      <c r="AC80">
-        <v>2.52</v>
-      </c>
-      <c r="AD80">
-        <v>1.41</v>
-      </c>
-      <c r="AE80">
-        <v>1.17</v>
-      </c>
-      <c r="AF80">
-        <v>1.63</v>
-      </c>
       <c r="AG80">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>2.01</v>
+        <v>1.24</v>
       </c>
       <c r="AK80">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.99</v>
+        <v>2.85</v>
       </c>
       <c r="O84">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="P84">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="Q84">
+        <v>3.38</v>
+      </c>
+      <c r="R84">
+        <v>2.38</v>
+      </c>
+      <c r="S84">
+        <v>1.24</v>
+      </c>
+      <c r="T84">
+        <v>3.5</v>
+      </c>
+      <c r="U84">
+        <v>2.47</v>
+      </c>
+      <c r="V84">
+        <v>1.52</v>
+      </c>
+      <c r="W84">
+        <v>1.12</v>
+      </c>
+      <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
+        <v>1.19</v>
+      </c>
+      <c r="Z84">
+        <v>4.3</v>
+      </c>
+      <c r="AA84">
+        <v>1.62</v>
+      </c>
+      <c r="AB84">
+        <v>2.25</v>
+      </c>
+      <c r="AC84">
         <v>2.64</v>
       </c>
-      <c r="R84">
-        <v>2.2</v>
-      </c>
-      <c r="S84">
+      <c r="AD84">
+        <v>1.42</v>
+      </c>
+      <c r="AE84">
+        <v>1.17</v>
+      </c>
+      <c r="AF84">
+        <v>1.53</v>
+      </c>
+      <c r="AG84">
+        <v>2.32</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
+        <v>1.25</v>
+      </c>
+      <c r="AK84">
         <v>1.32</v>
-      </c>
-      <c r="T84">
-        <v>3.13</v>
-      </c>
-      <c r="U84">
-        <v>2.62</v>
-      </c>
-      <c r="V84">
-        <v>1.44</v>
-      </c>
-      <c r="W84">
-        <v>1.08</v>
-      </c>
-      <c r="X84">
-        <v>1.04</v>
-      </c>
-      <c r="Y84">
-        <v>1.24</v>
-      </c>
-      <c r="Z84">
-        <v>3.79</v>
-      </c>
-      <c r="AA84">
-        <v>1.77</v>
-      </c>
-      <c r="AB84">
-        <v>1.91</v>
-      </c>
-      <c r="AC84">
-        <v>3.06</v>
-      </c>
-      <c r="AD84">
-        <v>1.35</v>
-      </c>
-      <c r="AE84">
-        <v>1.12</v>
-      </c>
-      <c r="AF84">
-        <v>1.65</v>
-      </c>
-      <c r="AG84">
-        <v>2.08</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.23</v>
-      </c>
-      <c r="AK84">
-        <v>1.67</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O85">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P85">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q85">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R85">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U85">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="V85">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W85">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z85">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA85">
+        <v>1.78</v>
+      </c>
+      <c r="AB85">
+        <v>2.01</v>
+      </c>
+      <c r="AC85">
+        <v>2.78</v>
+      </c>
+      <c r="AD85">
+        <v>1.38</v>
+      </c>
+      <c r="AE85">
+        <v>1.14</v>
+      </c>
+      <c r="AF85">
         <v>1.62</v>
       </c>
-      <c r="AB85">
-        <v>2.25</v>
-      </c>
-      <c r="AC85">
-        <v>2.64</v>
-      </c>
-      <c r="AD85">
-        <v>1.42</v>
-      </c>
-      <c r="AE85">
-        <v>1.17</v>
-      </c>
-      <c r="AF85">
-        <v>1.53</v>
-      </c>
       <c r="AG85">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK85">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O86">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P86">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q86">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R86">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S86">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T86">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U86">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="V86">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z86">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA86">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AB86">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AC86">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AD86">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE86">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF86">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG86">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK86">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="O87">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P87">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="Q87">
-        <v>3.25</v>
+        <v>4.41</v>
       </c>
       <c r="R87">
         <v>2.2</v>
       </c>
       <c r="S87">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U87">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="V87">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y87">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z87">
-        <v>3.28</v>
+        <v>3.86</v>
       </c>
       <c r="AA87">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB87">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AC87">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AD87">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE87">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF87">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG87">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AK87">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T88">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U88">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V88">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W88">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X88">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y88">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z88">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA88">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC88">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD88">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG88">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AK88">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="O94">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P94">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="Q94">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R94">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S94">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T94">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="U94">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V94">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W94">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y94">
         <v>1.29</v>
       </c>
       <c r="Z94">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AA94">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB94">
+        <v>1.71</v>
+      </c>
+      <c r="AC94">
+        <v>3.6</v>
+      </c>
+      <c r="AD94">
+        <v>1.23</v>
+      </c>
+      <c r="AE94">
+        <v>1.08</v>
+      </c>
+      <c r="AF94">
         <v>1.8</v>
       </c>
-      <c r="AC94">
-        <v>3.2</v>
-      </c>
-      <c r="AD94">
-        <v>1.29</v>
-      </c>
-      <c r="AE94">
-        <v>1.12</v>
-      </c>
-      <c r="AF94">
-        <v>1.68</v>
-      </c>
       <c r="AG94">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK94">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="O95">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P95">
-        <v>2.97</v>
+        <v>2.53</v>
       </c>
       <c r="Q95">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R95">
         <v>1.99</v>
       </c>
       <c r="S95">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T95">
         <v>2.66</v>
       </c>
       <c r="U95">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V95">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W95">
         <v>1.05</v>
       </c>
       <c r="X95">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z95">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AA95">
         <v>2</v>
       </c>
       <c r="AB95">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC95">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD95">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE95">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF95">
         <v>1.8</v>
       </c>
       <c r="AG95">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AK95">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,31 +15957,31 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.94</v>
+        <v>2.18</v>
       </c>
       <c r="O96">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="P96">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="Q96">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="R96">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S96">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T96">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="U96">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V96">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W96">
         <v>1.04</v>
@@ -15993,7 +15993,7 @@
         <v>1.29</v>
       </c>
       <c r="Z96">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA96">
         <v>1.87</v>
@@ -16002,35 +16002,35 @@
         <v>1.82</v>
       </c>
       <c r="AC96">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD96">
         <v>1.3</v>
       </c>
       <c r="AE96">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF96">
+        <v>1.72</v>
+      </c>
+      <c r="AG96">
+        <v>2.01</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.25</v>
+      </c>
+      <c r="AK96">
         <v>1.67</v>
-      </c>
-      <c r="AG96">
-        <v>2.05</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.42</v>
-      </c>
-      <c r="AK96">
-        <v>1.44</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.02</v>
+        <v>2.94</v>
       </c>
       <c r="O97">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="P97">
-        <v>3.55</v>
+        <v>2.34</v>
       </c>
       <c r="Q97">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R97">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S97">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T97">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="U97">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V97">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W97">
+        <v>1.04</v>
+      </c>
+      <c r="X97">
         <v>1.05</v>
       </c>
-      <c r="X97">
-        <v>1</v>
-      </c>
       <c r="Y97">
+        <v>1.29</v>
+      </c>
+      <c r="Z97">
+        <v>3.34</v>
+      </c>
+      <c r="AA97">
+        <v>1.87</v>
+      </c>
+      <c r="AB97">
+        <v>1.82</v>
+      </c>
+      <c r="AC97">
+        <v>3.2</v>
+      </c>
+      <c r="AD97">
         <v>1.3</v>
-      </c>
-      <c r="Z97">
-        <v>3</v>
-      </c>
-      <c r="AA97">
-        <v>2</v>
-      </c>
-      <c r="AB97">
-        <v>1.7</v>
-      </c>
-      <c r="AC97">
-        <v>3.74</v>
-      </c>
-      <c r="AD97">
-        <v>1.19</v>
       </c>
       <c r="AE97">
         <v>1.07</v>
       </c>
       <c r="AF97">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AK97">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,40 +16283,40 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="O98">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="P98">
-        <v>2.53</v>
+        <v>3.55</v>
       </c>
       <c r="Q98">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="R98">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S98">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="U98">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="V98">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W98">
         <v>1.05</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z98">
         <v>3</v>
@@ -16328,19 +16328,19 @@
         <v>1.7</v>
       </c>
       <c r="AC98">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AD98">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE98">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF98">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG98">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="O99">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="P99">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="Q99">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R99">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S99">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T99">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="U99">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="V99">
         <v>1.4</v>
       </c>
       <c r="W99">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X99">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
         <v>1.29</v>
       </c>
       <c r="Z99">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA99">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB99">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC99">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD99">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE99">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF99">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG99">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16781,55 +16781,55 @@
         <v>2.42</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.02</v>
+        <v>2.49</v>
       </c>
       <c r="O102">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
       <c r="P102">
-        <v>3.54</v>
+        <v>2.71</v>
       </c>
       <c r="Q102">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S102">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T102">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U102">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W102">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X102">
         <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z102">
         <v>3.3</v>
       </c>
       <c r="AA102">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB102">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC102">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AD102">
         <v>1.3</v>
       </c>
       <c r="AE102">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF102">
         <v>1.75</v>
       </c>
       <c r="AG102">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.14</v>
+        <v>1.31</v>
       </c>
       <c r="O104">
-        <v>3.54</v>
+        <v>5.2</v>
       </c>
       <c r="P104">
-        <v>3.22</v>
+        <v>8.9</v>
       </c>
       <c r="Q104">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="R104">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S104">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T104">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="U104">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="V104">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W104">
+        <v>1.11</v>
+      </c>
+      <c r="X104">
         <v>1.04</v>
       </c>
-      <c r="X104">
-        <v>1.05</v>
-      </c>
       <c r="Y104">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z104">
-        <v>3.6</v>
+        <v>4.37</v>
       </c>
       <c r="AA104">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB104">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC104">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD104">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE104">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF104">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK104">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="O105">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="P105">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="Q105">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R105">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S105">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T105">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U105">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="V105">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W105">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y105">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z105">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA105">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB105">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AC105">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD105">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE105">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF105">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG105">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK105">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.31</v>
+        <v>2.14</v>
       </c>
       <c r="O106">
-        <v>5.2</v>
+        <v>3.54</v>
       </c>
       <c r="P106">
-        <v>8.9</v>
+        <v>3.22</v>
       </c>
       <c r="Q106">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="R106">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S106">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T106">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="U106">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="V106">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W106">
+        <v>1.04</v>
+      </c>
+      <c r="X106">
+        <v>1.05</v>
+      </c>
+      <c r="Y106">
+        <v>1.25</v>
+      </c>
+      <c r="Z106">
+        <v>3.6</v>
+      </c>
+      <c r="AA106">
+        <v>1.82</v>
+      </c>
+      <c r="AB106">
+        <v>1.94</v>
+      </c>
+      <c r="AC106">
+        <v>3.1</v>
+      </c>
+      <c r="AD106">
+        <v>1.33</v>
+      </c>
+      <c r="AE106">
         <v>1.11</v>
       </c>
-      <c r="X106">
-        <v>1.04</v>
-      </c>
-      <c r="Y106">
-        <v>1.21</v>
-      </c>
-      <c r="Z106">
-        <v>4.37</v>
-      </c>
-      <c r="AA106">
-        <v>1.61</v>
-      </c>
-      <c r="AB106">
-        <v>2.15</v>
-      </c>
-      <c r="AC106">
-        <v>2.55</v>
-      </c>
-      <c r="AD106">
-        <v>1.46</v>
-      </c>
-      <c r="AE106">
-        <v>1.14</v>
-      </c>
       <c r="AF106">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG106">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK106">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,61 +17750,61 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O107">
-        <v>3.22</v>
+        <v>3.46</v>
       </c>
       <c r="P107">
-        <v>2.94</v>
+        <v>3.54</v>
       </c>
       <c r="Q107">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R107">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S107">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="U107">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="V107">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W107">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X107">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z107">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA107">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB107">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC107">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="AD107">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE107">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG107">
         <v>1.95</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK107">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="O112">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P112">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q112">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R112">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S112">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U112">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="V112">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W112">
         <v>1.08</v>
       </c>
       <c r="X112">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z112">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AA112">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AB112">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC112">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AD112">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE112">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF112">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG112">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="O113">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P113">
+        <v>2.98</v>
+      </c>
+      <c r="Q113">
+        <v>2.75</v>
+      </c>
+      <c r="R113">
+        <v>2.03</v>
+      </c>
+      <c r="S113">
+        <v>1.36</v>
+      </c>
+      <c r="T113">
+        <v>2.77</v>
+      </c>
+      <c r="U113">
         <v>2.8</v>
       </c>
-      <c r="Q113">
-        <v>3</v>
-      </c>
-      <c r="R113">
-        <v>2</v>
-      </c>
-      <c r="S113">
-        <v>1.42</v>
-      </c>
-      <c r="T113">
-        <v>2.65</v>
-      </c>
-      <c r="U113">
-        <v>3</v>
-      </c>
       <c r="V113">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W113">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y113">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z113">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="AA113">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB113">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AC113">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="AD113">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE113">
         <v>1.06</v>
       </c>
       <c r="AF113">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK113">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="O114">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="P114">
-        <v>3</v>
+        <v>4.84</v>
       </c>
       <c r="Q114">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="R114">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S114">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T114">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U114">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V114">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W114">
         <v>1.08</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y114">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z114">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AA114">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AB114">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC114">
         <v>2.8</v>
       </c>
       <c r="AD114">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE114">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF114">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG114">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK114">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="O115">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="Q115">
+        <v>3</v>
+      </c>
+      <c r="R115">
+        <v>2</v>
+      </c>
+      <c r="S115">
+        <v>1.42</v>
+      </c>
+      <c r="T115">
+        <v>2.65</v>
+      </c>
+      <c r="U115">
+        <v>3</v>
+      </c>
+      <c r="V115">
+        <v>1.35</v>
+      </c>
+      <c r="W115">
+        <v>1.07</v>
+      </c>
+      <c r="X115">
+        <v>1.08</v>
+      </c>
+      <c r="Y115">
+        <v>1.35</v>
+      </c>
+      <c r="Z115">
         <v>2.75</v>
       </c>
-      <c r="R115">
-        <v>2.03</v>
-      </c>
-      <c r="S115">
-        <v>1.36</v>
-      </c>
-      <c r="T115">
-        <v>2.77</v>
-      </c>
-      <c r="U115">
-        <v>2.8</v>
-      </c>
-      <c r="V115">
-        <v>1.4</v>
-      </c>
-      <c r="W115">
-        <v>1.08</v>
-      </c>
-      <c r="X115">
-        <v>1.05</v>
-      </c>
-      <c r="Y115">
-        <v>1.29</v>
-      </c>
-      <c r="Z115">
-        <v>3.52</v>
-      </c>
       <c r="AA115">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB115">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AC115">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="AD115">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE115">
         <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG115">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK115">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="O116">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="P116">
-        <v>4.84</v>
+        <v>3.03</v>
       </c>
       <c r="Q116">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="R116">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S116">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T116">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U116">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V116">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W116">
         <v>1.08</v>
       </c>
       <c r="X116">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z116">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AA116">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AB116">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC116">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD116">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE116">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF116">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG116">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK116">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19878,55 +19878,55 @@
         <v>2.05</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>4.37</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20204,55 +20204,55 @@
         <v>1.58</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -22649,55 +22649,55 @@
         <v>1.84</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22812,55 +22812,55 @@
         <v>3.92</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="O156">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="P156">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q156">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R156">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S156">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T156">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U156">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="V156">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W156">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X156">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z156">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AA156">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB156">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC156">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AD156">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE156">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF156">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG156">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK156">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="O157">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="P157">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q157">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="R157">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S157">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T157">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U157">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="V157">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W157">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X157">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y157">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z157">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA157">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB157">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC157">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AD157">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE157">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF157">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG157">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK157">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G165">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T174">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U174">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V174">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W174">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X174">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y174">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE174">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF174">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG174">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK174">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -29495,34 +29495,34 @@
         <v>4.67</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA179">
         <v>2.03</v>
@@ -29531,19 +29531,19 @@
         <v>1.78</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29984,40 +29984,40 @@
         <v>1.99</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U182">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V182">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W182">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X182">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z182">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB182">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC182">
         <v>1.8</v>
@@ -30026,13 +30026,13 @@
         <v>1.87</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG182">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK182">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -31777,28 +31777,28 @@
         <v>4.4</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W193">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y193">
         <v>1.57</v>
@@ -31807,25 +31807,25 @@
         <v>2.25</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC193">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD193">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>2.05</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -32103,28 +32103,28 @@
         <v>4.59</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y195">
         <v>1.55</v>
@@ -32133,25 +32133,25 @@
         <v>2.25</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,65 +32257,65 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="O196">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="P196">
-        <v>5.93</v>
+        <v>4.66</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y196">
+        <v>1.49</v>
+      </c>
+      <c r="Z196">
+        <v>2.4</v>
+      </c>
+      <c r="AA196">
+        <v>2.7</v>
+      </c>
+      <c r="AB196">
+        <v>1.36</v>
+      </c>
+      <c r="AC196">
+        <v>5.55</v>
+      </c>
+      <c r="AD196">
+        <v>1.08</v>
+      </c>
+      <c r="AE196">
+        <v>1.03</v>
+      </c>
+      <c r="AF196">
+        <v>2.34</v>
+      </c>
+      <c r="AG196">
         <v>1.52</v>
       </c>
-      <c r="Z196">
-        <v>2.35</v>
-      </c>
-      <c r="AA196">
-        <v>0</v>
-      </c>
-      <c r="AB196">
-        <v>0</v>
-      </c>
-      <c r="AC196">
-        <v>0</v>
-      </c>
-      <c r="AD196">
-        <v>0</v>
-      </c>
-      <c r="AE196">
-        <v>0</v>
-      </c>
-      <c r="AF196">
-        <v>0</v>
-      </c>
-      <c r="AG196">
-        <v>0</v>
-      </c>
       <c r="AH196" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="O197">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="P197">
-        <v>4.66</v>
+        <v>5.93</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y197">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z197">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL197">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="O32">
+        <v>3.6</v>
+      </c>
+      <c r="P32">
         <v>3.38</v>
       </c>
-      <c r="P32">
-        <v>2.91</v>
-      </c>
       <c r="Q32">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V32">
+        <v>1.52</v>
+      </c>
+      <c r="W32">
+        <v>1.08</v>
+      </c>
+      <c r="X32">
+        <v>1.03</v>
+      </c>
+      <c r="Y32">
+        <v>1.15</v>
+      </c>
+      <c r="Z32">
+        <v>4.3</v>
+      </c>
+      <c r="AA32">
+        <v>1.62</v>
+      </c>
+      <c r="AB32">
+        <v>2.22</v>
+      </c>
+      <c r="AC32">
+        <v>2.6</v>
+      </c>
+      <c r="AD32">
         <v>1.41</v>
       </c>
-      <c r="W32">
-        <v>1.11</v>
-      </c>
-      <c r="X32">
-        <v>1.05</v>
-      </c>
-      <c r="Y32">
-        <v>1.22</v>
-      </c>
-      <c r="Z32">
-        <v>3.75</v>
-      </c>
-      <c r="AA32">
-        <v>1.88</v>
-      </c>
-      <c r="AB32">
-        <v>1.81</v>
-      </c>
-      <c r="AC32">
-        <v>2.9</v>
-      </c>
-      <c r="AD32">
-        <v>1.38</v>
-      </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="P33">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q33">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U33">
-        <v>2.38</v>
+        <v>2.82</v>
       </c>
       <c r="V33">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA33">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AB33">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="AC33">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="AD33">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="O34">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="P34">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q34">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S34">
+        <v>1.36</v>
+      </c>
+      <c r="T34">
+        <v>2.74</v>
+      </c>
+      <c r="U34">
+        <v>2.96</v>
+      </c>
+      <c r="V34">
         <v>1.35</v>
       </c>
-      <c r="T34">
-        <v>3</v>
-      </c>
-      <c r="U34">
-        <v>2.82</v>
-      </c>
-      <c r="V34">
-        <v>1.36</v>
-      </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA34">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AD34">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.32</v>
+        <v>2.18</v>
       </c>
       <c r="O35">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P35">
-        <v>2</v>
+        <v>2.91</v>
       </c>
       <c r="Q35">
-        <v>3.94</v>
+        <v>2.63</v>
       </c>
       <c r="R35">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="U35">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="V35">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="AA35">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC35">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="AD35">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AE35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AG35">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.76</v>
+        <v>3.66</v>
       </c>
       <c r="O54">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="P54">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q54">
-        <v>3.14</v>
+        <v>3.78</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S54">
+        <v>1.31</v>
+      </c>
+      <c r="T54">
+        <v>3.6</v>
+      </c>
+      <c r="U54">
+        <v>2.47</v>
+      </c>
+      <c r="V54">
+        <v>1.5</v>
+      </c>
+      <c r="W54">
+        <v>1.09</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>1.17</v>
+      </c>
+      <c r="Z54">
+        <v>3.96</v>
+      </c>
+      <c r="AA54">
+        <v>1.7</v>
+      </c>
+      <c r="AB54">
+        <v>2.17</v>
+      </c>
+      <c r="AC54">
+        <v>2.49</v>
+      </c>
+      <c r="AD54">
+        <v>1.42</v>
+      </c>
+      <c r="AE54">
         <v>1.18</v>
       </c>
-      <c r="T54">
-        <v>4.05</v>
-      </c>
-      <c r="U54">
-        <v>1.98</v>
-      </c>
-      <c r="V54">
-        <v>1.76</v>
-      </c>
-      <c r="W54">
-        <v>1.17</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.06</v>
-      </c>
-      <c r="Z54">
-        <v>6.25</v>
-      </c>
-      <c r="AA54">
-        <v>1.33</v>
-      </c>
-      <c r="AB54">
-        <v>2.94</v>
-      </c>
-      <c r="AC54">
-        <v>1.97</v>
-      </c>
-      <c r="AD54">
-        <v>1.84</v>
-      </c>
-      <c r="AE54">
-        <v>1.29</v>
-      </c>
       <c r="AF54">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AG54">
-        <v>2.98</v>
+        <v>2.28</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AK54">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.66</v>
+        <v>2.76</v>
       </c>
       <c r="O55">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="P55">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q55">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="R55">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S55">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="T55">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="U55">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="V55">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="W55">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z55">
-        <v>3.96</v>
+        <v>6.25</v>
       </c>
       <c r="AA55">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AB55">
-        <v>2.17</v>
+        <v>2.94</v>
       </c>
       <c r="AC55">
-        <v>2.49</v>
+        <v>1.97</v>
       </c>
       <c r="AD55">
-        <v>1.42</v>
+        <v>1.84</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AF55">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AG55">
-        <v>2.28</v>
+        <v>2.98</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="AK55">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="O56">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="P56">
-        <v>3.26</v>
+        <v>2.8</v>
       </c>
       <c r="Q56">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R56">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S56">
+        <v>1.2</v>
+      </c>
+      <c r="T56">
+        <v>4</v>
+      </c>
+      <c r="U56">
+        <v>1.97</v>
+      </c>
+      <c r="V56">
+        <v>1.77</v>
+      </c>
+      <c r="W56">
         <v>1.19</v>
-      </c>
-      <c r="T56">
-        <v>3.9</v>
-      </c>
-      <c r="U56">
-        <v>2.05</v>
-      </c>
-      <c r="V56">
-        <v>1.71</v>
-      </c>
-      <c r="W56">
-        <v>1.18</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA56">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AB56">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AC56">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AD56">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE56">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF56">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG56">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK56">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="O57">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="P57">
-        <v>2.8</v>
+        <v>3.26</v>
       </c>
       <c r="Q57">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S57">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U57">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="V57">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="W57">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z57">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA57">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AB57">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AC57">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AD57">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE57">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG57">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK57">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G75">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G102">
@@ -16938,55 +16938,55 @@
         <v>2.49</v>
       </c>
       <c r="O102">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P102">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="Q102">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R102">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T102">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U102">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="V102">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W102">
         <v>1.03</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y102">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="AA102">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AB102">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AC102">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD102">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE102">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF102">
         <v>1.75</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AK102">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.49</v>
+        <v>1.31</v>
       </c>
       <c r="O103">
-        <v>3.28</v>
+        <v>5.2</v>
       </c>
       <c r="P103">
-        <v>2.74</v>
+        <v>8.9</v>
       </c>
       <c r="Q103">
-        <v>3.1</v>
+        <v>1.79</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S103">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T103">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="U103">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="V103">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W103">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X103">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z103">
-        <v>3.39</v>
+        <v>4.37</v>
       </c>
       <c r="AA103">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="AB103">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC103">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD103">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AE103">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="AK103">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="O104">
-        <v>5.2</v>
+        <v>3.22</v>
       </c>
       <c r="P104">
-        <v>8.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q104">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="R104">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S104">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T104">
-        <v>3.15</v>
+        <v>2.53</v>
       </c>
       <c r="U104">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="V104">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="W104">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X104">
+        <v>1.06</v>
+      </c>
+      <c r="Y104">
+        <v>1.33</v>
+      </c>
+      <c r="Z104">
+        <v>3.1</v>
+      </c>
+      <c r="AA104">
+        <v>2.05</v>
+      </c>
+      <c r="AB104">
+        <v>1.66</v>
+      </c>
+      <c r="AC104">
+        <v>3.8</v>
+      </c>
+      <c r="AD104">
+        <v>1.26</v>
+      </c>
+      <c r="AE104">
         <v>1.04</v>
       </c>
-      <c r="Y104">
-        <v>1.21</v>
-      </c>
-      <c r="Z104">
-        <v>4.37</v>
-      </c>
-      <c r="AA104">
-        <v>1.61</v>
-      </c>
-      <c r="AB104">
-        <v>2.15</v>
-      </c>
-      <c r="AC104">
-        <v>2.55</v>
-      </c>
-      <c r="AD104">
-        <v>1.46</v>
-      </c>
-      <c r="AE104">
-        <v>1.14</v>
-      </c>
       <c r="AF104">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AG104">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AK104">
-        <v>3.25</v>
+        <v>1.57</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,61 +17424,61 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O105">
-        <v>3.22</v>
+        <v>3.46</v>
       </c>
       <c r="P105">
-        <v>2.94</v>
+        <v>3.54</v>
       </c>
       <c r="Q105">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R105">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S105">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="U105">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="V105">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W105">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z105">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA105">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB105">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC105">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="AD105">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE105">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG105">
         <v>1.95</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK105">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.02</v>
+        <v>2.49</v>
       </c>
       <c r="O107">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
       <c r="P107">
-        <v>3.54</v>
+        <v>2.71</v>
       </c>
       <c r="Q107">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R107">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S107">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T107">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U107">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V107">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X107">
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z107">
         <v>3.3</v>
       </c>
       <c r="AA107">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB107">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC107">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AD107">
         <v>1.3</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
         <v>1.75</v>
       </c>
       <c r="AG107">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.79</v>
+        <v>3.17</v>
       </c>
       <c r="O108">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="P108">
-        <v>4.32</v>
+        <v>2.16</v>
       </c>
       <c r="Q108">
-        <v>2.17</v>
+        <v>3.5</v>
       </c>
       <c r="R108">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S108">
+        <v>1.32</v>
+      </c>
+      <c r="T108">
+        <v>3</v>
+      </c>
+      <c r="U108">
+        <v>2.77</v>
+      </c>
+      <c r="V108">
+        <v>1.4</v>
+      </c>
+      <c r="W108">
+        <v>1.07</v>
+      </c>
+      <c r="X108">
+        <v>1.01</v>
+      </c>
+      <c r="Y108">
+        <v>1.3</v>
+      </c>
+      <c r="Z108">
+        <v>3.44</v>
+      </c>
+      <c r="AA108">
+        <v>1.85</v>
+      </c>
+      <c r="AB108">
+        <v>1.85</v>
+      </c>
+      <c r="AC108">
+        <v>3.05</v>
+      </c>
+      <c r="AD108">
         <v>1.33</v>
-      </c>
-      <c r="T108">
-        <v>2.77</v>
-      </c>
-      <c r="U108">
-        <v>2.55</v>
-      </c>
-      <c r="V108">
-        <v>1.42</v>
-      </c>
-      <c r="W108">
-        <v>1.05</v>
-      </c>
-      <c r="X108">
-        <v>1.03</v>
-      </c>
-      <c r="Y108">
-        <v>1.25</v>
-      </c>
-      <c r="Z108">
-        <v>3.6</v>
-      </c>
-      <c r="AA108">
-        <v>1.86</v>
-      </c>
-      <c r="AB108">
-        <v>1.84</v>
-      </c>
-      <c r="AC108">
-        <v>3</v>
-      </c>
-      <c r="AD108">
-        <v>1.38</v>
       </c>
       <c r="AE108">
         <v>1.11</v>
       </c>
       <c r="AF108">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AK108">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,52 +18076,52 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.17</v>
+        <v>1.8</v>
       </c>
       <c r="O109">
-        <v>3.46</v>
+        <v>3.68</v>
       </c>
       <c r="P109">
-        <v>2.16</v>
+        <v>4.18</v>
       </c>
       <c r="Q109">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S109">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T109">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U109">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="V109">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W109">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y109">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z109">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="AA109">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB109">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC109">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="AD109">
         <v>1.33</v>
@@ -18130,10 +18130,10 @@
         <v>1.11</v>
       </c>
       <c r="AF109">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG109">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AK109">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="O110">
-        <v>3.68</v>
+        <v>3.15</v>
       </c>
       <c r="P110">
-        <v>4.18</v>
+        <v>3.14</v>
       </c>
       <c r="Q110">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R110">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="S110">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T110">
-        <v>3.02</v>
+        <v>2.33</v>
       </c>
       <c r="U110">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="V110">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="W110">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y110">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="Z110">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA110">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AB110">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AC110">
-        <v>3.24</v>
+        <v>4.72</v>
       </c>
       <c r="AD110">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AE110">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF110">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O111">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="P111">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="Q111">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R111">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="S111">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="T111">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="U111">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="V111">
+        <v>1.4</v>
+      </c>
+      <c r="W111">
+        <v>1.08</v>
+      </c>
+      <c r="X111">
+        <v>1.05</v>
+      </c>
+      <c r="Y111">
         <v>1.29</v>
       </c>
-      <c r="W111">
-        <v>1</v>
-      </c>
-      <c r="X111">
-        <v>1.08</v>
-      </c>
-      <c r="Y111">
-        <v>1.46</v>
-      </c>
       <c r="Z111">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="AA111">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB111">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AC111">
-        <v>4.72</v>
+        <v>3.18</v>
       </c>
       <c r="AD111">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE111">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF111">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG111">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK111">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="O113">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P113">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="Q113">
+        <v>3</v>
+      </c>
+      <c r="R113">
+        <v>2</v>
+      </c>
+      <c r="S113">
+        <v>1.42</v>
+      </c>
+      <c r="T113">
+        <v>2.65</v>
+      </c>
+      <c r="U113">
+        <v>3</v>
+      </c>
+      <c r="V113">
+        <v>1.35</v>
+      </c>
+      <c r="W113">
+        <v>1.07</v>
+      </c>
+      <c r="X113">
+        <v>1.08</v>
+      </c>
+      <c r="Y113">
+        <v>1.35</v>
+      </c>
+      <c r="Z113">
         <v>2.75</v>
       </c>
-      <c r="R113">
-        <v>2.03</v>
-      </c>
-      <c r="S113">
-        <v>1.36</v>
-      </c>
-      <c r="T113">
-        <v>2.77</v>
-      </c>
-      <c r="U113">
-        <v>2.8</v>
-      </c>
-      <c r="V113">
-        <v>1.4</v>
-      </c>
-      <c r="W113">
-        <v>1.08</v>
-      </c>
-      <c r="X113">
-        <v>1.05</v>
-      </c>
-      <c r="Y113">
-        <v>1.29</v>
-      </c>
-      <c r="Z113">
-        <v>3.52</v>
-      </c>
       <c r="AA113">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB113">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AC113">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="AD113">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AE113">
         <v>1.06</v>
       </c>
       <c r="AF113">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG113">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK113">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="O114">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="P114">
-        <v>4.84</v>
+        <v>3.03</v>
       </c>
       <c r="Q114">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="R114">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S114">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T114">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U114">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V114">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W114">
         <v>1.08</v>
       </c>
       <c r="X114">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z114">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AA114">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AB114">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC114">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD114">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE114">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG114">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK114">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.48</v>
+        <v>1.66</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="P115">
+        <v>4.84</v>
+      </c>
+      <c r="Q115">
+        <v>2.15</v>
+      </c>
+      <c r="R115">
+        <v>2.3</v>
+      </c>
+      <c r="S115">
+        <v>1.3</v>
+      </c>
+      <c r="T115">
+        <v>3.3</v>
+      </c>
+      <c r="U115">
+        <v>2.53</v>
+      </c>
+      <c r="V115">
+        <v>1.46</v>
+      </c>
+      <c r="W115">
+        <v>1.08</v>
+      </c>
+      <c r="X115">
+        <v>1.04</v>
+      </c>
+      <c r="Y115">
+        <v>1.24</v>
+      </c>
+      <c r="Z115">
+        <v>3.55</v>
+      </c>
+      <c r="AA115">
+        <v>1.71</v>
+      </c>
+      <c r="AB115">
+        <v>2</v>
+      </c>
+      <c r="AC115">
         <v>2.8</v>
       </c>
-      <c r="Q115">
-        <v>3</v>
-      </c>
-      <c r="R115">
-        <v>2</v>
-      </c>
-      <c r="S115">
+      <c r="AD115">
         <v>1.42</v>
       </c>
-      <c r="T115">
-        <v>2.65</v>
-      </c>
-      <c r="U115">
-        <v>3</v>
-      </c>
-      <c r="V115">
-        <v>1.35</v>
-      </c>
-      <c r="W115">
-        <v>1.07</v>
-      </c>
-      <c r="X115">
-        <v>1.08</v>
-      </c>
-      <c r="Y115">
-        <v>1.35</v>
-      </c>
-      <c r="Z115">
-        <v>2.75</v>
-      </c>
-      <c r="AA115">
-        <v>2.2</v>
-      </c>
-      <c r="AB115">
-        <v>1.58</v>
-      </c>
-      <c r="AC115">
-        <v>4.2</v>
-      </c>
-      <c r="AD115">
-        <v>1.18</v>
-      </c>
       <c r="AE115">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF115">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG115">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK115">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,34 +19217,34 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="O116">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P116">
-        <v>3.03</v>
+        <v>4.32</v>
       </c>
       <c r="Q116">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="R116">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S116">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T116">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U116">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="V116">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W116">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
         <v>1.03</v>
@@ -19253,44 +19253,44 @@
         <v>1.25</v>
       </c>
       <c r="Z116">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA116">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AB116">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC116">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD116">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE116">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF116">
         <v>1.75</v>
       </c>
       <c r="AG116">
+        <v>1.95</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ116">
+        <v>1.18</v>
+      </c>
+      <c r="AK116">
         <v>2.05</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>1.3</v>
-      </c>
-      <c r="AK116">
-        <v>1.68</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>3.14</v>
+        <v>1.66</v>
       </c>
       <c r="O120">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="P120">
-        <v>2.05</v>
+        <v>4.37</v>
       </c>
       <c r="Q120">
-        <v>3.15</v>
+        <v>2.07</v>
       </c>
       <c r="R120">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="S120">
         <v>1.2</v>
       </c>
       <c r="T120">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="U120">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="V120">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W120">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X120">
         <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z120">
-        <v>6.17</v>
+        <v>5.84</v>
       </c>
       <c r="AA120">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB120">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AC120">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AD120">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AE120">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AF120">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG120">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK120">
-        <v>1.39</v>
+        <v>2.19</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.66</v>
+        <v>4.36</v>
       </c>
       <c r="O121">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="P121">
-        <v>4.37</v>
+        <v>1.58</v>
       </c>
       <c r="Q121">
-        <v>2.07</v>
+        <v>3.8</v>
       </c>
       <c r="R121">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="S121">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T121">
-        <v>4.1</v>
+        <v>5.05</v>
       </c>
       <c r="U121">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="V121">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="W121">
+        <v>1.28</v>
+      </c>
+      <c r="X121">
+        <v>1</v>
+      </c>
+      <c r="Y121">
+        <v>1.01</v>
+      </c>
+      <c r="Z121">
+        <v>8.5</v>
+      </c>
+      <c r="AA121">
+        <v>1.19</v>
+      </c>
+      <c r="AB121">
+        <v>3.8</v>
+      </c>
+      <c r="AC121">
+        <v>1.61</v>
+      </c>
+      <c r="AD121">
+        <v>2.25</v>
+      </c>
+      <c r="AE121">
+        <v>1.51</v>
+      </c>
+      <c r="AF121">
+        <v>1.28</v>
+      </c>
+      <c r="AG121">
+        <v>3.34</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
+        <v>1.16</v>
+      </c>
+      <c r="AK121">
         <v>1.17</v>
-      </c>
-      <c r="X121">
-        <v>1.02</v>
-      </c>
-      <c r="Y121">
-        <v>1.12</v>
-      </c>
-      <c r="Z121">
-        <v>5.84</v>
-      </c>
-      <c r="AA121">
-        <v>1.42</v>
-      </c>
-      <c r="AB121">
-        <v>2.66</v>
-      </c>
-      <c r="AC121">
-        <v>2.08</v>
-      </c>
-      <c r="AD121">
-        <v>1.71</v>
-      </c>
-      <c r="AE121">
-        <v>1.25</v>
-      </c>
-      <c r="AF121">
-        <v>1.44</v>
-      </c>
-      <c r="AG121">
-        <v>2.58</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.18</v>
-      </c>
-      <c r="AK121">
-        <v>2.19</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>4.36</v>
+        <v>3.14</v>
       </c>
       <c r="O122">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="P122">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="Q122">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="R122">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="S122">
+        <v>1.2</v>
+      </c>
+      <c r="T122">
+        <v>3.78</v>
+      </c>
+      <c r="U122">
+        <v>2.01</v>
+      </c>
+      <c r="V122">
+        <v>1.74</v>
+      </c>
+      <c r="W122">
+        <v>1.18</v>
+      </c>
+      <c r="X122">
+        <v>1.02</v>
+      </c>
+      <c r="Y122">
         <v>1.11</v>
       </c>
-      <c r="T122">
-        <v>5.05</v>
-      </c>
-      <c r="U122">
-        <v>1.72</v>
-      </c>
-      <c r="V122">
-        <v>2.04</v>
-      </c>
-      <c r="W122">
-        <v>1.28</v>
-      </c>
-      <c r="X122">
-        <v>1</v>
-      </c>
-      <c r="Y122">
-        <v>1.01</v>
-      </c>
       <c r="Z122">
-        <v>8.5</v>
+        <v>6.17</v>
       </c>
       <c r="AA122">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AB122">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC122">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AD122">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AE122">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AF122">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AG122">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK122">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="O193">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="P193">
-        <v>4.4</v>
+        <v>3.13</v>
       </c>
       <c r="Q193">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R193">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S193">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="T193">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U193">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V193">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W193">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X193">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y193">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="Z193">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AA193">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AB193">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC193">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AD193">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE193">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF193">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG193">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK193">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.52</v>
+        <v>1.85</v>
       </c>
       <c r="O194">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="P194">
-        <v>3.13</v>
+        <v>4.59</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y194">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="Z194">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA194">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="AB194">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G195">
@@ -32097,52 +32097,52 @@
         <v>1.85</v>
       </c>
       <c r="O195">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="P195">
-        <v>4.59</v>
+        <v>4.66</v>
       </c>
       <c r="Q195">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="R195">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="S195">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T195">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="U195">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="V195">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W195">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X195">
+        <v>1.07</v>
+      </c>
+      <c r="Y195">
+        <v>1.49</v>
+      </c>
+      <c r="Z195">
+        <v>2.4</v>
+      </c>
+      <c r="AA195">
+        <v>2.7</v>
+      </c>
+      <c r="AB195">
+        <v>1.36</v>
+      </c>
+      <c r="AC195">
+        <v>5.55</v>
+      </c>
+      <c r="AD195">
         <v>1.08</v>
-      </c>
-      <c r="Y195">
-        <v>1.55</v>
-      </c>
-      <c r="Z195">
-        <v>2.25</v>
-      </c>
-      <c r="AA195">
-        <v>2.66</v>
-      </c>
-      <c r="AB195">
-        <v>1.37</v>
-      </c>
-      <c r="AC195">
-        <v>5.3</v>
-      </c>
-      <c r="AD195">
-        <v>1.11</v>
       </c>
       <c r="AE195">
         <v>1.03</v>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK195">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="O196">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="P196">
-        <v>4.66</v>
+        <v>5.93</v>
       </c>
       <c r="Q196">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="R196">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="S196">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T196">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U196">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="V196">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W196">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X196">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y196">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z196">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA196">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AB196">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AC196">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="AD196">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE196">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF196">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AG196">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK196">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="O197">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P197">
-        <v>5.93</v>
+        <v>4.4</v>
       </c>
       <c r="Q197">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="R197">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S197">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T197">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="U197">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="V197">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W197">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X197">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y197">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Z197">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA197">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AB197">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AC197">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AD197">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE197">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF197">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AG197">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK197">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AL197">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.66</v>
+        <v>2.76</v>
       </c>
       <c r="O54">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="P54">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q54">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="R54">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="T54">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="U54">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="W54">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z54">
-        <v>3.96</v>
+        <v>6.25</v>
       </c>
       <c r="AA54">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AB54">
-        <v>2.17</v>
+        <v>2.94</v>
       </c>
       <c r="AC54">
-        <v>2.49</v>
+        <v>1.97</v>
       </c>
       <c r="AD54">
-        <v>1.42</v>
+        <v>1.84</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AF54">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AG54">
-        <v>2.28</v>
+        <v>2.98</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.76</v>
+        <v>3.66</v>
       </c>
       <c r="O55">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="P55">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q55">
-        <v>3.14</v>
+        <v>3.78</v>
       </c>
       <c r="R55">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
+        <v>1.31</v>
+      </c>
+      <c r="T55">
+        <v>3.6</v>
+      </c>
+      <c r="U55">
+        <v>2.47</v>
+      </c>
+      <c r="V55">
+        <v>1.5</v>
+      </c>
+      <c r="W55">
+        <v>1.09</v>
+      </c>
+      <c r="X55">
+        <v>1</v>
+      </c>
+      <c r="Y55">
+        <v>1.17</v>
+      </c>
+      <c r="Z55">
+        <v>3.96</v>
+      </c>
+      <c r="AA55">
+        <v>1.7</v>
+      </c>
+      <c r="AB55">
+        <v>2.17</v>
+      </c>
+      <c r="AC55">
+        <v>2.49</v>
+      </c>
+      <c r="AD55">
+        <v>1.42</v>
+      </c>
+      <c r="AE55">
         <v>1.18</v>
       </c>
-      <c r="T55">
-        <v>4.05</v>
-      </c>
-      <c r="U55">
-        <v>1.98</v>
-      </c>
-      <c r="V55">
-        <v>1.76</v>
-      </c>
-      <c r="W55">
-        <v>1.17</v>
-      </c>
-      <c r="X55">
-        <v>1.01</v>
-      </c>
-      <c r="Y55">
-        <v>1.06</v>
-      </c>
-      <c r="Z55">
-        <v>6.25</v>
-      </c>
-      <c r="AA55">
-        <v>1.33</v>
-      </c>
-      <c r="AB55">
-        <v>2.94</v>
-      </c>
-      <c r="AC55">
-        <v>1.97</v>
-      </c>
-      <c r="AD55">
-        <v>1.84</v>
-      </c>
-      <c r="AE55">
-        <v>1.29</v>
-      </c>
       <c r="AF55">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AG55">
-        <v>2.98</v>
+        <v>2.28</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AK55">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G69">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O84">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P84">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q84">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S84">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T84">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U84">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="V84">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z84">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA84">
+        <v>1.78</v>
+      </c>
+      <c r="AB84">
+        <v>2.01</v>
+      </c>
+      <c r="AC84">
+        <v>2.78</v>
+      </c>
+      <c r="AD84">
+        <v>1.38</v>
+      </c>
+      <c r="AE84">
+        <v>1.14</v>
+      </c>
+      <c r="AF84">
         <v>1.62</v>
       </c>
-      <c r="AB84">
-        <v>2.25</v>
-      </c>
-      <c r="AC84">
-        <v>2.64</v>
-      </c>
-      <c r="AD84">
-        <v>1.42</v>
-      </c>
-      <c r="AE84">
-        <v>1.17</v>
-      </c>
-      <c r="AF84">
-        <v>1.53</v>
-      </c>
       <c r="AG84">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK84">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O85">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P85">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q85">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S85">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T85">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U85">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="V85">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W85">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z85">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA85">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AB85">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AC85">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="AD85">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE85">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF85">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG85">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK85">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="O86">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P86">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="Q86">
-        <v>3.25</v>
+        <v>4.41</v>
       </c>
       <c r="R86">
         <v>2.2</v>
       </c>
       <c r="S86">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T86">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U86">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="V86">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z86">
-        <v>3.28</v>
+        <v>3.86</v>
       </c>
       <c r="AA86">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB86">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AC86">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AD86">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE86">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF86">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG86">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AK86">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q87">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S87">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T87">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U87">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V87">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W87">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y87">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z87">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD87">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF87">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG87">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AK87">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.68</v>
+        <v>2.33</v>
       </c>
       <c r="O93">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="P93">
-        <v>4.77</v>
+        <v>2.97</v>
       </c>
       <c r="Q93">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R93">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="S93">
+        <v>1.42</v>
+      </c>
+      <c r="T93">
+        <v>2.66</v>
+      </c>
+      <c r="U93">
+        <v>2.75</v>
+      </c>
+      <c r="V93">
         <v>1.35</v>
       </c>
-      <c r="T93">
-        <v>2.75</v>
-      </c>
-      <c r="U93">
-        <v>2.8</v>
-      </c>
-      <c r="V93">
-        <v>1.38</v>
-      </c>
       <c r="W93">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y93">
+        <v>1.29</v>
+      </c>
+      <c r="Z93">
+        <v>3.04</v>
+      </c>
+      <c r="AA93">
+        <v>2</v>
+      </c>
+      <c r="AB93">
+        <v>1.71</v>
+      </c>
+      <c r="AC93">
+        <v>3.6</v>
+      </c>
+      <c r="AD93">
+        <v>1.23</v>
+      </c>
+      <c r="AE93">
+        <v>1.08</v>
+      </c>
+      <c r="AF93">
+        <v>1.8</v>
+      </c>
+      <c r="AG93">
+        <v>1.91</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
         <v>1.3</v>
       </c>
-      <c r="Z93">
-        <v>3.2</v>
-      </c>
-      <c r="AA93">
-        <v>1.9</v>
-      </c>
-      <c r="AB93">
-        <v>1.78</v>
-      </c>
-      <c r="AC93">
-        <v>3.5</v>
-      </c>
-      <c r="AD93">
-        <v>1.25</v>
-      </c>
-      <c r="AE93">
-        <v>1.1</v>
-      </c>
-      <c r="AF93">
-        <v>1.85</v>
-      </c>
-      <c r="AG93">
-        <v>1.85</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.2</v>
-      </c>
       <c r="AK93">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="O94">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P94">
-        <v>2.97</v>
+        <v>2.53</v>
       </c>
       <c r="Q94">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R94">
         <v>1.99</v>
       </c>
       <c r="S94">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T94">
         <v>2.66</v>
       </c>
       <c r="U94">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V94">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W94">
         <v>1.05</v>
       </c>
       <c r="X94">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z94">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AA94">
         <v>2</v>
       </c>
       <c r="AB94">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC94">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD94">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE94">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF94">
         <v>1.8</v>
       </c>
       <c r="AG94">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AK94">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="O95">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="P95">
-        <v>2.53</v>
+        <v>3.14</v>
       </c>
       <c r="Q95">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="R95">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="S95">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T95">
-        <v>2.66</v>
+        <v>3.01</v>
       </c>
       <c r="U95">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="V95">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W95">
+        <v>1.04</v>
+      </c>
+      <c r="X95">
         <v>1.05</v>
       </c>
-      <c r="X95">
-        <v>1.01</v>
-      </c>
       <c r="Y95">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z95">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AA95">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB95">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC95">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD95">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE95">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF95">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG95">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AK95">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="O96">
         <v>3.38</v>
       </c>
       <c r="P96">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="Q96">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R96">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S96">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T96">
-        <v>3.01</v>
+        <v>2.69</v>
       </c>
       <c r="U96">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V96">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W96">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X96">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y96">
+        <v>1.3</v>
+      </c>
+      <c r="Z96">
+        <v>3</v>
+      </c>
+      <c r="AA96">
+        <v>2</v>
+      </c>
+      <c r="AB96">
+        <v>1.7</v>
+      </c>
+      <c r="AC96">
+        <v>3.74</v>
+      </c>
+      <c r="AD96">
+        <v>1.19</v>
+      </c>
+      <c r="AE96">
+        <v>1.07</v>
+      </c>
+      <c r="AF96">
+        <v>1.77</v>
+      </c>
+      <c r="AG96">
+        <v>1.85</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
         <v>1.29</v>
       </c>
-      <c r="Z96">
-        <v>3.4</v>
-      </c>
-      <c r="AA96">
-        <v>1.87</v>
-      </c>
-      <c r="AB96">
-        <v>1.82</v>
-      </c>
-      <c r="AC96">
-        <v>3.1</v>
-      </c>
-      <c r="AD96">
-        <v>1.3</v>
-      </c>
-      <c r="AE96">
-        <v>1.1</v>
-      </c>
-      <c r="AF96">
-        <v>1.72</v>
-      </c>
-      <c r="AG96">
-        <v>2.01</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.25</v>
-      </c>
       <c r="AK96">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.94</v>
+        <v>1.68</v>
       </c>
       <c r="O97">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="P97">
-        <v>2.34</v>
+        <v>4.77</v>
       </c>
       <c r="Q97">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R97">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S97">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T97">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="U97">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V97">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W97">
         <v>1.04</v>
       </c>
       <c r="X97">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z97">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA97">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB97">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC97">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD97">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE97">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG97">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.02</v>
+        <v>2.94</v>
       </c>
       <c r="O98">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="P98">
-        <v>3.55</v>
+        <v>2.34</v>
       </c>
       <c r="Q98">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R98">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S98">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T98">
-        <v>2.69</v>
+        <v>3.03</v>
       </c>
       <c r="U98">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V98">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W98">
+        <v>1.04</v>
+      </c>
+      <c r="X98">
         <v>1.05</v>
       </c>
-      <c r="X98">
-        <v>1</v>
-      </c>
       <c r="Y98">
+        <v>1.29</v>
+      </c>
+      <c r="Z98">
+        <v>3.34</v>
+      </c>
+      <c r="AA98">
+        <v>1.87</v>
+      </c>
+      <c r="AB98">
+        <v>1.82</v>
+      </c>
+      <c r="AC98">
+        <v>3.2</v>
+      </c>
+      <c r="AD98">
         <v>1.3</v>
-      </c>
-      <c r="Z98">
-        <v>3</v>
-      </c>
-      <c r="AA98">
-        <v>2</v>
-      </c>
-      <c r="AB98">
-        <v>1.7</v>
-      </c>
-      <c r="AC98">
-        <v>3.74</v>
-      </c>
-      <c r="AD98">
-        <v>1.19</v>
       </c>
       <c r="AE98">
         <v>1.07</v>
       </c>
       <c r="AF98">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AK98">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36208,10 +36208,10 @@
         <v>0</v>
       </c>
       <c r="AA220">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB220">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC220">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O221">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="P221">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36371,10 +36371,10 @@
         <v>0</v>
       </c>
       <c r="AA221">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB221">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC221">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12872,7 +12872,7 @@
         <v>2.65</v>
       </c>
       <c r="R77">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S77">
         <v>1.35</v>
@@ -12899,25 +12899,25 @@
         <v>3</v>
       </c>
       <c r="AA77">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AB77">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AC77">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD77">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE77">
         <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG77">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.94</v>
+        <v>2.29</v>
       </c>
       <c r="O98">
         <v>3.28</v>
       </c>
       <c r="P98">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="Q98">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R98">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S98">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T98">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="U98">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="V98">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W98">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
         <v>1.29</v>
       </c>
       <c r="Z98">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA98">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB98">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC98">
         <v>3.2</v>
       </c>
       <c r="AD98">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE98">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF98">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG98">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
       <c r="O99">
         <v>3.28</v>
       </c>
       <c r="P99">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="Q99">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R99">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S99">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T99">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="U99">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="V99">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W99">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y99">
         <v>1.29</v>
       </c>
       <c r="Z99">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA99">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB99">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC99">
         <v>3.2</v>
       </c>
       <c r="AD99">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE99">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF99">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AK99">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,80 +17587,80 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.14</v>
+        <v>2.49</v>
       </c>
       <c r="O106">
-        <v>3.54</v>
+        <v>3.32</v>
       </c>
       <c r="P106">
-        <v>3.22</v>
+        <v>2.71</v>
       </c>
       <c r="Q106">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R106">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S106">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T106">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U106">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="V106">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W106">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
+        <v>1.28</v>
+      </c>
+      <c r="Z106">
+        <v>3.3</v>
+      </c>
+      <c r="AA106">
+        <v>1.94</v>
+      </c>
+      <c r="AB106">
+        <v>1.82</v>
+      </c>
+      <c r="AC106">
+        <v>3.4</v>
+      </c>
+      <c r="AD106">
+        <v>1.3</v>
+      </c>
+      <c r="AE106">
+        <v>1.1</v>
+      </c>
+      <c r="AF106">
+        <v>1.75</v>
+      </c>
+      <c r="AG106">
+        <v>2</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
         <v>1.25</v>
       </c>
-      <c r="Z106">
-        <v>3.6</v>
-      </c>
-      <c r="AA106">
-        <v>1.82</v>
-      </c>
-      <c r="AB106">
-        <v>1.94</v>
-      </c>
-      <c r="AC106">
-        <v>3.1</v>
-      </c>
-      <c r="AD106">
-        <v>1.33</v>
-      </c>
-      <c r="AE106">
-        <v>1.11</v>
-      </c>
-      <c r="AF106">
-        <v>1.65</v>
-      </c>
-      <c r="AG106">
-        <v>2.1</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>1.3</v>
-      </c>
       <c r="AK106">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.49</v>
+        <v>2.14</v>
       </c>
       <c r="O107">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="P107">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="Q107">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R107">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S107">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T107">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="U107">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V107">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W107">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y107">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z107">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA107">
+        <v>1.82</v>
+      </c>
+      <c r="AB107">
         <v>1.94</v>
       </c>
-      <c r="AB107">
-        <v>1.82</v>
-      </c>
       <c r="AC107">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD107">
+        <v>1.33</v>
+      </c>
+      <c r="AE107">
+        <v>1.11</v>
+      </c>
+      <c r="AF107">
+        <v>1.65</v>
+      </c>
+      <c r="AG107">
+        <v>2.1</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.3</v>
       </c>
-      <c r="AE107">
-        <v>1.1</v>
-      </c>
-      <c r="AF107">
-        <v>1.75</v>
-      </c>
-      <c r="AG107">
-        <v>2</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.25</v>
-      </c>
       <c r="AK107">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="O114">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="P114">
-        <v>3.03</v>
+        <v>4.84</v>
       </c>
       <c r="Q114">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="R114">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S114">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T114">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U114">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V114">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W114">
         <v>1.08</v>
       </c>
       <c r="X114">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y114">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z114">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AA114">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AB114">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AC114">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AD114">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE114">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF114">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG114">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK114">
-        <v>1.68</v>
+        <v>2.23</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="O115">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P115">
-        <v>4.84</v>
+        <v>4.32</v>
       </c>
       <c r="Q115">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R115">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S115">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="U115">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V115">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z115">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA115">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AB115">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AC115">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD115">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE115">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF115">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG115">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,34 +19217,34 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="O116">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P116">
-        <v>4.32</v>
+        <v>3.03</v>
       </c>
       <c r="Q116">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="R116">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S116">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T116">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U116">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="V116">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W116">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X116">
         <v>1.03</v>
@@ -19253,28 +19253,28 @@
         <v>1.25</v>
       </c>
       <c r="Z116">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA116">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AB116">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC116">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AD116">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE116">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF116">
         <v>1.75</v>
       </c>
       <c r="AG116">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK116">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -26887,55 +26887,55 @@
         <v>0</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T167">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U167">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V167">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W167">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X167">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y167">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z167">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD167">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE167">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG167">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK167">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29658,55 +29658,55 @@
         <v>0</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W180">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29821,34 +29821,34 @@
         <v>4.84</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S181">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T181">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U181">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V181">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W181">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X181">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y181">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z181">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA181">
         <v>1.91</v>
@@ -29857,19 +29857,19 @@
         <v>1.81</v>
       </c>
       <c r="AC181">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD181">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG181">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK181">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T185">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U185">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X185">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK185">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30636,55 +30636,55 @@
         <v>3.58</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30799,55 +30799,55 @@
         <v>5.48</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S190">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="T190">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="U190">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V190">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="W190">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X190">
         <v>0</v>
       </c>
       <c r="Y190">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z190">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AC190">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD190">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE190">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF190">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG190">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK190">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC191">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD191">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31614,55 +31614,55 @@
         <v>1.22</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S192">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T192">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U192">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V192">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W192">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y192">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z192">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC192">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD192">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE192">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF192">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG192">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK192">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -32592,55 +32592,55 @@
         <v>0</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T198">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V198">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X198">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y198">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z198">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE198">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG198">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32918,55 +32918,55 @@
         <v>1.64</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S200">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T200">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U200">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V200">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W200">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X200">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y200">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z200">
-        <v>0</v>
+        <v>6.94</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC200">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD200">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE200">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG200">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK200">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33244,34 +33244,34 @@
         <v>2.54</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S202">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T202">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U202">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V202">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W202">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X202">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y202">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z202">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA202">
         <v>1.8</v>
@@ -33280,19 +33280,19 @@
         <v>1.87</v>
       </c>
       <c r="AC202">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD202">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE202">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF202">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG202">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK202">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33407,55 +33407,55 @@
         <v>3.87</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R203">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S203">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T203">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U203">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V203">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W203">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X203">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y203">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z203">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA203">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB203">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC203">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD203">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG203">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK203">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33570,55 +33570,55 @@
         <v>5.15</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S204">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T204">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U204">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V204">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W204">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X204">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y204">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z204">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC204">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD204">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG204">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK204">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA205">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q206">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R206">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S206">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T206">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U206">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V206">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W206">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X206">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y206">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z206">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA206">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB206">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC206">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD206">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE206">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF206">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG206">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AK206">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34059,55 +34059,55 @@
         <v>2.99</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S207">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T207">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U207">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V207">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W207">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X207">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y207">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z207">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA207">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB207">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG207">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK207">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34741,10 +34741,10 @@
         <v>0</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC211">
         <v>0</v>
@@ -34904,10 +34904,10 @@
         <v>0</v>
       </c>
       <c r="AA212">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB212">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC212">
         <v>0</v>
@@ -35363,34 +35363,34 @@
         <v>3.45</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S215">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T215">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U215">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V215">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W215">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X215">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA215">
         <v>1.98</v>
@@ -35399,19 +35399,19 @@
         <v>1.83</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD215">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK215">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -36015,34 +36015,34 @@
         <v>3.89</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U219">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V219">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W219">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X219">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y219">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z219">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA219">
         <v>1.57</v>
@@ -36051,19 +36051,19 @@
         <v>2.25</v>
       </c>
       <c r="AC219">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD219">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG219">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK219">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36178,34 +36178,34 @@
         <v>3.85</v>
       </c>
       <c r="Q220">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R220">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S220">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T220">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U220">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V220">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W220">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X220">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y220">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z220">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA220">
         <v>2.25</v>
@@ -36214,19 +36214,19 @@
         <v>1.55</v>
       </c>
       <c r="AC220">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD220">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE220">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF220">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG220">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK220">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R221">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S221">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T221">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U221">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V221">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W221">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X221">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y221">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z221">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA221">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB221">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC221">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD221">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG221">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK221">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36667,34 +36667,34 @@
         <v>5.03</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T223">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U223">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V223">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W223">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X223">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z223">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA223">
         <v>1.91</v>
@@ -36703,19 +36703,19 @@
         <v>1.81</v>
       </c>
       <c r="AC223">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD223">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG223">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK223">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36821,64 +36821,64 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36993,34 +36993,34 @@
         <v>1.37</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T225">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U225">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V225">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X225">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA225">
         <v>1.58</v>
@@ -37029,19 +37029,19 @@
         <v>2.2</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="O234">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="P234">
-        <v>3.77</v>
+        <v>3.68</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38484,16 +38484,16 @@
         <v>0</v>
       </c>
       <c r="Y234">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Z234">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC234">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="O235">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="P235">
-        <v>3.68</v>
+        <v>3.77</v>
       </c>
       <c r="Q235">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R235">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S235">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T235">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U235">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V235">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W235">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X235">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y235">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="Z235">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA235">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="AB235">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AC235">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD235">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE235">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF235">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG235">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK235">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O255">
-        <v>4.09</v>
+        <v>3.95</v>
       </c>
       <c r="P255">
-        <v>4.68</v>
+        <v>3.1</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -41913,16 +41913,16 @@
         <v>0</v>
       </c>
       <c r="AA255">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB255">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE255">
         <v>0</v>
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,55 +42037,55 @@
         </is>
       </c>
       <c r="N256">
+        <v>1.75</v>
+      </c>
+      <c r="O256">
+        <v>4.09</v>
+      </c>
+      <c r="P256">
+        <v>4.68</v>
+      </c>
+      <c r="Q256">
+        <v>0</v>
+      </c>
+      <c r="R256">
+        <v>0</v>
+      </c>
+      <c r="S256">
+        <v>0</v>
+      </c>
+      <c r="T256">
+        <v>0</v>
+      </c>
+      <c r="U256">
+        <v>0</v>
+      </c>
+      <c r="V256">
+        <v>0</v>
+      </c>
+      <c r="W256">
+        <v>0</v>
+      </c>
+      <c r="X256">
+        <v>0</v>
+      </c>
+      <c r="Y256">
+        <v>0</v>
+      </c>
+      <c r="Z256">
+        <v>0</v>
+      </c>
+      <c r="AA256">
+        <v>1.58</v>
+      </c>
+      <c r="AB256">
         <v>2.2</v>
       </c>
-      <c r="O256">
-        <v>3.95</v>
-      </c>
-      <c r="P256">
-        <v>3.1</v>
-      </c>
-      <c r="Q256">
-        <v>0</v>
-      </c>
-      <c r="R256">
-        <v>0</v>
-      </c>
-      <c r="S256">
-        <v>0</v>
-      </c>
-      <c r="T256">
-        <v>0</v>
-      </c>
-      <c r="U256">
-        <v>0</v>
-      </c>
-      <c r="V256">
-        <v>0</v>
-      </c>
-      <c r="W256">
-        <v>0</v>
-      </c>
-      <c r="X256">
-        <v>0</v>
-      </c>
-      <c r="Y256">
-        <v>0</v>
-      </c>
-      <c r="Z256">
-        <v>0</v>
-      </c>
-      <c r="AA256">
-        <v>0</v>
-      </c>
-      <c r="AB256">
-        <v>0</v>
-      </c>
       <c r="AC256">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD256">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE256">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.18</v>
+        <v>3.32</v>
       </c>
       <c r="O33">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>2.91</v>
+        <v>2</v>
       </c>
       <c r="Q33">
-        <v>2.63</v>
+        <v>3.94</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="U33">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="V33">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="AA33">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD33">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="P34">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q34">
-        <v>3.94</v>
+        <v>3.12</v>
       </c>
       <c r="R34">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
+        <v>1.35</v>
+      </c>
+      <c r="T34">
+        <v>3</v>
+      </c>
+      <c r="U34">
+        <v>2.82</v>
+      </c>
+      <c r="V34">
         <v>1.36</v>
       </c>
-      <c r="T34">
-        <v>2.74</v>
-      </c>
-      <c r="U34">
-        <v>2.96</v>
-      </c>
-      <c r="V34">
-        <v>1.35</v>
-      </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
         <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA34">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC34">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AD34">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="AK34">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="O35">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="P35">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="Q35">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U35">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W35">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
         <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AA35">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB35">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC35">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AD35">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
+        <v>1.63</v>
+      </c>
+      <c r="AG35">
+        <v>2.15</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.33</v>
+      </c>
+      <c r="AK35">
         <v>1.67</v>
-      </c>
-      <c r="AG35">
-        <v>2.05</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.23</v>
-      </c>
-      <c r="AK35">
-        <v>1.45</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="Q42">
-        <v>3.67</v>
+        <v>2.58</v>
       </c>
       <c r="R42">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA42">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC42">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD42">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,65 +7318,65 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="O43">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="Q43">
-        <v>2.58</v>
+        <v>3.67</v>
       </c>
       <c r="R43">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U43">
+        <v>2.5</v>
+      </c>
+      <c r="V43">
+        <v>1.54</v>
+      </c>
+      <c r="W43">
+        <v>1.08</v>
+      </c>
+      <c r="X43">
+        <v>1.04</v>
+      </c>
+      <c r="Y43">
+        <v>1.21</v>
+      </c>
+      <c r="Z43">
+        <v>4.1</v>
+      </c>
+      <c r="AA43">
+        <v>1.67</v>
+      </c>
+      <c r="AB43">
+        <v>2.16</v>
+      </c>
+      <c r="AC43">
+        <v>2.7</v>
+      </c>
+      <c r="AD43">
+        <v>1.42</v>
+      </c>
+      <c r="AE43">
+        <v>1.13</v>
+      </c>
+      <c r="AF43">
+        <v>1.53</v>
+      </c>
+      <c r="AG43">
         <v>2.3</v>
       </c>
-      <c r="V43">
-        <v>1.57</v>
-      </c>
-      <c r="W43">
-        <v>1.15</v>
-      </c>
-      <c r="X43">
-        <v>1.03</v>
-      </c>
-      <c r="Y43">
-        <v>1.2</v>
-      </c>
-      <c r="Z43">
-        <v>4.33</v>
-      </c>
-      <c r="AA43">
-        <v>1.62</v>
-      </c>
-      <c r="AB43">
-        <v>2.25</v>
-      </c>
-      <c r="AC43">
-        <v>2.2</v>
-      </c>
-      <c r="AD43">
-        <v>1.6</v>
-      </c>
-      <c r="AE43">
-        <v>1.18</v>
-      </c>
-      <c r="AF43">
-        <v>1.4</v>
-      </c>
-      <c r="AG43">
-        <v>2.45</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AK43">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="O84">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P84">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="Q84">
-        <v>3.25</v>
+        <v>4.41</v>
       </c>
       <c r="R84">
         <v>2.2</v>
       </c>
       <c r="S84">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T84">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U84">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="V84">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z84">
-        <v>3.28</v>
+        <v>3.86</v>
       </c>
       <c r="AA84">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB84">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AC84">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AD84">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE84">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF84">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG84">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AK84">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q85">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S85">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T85">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U85">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V85">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W85">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y85">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z85">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AA85">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC85">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD85">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE85">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG85">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AK85">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P87">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q87">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R87">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S87">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="T87">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="U87">
-        <v>2.47</v>
+        <v>2.82</v>
       </c>
       <c r="V87">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W87">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z87">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA87">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AB87">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AC87">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="AD87">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE87">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF87">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG87">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK87">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,61 +15794,61 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="O95">
-        <v>3.74</v>
+        <v>3.38</v>
       </c>
       <c r="P95">
-        <v>4.77</v>
+        <v>3.55</v>
       </c>
       <c r="Q95">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R95">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S95">
+        <v>1.36</v>
+      </c>
+      <c r="T95">
+        <v>2.69</v>
+      </c>
+      <c r="U95">
+        <v>3</v>
+      </c>
+      <c r="V95">
         <v>1.35</v>
       </c>
-      <c r="T95">
-        <v>2.75</v>
-      </c>
-      <c r="U95">
-        <v>2.8</v>
-      </c>
-      <c r="V95">
-        <v>1.38</v>
-      </c>
       <c r="W95">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X95">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y95">
         <v>1.3</v>
       </c>
       <c r="Z95">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA95">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB95">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC95">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AD95">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE95">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF95">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG95">
         <v>1.85</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK95">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
       <c r="O96">
         <v>3.28</v>
       </c>
       <c r="P96">
-        <v>3.01</v>
+        <v>2.34</v>
       </c>
       <c r="Q96">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R96">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S96">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T96">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="U96">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="V96">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y96">
         <v>1.29</v>
       </c>
       <c r="Z96">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA96">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB96">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC96">
         <v>3.2</v>
       </c>
       <c r="AD96">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE96">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF96">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG96">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AK96">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.94</v>
+        <v>1.68</v>
       </c>
       <c r="O97">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="P97">
-        <v>2.34</v>
+        <v>4.77</v>
       </c>
       <c r="Q97">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R97">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S97">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T97">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="U97">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V97">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W97">
         <v>1.04</v>
       </c>
       <c r="X97">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z97">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA97">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB97">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC97">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD97">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE97">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG97">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="O98">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="P98">
-        <v>3.55</v>
+        <v>3.01</v>
       </c>
       <c r="Q98">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R98">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S98">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T98">
-        <v>2.69</v>
+        <v>3.02</v>
       </c>
       <c r="U98">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="V98">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W98">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z98">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA98">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB98">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC98">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="AD98">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AE98">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF98">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG98">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,80 +17098,80 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.49</v>
+        <v>2.14</v>
       </c>
       <c r="O103">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P103">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="Q103">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="R103">
         <v>2.1</v>
       </c>
       <c r="S103">
+        <v>1.33</v>
+      </c>
+      <c r="T103">
+        <v>2.89</v>
+      </c>
+      <c r="U103">
+        <v>2.69</v>
+      </c>
+      <c r="V103">
         <v>1.42</v>
       </c>
-      <c r="T103">
-        <v>2.8</v>
-      </c>
-      <c r="U103">
-        <v>2.89</v>
-      </c>
-      <c r="V103">
-        <v>1.36</v>
-      </c>
       <c r="W103">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y103">
+        <v>1.25</v>
+      </c>
+      <c r="Z103">
+        <v>3.6</v>
+      </c>
+      <c r="AA103">
+        <v>1.82</v>
+      </c>
+      <c r="AB103">
+        <v>1.94</v>
+      </c>
+      <c r="AC103">
+        <v>3.1</v>
+      </c>
+      <c r="AD103">
+        <v>1.33</v>
+      </c>
+      <c r="AE103">
+        <v>1.11</v>
+      </c>
+      <c r="AF103">
+        <v>1.65</v>
+      </c>
+      <c r="AG103">
+        <v>2.1</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ103">
         <v>1.3</v>
       </c>
-      <c r="Z103">
-        <v>3.39</v>
-      </c>
-      <c r="AA103">
-        <v>2.01</v>
-      </c>
-      <c r="AB103">
-        <v>1.76</v>
-      </c>
-      <c r="AC103">
-        <v>3.6</v>
-      </c>
-      <c r="AD103">
-        <v>1.26</v>
-      </c>
-      <c r="AE103">
-        <v>1.05</v>
-      </c>
-      <c r="AF103">
-        <v>1.75</v>
-      </c>
-      <c r="AG103">
-        <v>2</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ103">
-        <v>1.48</v>
-      </c>
       <c r="AK103">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.14</v>
+        <v>2.49</v>
       </c>
       <c r="O104">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="P104">
-        <v>3.22</v>
+        <v>2.74</v>
       </c>
       <c r="Q104">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="R104">
         <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T104">
+        <v>2.8</v>
+      </c>
+      <c r="U104">
         <v>2.89</v>
       </c>
-      <c r="U104">
-        <v>2.69</v>
-      </c>
       <c r="V104">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W104">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X104">
+        <v>1.06</v>
+      </c>
+      <c r="Y104">
+        <v>1.3</v>
+      </c>
+      <c r="Z104">
+        <v>3.39</v>
+      </c>
+      <c r="AA104">
+        <v>2.01</v>
+      </c>
+      <c r="AB104">
+        <v>1.76</v>
+      </c>
+      <c r="AC104">
+        <v>3.6</v>
+      </c>
+      <c r="AD104">
+        <v>1.26</v>
+      </c>
+      <c r="AE104">
         <v>1.05</v>
       </c>
-      <c r="Y104">
-        <v>1.25</v>
-      </c>
-      <c r="Z104">
-        <v>3.6</v>
-      </c>
-      <c r="AA104">
-        <v>1.82</v>
-      </c>
-      <c r="AB104">
-        <v>1.94</v>
-      </c>
-      <c r="AC104">
-        <v>3.1</v>
-      </c>
-      <c r="AD104">
-        <v>1.33</v>
-      </c>
-      <c r="AE104">
-        <v>1.11</v>
-      </c>
       <c r="AF104">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK104">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,80 +18239,80 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O110">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P110">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q110">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R110">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="S110">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T110">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="V110">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
         <v>1.08</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z110">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="AA110">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AB110">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC110">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="AD110">
+        <v>1.41</v>
+      </c>
+      <c r="AE110">
+        <v>1.15</v>
+      </c>
+      <c r="AF110">
+        <v>1.6</v>
+      </c>
+      <c r="AG110">
+        <v>2.25</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
         <v>1.3</v>
       </c>
-      <c r="AE110">
-        <v>1.06</v>
-      </c>
-      <c r="AF110">
-        <v>1.7</v>
-      </c>
-      <c r="AG110">
-        <v>2.05</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>1.44</v>
-      </c>
       <c r="AK110">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="O111">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
+        <v>2.8</v>
+      </c>
+      <c r="Q111">
         <v>3</v>
       </c>
-      <c r="Q111">
-        <v>2.88</v>
-      </c>
       <c r="R111">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T111">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U111">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="V111">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W111">
+        <v>1.07</v>
+      </c>
+      <c r="X111">
         <v>1.08</v>
       </c>
-      <c r="X111">
-        <v>1.02</v>
-      </c>
       <c r="Y111">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="Z111">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="AA111">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AB111">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AC111">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD111">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AE111">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF111">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG111">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK111">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="O112">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P112">
+        <v>2.98</v>
+      </c>
+      <c r="Q112">
+        <v>2.75</v>
+      </c>
+      <c r="R112">
+        <v>2.03</v>
+      </c>
+      <c r="S112">
+        <v>1.36</v>
+      </c>
+      <c r="T112">
+        <v>2.77</v>
+      </c>
+      <c r="U112">
         <v>2.8</v>
       </c>
-      <c r="Q112">
-        <v>3</v>
-      </c>
-      <c r="R112">
-        <v>2</v>
-      </c>
-      <c r="S112">
-        <v>1.42</v>
-      </c>
-      <c r="T112">
-        <v>2.65</v>
-      </c>
-      <c r="U112">
-        <v>3</v>
-      </c>
       <c r="V112">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W112">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X112">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y112">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z112">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="AA112">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB112">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AC112">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="AD112">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE112">
         <v>1.06</v>
       </c>
       <c r="AF112">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG112">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK112">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G157">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G163">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,80 +40570,80 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.77</v>
+        <v>2.61</v>
       </c>
       <c r="O247">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="P247">
-        <v>3.75</v>
+        <v>2.51</v>
       </c>
       <c r="Q247">
-        <v>2.29</v>
+        <v>3.32</v>
       </c>
       <c r="R247">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="S247">
+        <v>1.4</v>
+      </c>
+      <c r="T247">
+        <v>2.62</v>
+      </c>
+      <c r="U247">
+        <v>3.02</v>
+      </c>
+      <c r="V247">
+        <v>1.36</v>
+      </c>
+      <c r="W247">
+        <v>1.04</v>
+      </c>
+      <c r="X247">
+        <v>1.02</v>
+      </c>
+      <c r="Y247">
+        <v>1.32</v>
+      </c>
+      <c r="Z247">
+        <v>3.22</v>
+      </c>
+      <c r="AA247">
+        <v>2.05</v>
+      </c>
+      <c r="AB247">
+        <v>1.75</v>
+      </c>
+      <c r="AC247">
+        <v>3.56</v>
+      </c>
+      <c r="AD247">
+        <v>1.24</v>
+      </c>
+      <c r="AE247">
+        <v>1.05</v>
+      </c>
+      <c r="AF247">
+        <v>1.75</v>
+      </c>
+      <c r="AG247">
+        <v>1.92</v>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ247">
         <v>1.28</v>
       </c>
-      <c r="T247">
-        <v>3.15</v>
-      </c>
-      <c r="U247">
-        <v>2.41</v>
-      </c>
-      <c r="V247">
-        <v>1.47</v>
-      </c>
-      <c r="W247">
-        <v>1.08</v>
-      </c>
-      <c r="X247">
-        <v>1.03</v>
-      </c>
-      <c r="Y247">
-        <v>1.18</v>
-      </c>
-      <c r="Z247">
-        <v>3.92</v>
-      </c>
-      <c r="AA247">
-        <v>1.75</v>
-      </c>
-      <c r="AB247">
-        <v>1.93</v>
-      </c>
-      <c r="AC247">
-        <v>2.66</v>
-      </c>
-      <c r="AD247">
-        <v>1.37</v>
-      </c>
-      <c r="AE247">
-        <v>1.16</v>
-      </c>
-      <c r="AF247">
-        <v>1.62</v>
-      </c>
-      <c r="AG247">
-        <v>2.15</v>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ247">
-        <v>1.2</v>
-      </c>
       <c r="AK247">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,64 +40733,64 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.61</v>
+        <v>1.77</v>
       </c>
       <c r="O248">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="P248">
-        <v>2.51</v>
+        <v>3.75</v>
       </c>
       <c r="Q248">
-        <v>3.32</v>
+        <v>2.29</v>
       </c>
       <c r="R248">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S248">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T248">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="U248">
-        <v>3.02</v>
+        <v>2.41</v>
       </c>
       <c r="V248">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W248">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X248">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y248">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="Z248">
-        <v>3.22</v>
+        <v>3.92</v>
       </c>
       <c r="AA248">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AB248">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC248">
-        <v>3.56</v>
+        <v>2.66</v>
       </c>
       <c r="AD248">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AE248">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF248">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG248">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK248">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AL248">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G19">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.87</v>
+        <v>2.18</v>
       </c>
       <c r="O25">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="P25">
-        <v>1.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
-        <v>3.94</v>
+        <v>2.8</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="V25">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
+        <v>1.11</v>
+      </c>
+      <c r="X25">
         <v>1.05</v>
       </c>
-      <c r="X25">
-        <v>1</v>
-      </c>
       <c r="Y25">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>3.3</v>
+        <v>4.16</v>
       </c>
       <c r="AA25">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC25">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="AD25">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF25">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.81</v>
+        <v>3.87</v>
       </c>
       <c r="O26">
-        <v>3.33</v>
+        <v>3.61</v>
       </c>
       <c r="P26">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="Q26">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="T26">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U26">
-        <v>3.04</v>
+        <v>2.61</v>
       </c>
       <c r="V26">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
         <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA26">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="AD26">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
         <v>1.25</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.18</v>
+        <v>3.81</v>
       </c>
       <c r="O27">
+        <v>3.33</v>
+      </c>
+      <c r="P27">
+        <v>2.07</v>
+      </c>
+      <c r="Q27">
+        <v>4.5</v>
+      </c>
+      <c r="R27">
+        <v>2.1</v>
+      </c>
+      <c r="S27">
+        <v>1.46</v>
+      </c>
+      <c r="T27">
+        <v>2.53</v>
+      </c>
+      <c r="U27">
+        <v>3.04</v>
+      </c>
+      <c r="V27">
+        <v>1.33</v>
+      </c>
+      <c r="W27">
+        <v>1.05</v>
+      </c>
+      <c r="X27">
+        <v>1.06</v>
+      </c>
+      <c r="Y27">
+        <v>1.36</v>
+      </c>
+      <c r="Z27">
+        <v>2.9</v>
+      </c>
+      <c r="AA27">
+        <v>2.1</v>
+      </c>
+      <c r="AB27">
+        <v>1.7</v>
+      </c>
+      <c r="AC27">
         <v>3.62</v>
       </c>
-      <c r="P27">
-        <v>3.2</v>
-      </c>
-      <c r="Q27">
-        <v>2.8</v>
-      </c>
-      <c r="R27">
-        <v>2.3</v>
-      </c>
-      <c r="S27">
-        <v>1.3</v>
-      </c>
-      <c r="T27">
-        <v>3.2</v>
-      </c>
-      <c r="U27">
-        <v>2.6</v>
-      </c>
-      <c r="V27">
-        <v>1.46</v>
-      </c>
-      <c r="W27">
-        <v>1.11</v>
-      </c>
-      <c r="X27">
-        <v>1.05</v>
-      </c>
-      <c r="Y27">
-        <v>1.23</v>
-      </c>
-      <c r="Z27">
-        <v>4.16</v>
-      </c>
-      <c r="AA27">
-        <v>1.74</v>
-      </c>
-      <c r="AB27">
-        <v>2.05</v>
-      </c>
-      <c r="AC27">
-        <v>2.86</v>
-      </c>
       <c r="AD27">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="O42">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="Q42">
-        <v>2.58</v>
+        <v>3.67</v>
       </c>
       <c r="R42">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U42">
+        <v>2.5</v>
+      </c>
+      <c r="V42">
+        <v>1.54</v>
+      </c>
+      <c r="W42">
+        <v>1.08</v>
+      </c>
+      <c r="X42">
+        <v>1.04</v>
+      </c>
+      <c r="Y42">
+        <v>1.21</v>
+      </c>
+      <c r="Z42">
+        <v>4.1</v>
+      </c>
+      <c r="AA42">
+        <v>1.67</v>
+      </c>
+      <c r="AB42">
+        <v>2.16</v>
+      </c>
+      <c r="AC42">
+        <v>2.7</v>
+      </c>
+      <c r="AD42">
+        <v>1.42</v>
+      </c>
+      <c r="AE42">
+        <v>1.13</v>
+      </c>
+      <c r="AF42">
+        <v>1.53</v>
+      </c>
+      <c r="AG42">
         <v>2.3</v>
       </c>
-      <c r="V42">
-        <v>1.57</v>
-      </c>
-      <c r="W42">
-        <v>1.15</v>
-      </c>
-      <c r="X42">
-        <v>1.03</v>
-      </c>
-      <c r="Y42">
-        <v>1.2</v>
-      </c>
-      <c r="Z42">
-        <v>4.33</v>
-      </c>
-      <c r="AA42">
-        <v>1.62</v>
-      </c>
-      <c r="AB42">
-        <v>2.25</v>
-      </c>
-      <c r="AC42">
-        <v>2.2</v>
-      </c>
-      <c r="AD42">
-        <v>1.6</v>
-      </c>
-      <c r="AE42">
-        <v>1.18</v>
-      </c>
-      <c r="AF42">
-        <v>1.4</v>
-      </c>
-      <c r="AG42">
-        <v>2.45</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AK42">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="Q43">
-        <v>3.67</v>
+        <v>2.58</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V43">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA43">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB43">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC43">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AD43">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R76">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S76">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T76">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U76">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V76">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W76">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z76">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD76">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK76">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="O94">
-        <v>3.38</v>
+        <v>3.74</v>
       </c>
       <c r="P94">
-        <v>3.14</v>
+        <v>4.77</v>
       </c>
       <c r="Q94">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="R94">
         <v>2.15</v>
       </c>
       <c r="S94">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T94">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="U94">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V94">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
         <v>1.04</v>
       </c>
       <c r="X94">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z94">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA94">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB94">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC94">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD94">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE94">
         <v>1.1</v>
       </c>
       <c r="AF94">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG94">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK94">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="O95">
         <v>3.38</v>
       </c>
       <c r="P95">
-        <v>3.55</v>
+        <v>3.14</v>
       </c>
       <c r="Q95">
+        <v>2.62</v>
+      </c>
+      <c r="R95">
+        <v>2.15</v>
+      </c>
+      <c r="S95">
+        <v>1.39</v>
+      </c>
+      <c r="T95">
+        <v>3.01</v>
+      </c>
+      <c r="U95">
         <v>2.75</v>
       </c>
-      <c r="R95">
-        <v>2.05</v>
-      </c>
-      <c r="S95">
-        <v>1.36</v>
-      </c>
-      <c r="T95">
-        <v>2.69</v>
-      </c>
-      <c r="U95">
-        <v>3</v>
-      </c>
       <c r="V95">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W95">
+        <v>1.04</v>
+      </c>
+      <c r="X95">
         <v>1.05</v>
       </c>
-      <c r="X95">
-        <v>1</v>
-      </c>
       <c r="Y95">
+        <v>1.29</v>
+      </c>
+      <c r="Z95">
+        <v>3.4</v>
+      </c>
+      <c r="AA95">
+        <v>1.87</v>
+      </c>
+      <c r="AB95">
+        <v>1.82</v>
+      </c>
+      <c r="AC95">
+        <v>3.1</v>
+      </c>
+      <c r="AD95">
         <v>1.3</v>
       </c>
-      <c r="Z95">
-        <v>3</v>
-      </c>
-      <c r="AA95">
-        <v>2</v>
-      </c>
-      <c r="AB95">
-        <v>1.7</v>
-      </c>
-      <c r="AC95">
-        <v>3.74</v>
-      </c>
-      <c r="AD95">
-        <v>1.19</v>
-      </c>
       <c r="AE95">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF95">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AG95">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK95">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.94</v>
+        <v>2.29</v>
       </c>
       <c r="O96">
         <v>3.28</v>
       </c>
       <c r="P96">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="Q96">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R96">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S96">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T96">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="U96">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="V96">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W96">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
         <v>1.29</v>
       </c>
       <c r="Z96">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA96">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB96">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC96">
         <v>3.2</v>
       </c>
       <c r="AD96">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE96">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF96">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG96">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.68</v>
+        <v>2.94</v>
       </c>
       <c r="O97">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="P97">
-        <v>4.77</v>
+        <v>2.34</v>
       </c>
       <c r="Q97">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R97">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S97">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T97">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="U97">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V97">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W97">
         <v>1.04</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y97">
+        <v>1.29</v>
+      </c>
+      <c r="Z97">
+        <v>3.34</v>
+      </c>
+      <c r="AA97">
+        <v>1.87</v>
+      </c>
+      <c r="AB97">
+        <v>1.82</v>
+      </c>
+      <c r="AC97">
+        <v>3.2</v>
+      </c>
+      <c r="AD97">
         <v>1.3</v>
       </c>
-      <c r="Z97">
-        <v>3.2</v>
-      </c>
-      <c r="AA97">
-        <v>1.9</v>
-      </c>
-      <c r="AB97">
-        <v>1.78</v>
-      </c>
-      <c r="AC97">
-        <v>3.5</v>
-      </c>
-      <c r="AD97">
-        <v>1.25</v>
-      </c>
       <c r="AE97">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF97">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AK97">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="O98">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="P98">
-        <v>3.01</v>
+        <v>3.55</v>
       </c>
       <c r="Q98">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R98">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S98">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
-        <v>3.02</v>
+        <v>2.69</v>
       </c>
       <c r="U98">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="V98">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W98">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y98">
+        <v>1.3</v>
+      </c>
+      <c r="Z98">
+        <v>3</v>
+      </c>
+      <c r="AA98">
+        <v>2</v>
+      </c>
+      <c r="AB98">
+        <v>1.7</v>
+      </c>
+      <c r="AC98">
+        <v>3.74</v>
+      </c>
+      <c r="AD98">
+        <v>1.19</v>
+      </c>
+      <c r="AE98">
+        <v>1.07</v>
+      </c>
+      <c r="AF98">
+        <v>1.77</v>
+      </c>
+      <c r="AG98">
+        <v>1.85</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
         <v>1.29</v>
       </c>
-      <c r="Z98">
-        <v>3.3</v>
-      </c>
-      <c r="AA98">
-        <v>1.89</v>
-      </c>
-      <c r="AB98">
-        <v>1.8</v>
-      </c>
-      <c r="AC98">
-        <v>3.2</v>
-      </c>
-      <c r="AD98">
-        <v>1.29</v>
-      </c>
-      <c r="AE98">
-        <v>1.12</v>
-      </c>
-      <c r="AF98">
-        <v>1.68</v>
-      </c>
-      <c r="AG98">
-        <v>2.03</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.25</v>
-      </c>
       <c r="AK98">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="O112">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="P112">
-        <v>2.98</v>
+        <v>4.84</v>
       </c>
       <c r="Q112">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="R112">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T112">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="U112">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="V112">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W112">
         <v>1.08</v>
       </c>
       <c r="X112">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y112">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z112">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="AA112">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AB112">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC112">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="AD112">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE112">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF112">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG112">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AK112">
-        <v>1.45</v>
+        <v>2.23</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="O113">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P113">
-        <v>4.84</v>
+        <v>4.32</v>
       </c>
       <c r="Q113">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R113">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S113">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T113">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="U113">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V113">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W113">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X113">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z113">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA113">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AB113">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AC113">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD113">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE113">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF113">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG113">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK113">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="O114">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P114">
-        <v>4.32</v>
+        <v>2.98</v>
       </c>
       <c r="Q114">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="R114">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S114">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T114">
         <v>2.77</v>
       </c>
       <c r="U114">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="V114">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W114">
+        <v>1.08</v>
+      </c>
+      <c r="X114">
         <v>1.05</v>
       </c>
-      <c r="X114">
-        <v>1.03</v>
-      </c>
       <c r="Y114">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z114">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AA114">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB114">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC114">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AD114">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE114">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF114">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG114">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AK114">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -20204,10 +20204,10 @@
         <v>6.22</v>
       </c>
       <c r="Q122">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="R122">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S122">
         <v>1.3</v>
@@ -20216,7 +20216,7 @@
         <v>3.2</v>
       </c>
       <c r="U122">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V122">
         <v>1.5</v>
@@ -20228,31 +20228,31 @@
         <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z122">
         <v>4.3</v>
       </c>
       <c r="AA122">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB122">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="AC122">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD122">
         <v>1.4</v>
       </c>
       <c r="AE122">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF122">
         <v>1.9</v>
       </c>
       <c r="AG122">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK122">
         <v>2.88</v>
@@ -23304,28 +23304,28 @@
         <v>3.25</v>
       </c>
       <c r="R141">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S141">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T141">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U141">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V141">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W141">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X141">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y141">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z141">
         <v>2.95</v>
@@ -23334,7 +23334,7 @@
         <v>2.1</v>
       </c>
       <c r="AB141">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC141">
         <v>3.7</v>
@@ -23349,7 +23349,7 @@
         <v>1.8</v>
       </c>
       <c r="AG141">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK141">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="O142">
-        <v>6.53</v>
+        <v>5.5</v>
       </c>
       <c r="P142">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25124,10 +25124,10 @@
         <v>0</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC152">
         <v>0</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,64 +41385,64 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="O252">
-        <v>3.66</v>
+        <v>3.79</v>
       </c>
       <c r="P252">
-        <v>2.85</v>
+        <v>3.17</v>
       </c>
       <c r="Q252">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R252">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S252">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T252">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U252">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V252">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W252">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X252">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z252">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA252">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB252">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC252">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD252">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE252">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF252">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG252">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK252">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,77 +41548,77 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="O253">
-        <v>3.79</v>
+        <v>4.21</v>
       </c>
       <c r="P253">
-        <v>3.17</v>
+        <v>2.68</v>
       </c>
       <c r="Q253">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="R253">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="S253">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T253">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="U253">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="V253">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="W253">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="X253">
         <v>1.01</v>
       </c>
       <c r="Y253">
+        <v>1.02</v>
+      </c>
+      <c r="Z253">
+        <v>7.9</v>
+      </c>
+      <c r="AA253">
+        <v>1.24</v>
+      </c>
+      <c r="AB253">
+        <v>3.6</v>
+      </c>
+      <c r="AC253">
+        <v>1.77</v>
+      </c>
+      <c r="AD253">
+        <v>1.93</v>
+      </c>
+      <c r="AE253">
+        <v>1.4</v>
+      </c>
+      <c r="AF253">
+        <v>1.26</v>
+      </c>
+      <c r="AG253">
+        <v>3.45</v>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ253">
         <v>1.2</v>
-      </c>
-      <c r="Z253">
-        <v>4.6</v>
-      </c>
-      <c r="AA253">
-        <v>1.62</v>
-      </c>
-      <c r="AB253">
-        <v>2.15</v>
-      </c>
-      <c r="AC253">
-        <v>2.57</v>
-      </c>
-      <c r="AD253">
-        <v>1.47</v>
-      </c>
-      <c r="AE253">
-        <v>1.17</v>
-      </c>
-      <c r="AF253">
-        <v>1.5</v>
-      </c>
-      <c r="AG253">
-        <v>2.4</v>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ253">
-        <v>1.38</v>
       </c>
       <c r="AK253">
         <v>1.62</v>
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,64 +41711,64 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O254">
-        <v>4.21</v>
+        <v>3.66</v>
       </c>
       <c r="P254">
-        <v>2.68</v>
+        <v>3.06</v>
       </c>
       <c r="Q254">
+        <v>2.7</v>
+      </c>
+      <c r="R254">
+        <v>2.3</v>
+      </c>
+      <c r="S254">
+        <v>1.29</v>
+      </c>
+      <c r="T254">
+        <v>3.25</v>
+      </c>
+      <c r="U254">
         <v>2.45</v>
       </c>
-      <c r="R254">
-        <v>2.6</v>
-      </c>
-      <c r="S254">
-        <v>1.17</v>
-      </c>
-      <c r="T254">
-        <v>5</v>
-      </c>
-      <c r="U254">
-        <v>1.78</v>
-      </c>
       <c r="V254">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="W254">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="X254">
         <v>1.01</v>
       </c>
       <c r="Y254">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="Z254">
-        <v>7.9</v>
+        <v>4.16</v>
       </c>
       <c r="AA254">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="AB254">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="AC254">
-        <v>1.77</v>
+        <v>2.82</v>
       </c>
       <c r="AD254">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="AE254">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AF254">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="AG254">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK254">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,64 +41874,64 @@
         </is>
       </c>
       <c r="N255">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="O255">
         <v>3.66</v>
       </c>
       <c r="P255">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="Q255">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R255">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S255">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T255">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U255">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V255">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W255">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X255">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y255">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z255">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AA255">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB255">
         <v>2.05</v>
       </c>
       <c r="AC255">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AD255">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE255">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF255">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG255">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK255">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL255">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="O2">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="R2">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="S2">
         <v>1.52</v>
       </c>
       <c r="T2">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="U2">
         <v>3.42</v>
@@ -662,7 +662,7 @@
         <v>1.26</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X2">
         <v>1.04</v>
@@ -671,7 +671,7 @@
         <v>1.43</v>
       </c>
       <c r="Z2">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="AA2">
         <v>2.42</v>
@@ -680,7 +680,7 @@
         <v>1.55</v>
       </c>
       <c r="AC2">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="AD2">
         <v>1.18</v>
@@ -692,7 +692,7 @@
         <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="O9">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>4.38</v>
+        <v>4.75</v>
       </c>
       <c r="Q9">
         <v>2.36</v>
@@ -1797,7 +1797,7 @@
         <v>2.5</v>
       </c>
       <c r="U9">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="V9">
         <v>1.32</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK9">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,77 +1939,77 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P10">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
         <v>3.2</v>
       </c>
       <c r="R10">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S10">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.87</v>
+        <v>2.57</v>
       </c>
       <c r="U10">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
         <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AA10">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AB10">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD10">
+        <v>1.28</v>
+      </c>
+      <c r="AE10">
+        <v>1.09</v>
+      </c>
+      <c r="AF10">
+        <v>1.76</v>
+      </c>
+      <c r="AG10">
+        <v>1.96</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.25</v>
-      </c>
-      <c r="AE10">
-        <v>1.06</v>
-      </c>
-      <c r="AF10">
-        <v>1.75</v>
-      </c>
-      <c r="AG10">
-        <v>1.93</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.29</v>
       </c>
       <c r="AK10">
         <v>1.4</v>
@@ -2102,28 +2102,28 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O11">
-        <v>3.73</v>
+        <v>3.6</v>
       </c>
       <c r="P11">
-        <v>4.81</v>
+        <v>4.72</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="U11">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="V11">
         <v>1.36</v>
@@ -2132,34 +2132,34 @@
         <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB11">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC11">
-        <v>3.53</v>
+        <v>3.38</v>
       </c>
       <c r="AD11">
         <v>1.24</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
         <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK11">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="O13">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P13">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="R13">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
         <v>1.41</v>
       </c>
       <c r="T13">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
         <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AA13">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC13">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="AD13">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK13">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="O14">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="Q14">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="R14">
         <v>1.99</v>
@@ -2612,13 +2612,13 @@
         <v>2.59</v>
       </c>
       <c r="U14">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1.07</v>
@@ -2630,10 +2630,10 @@
         <v>2.94</v>
       </c>
       <c r="AA14">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AB14">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC14">
         <v>3.74</v>
@@ -2642,10 +2642,10 @@
         <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG14">
         <v>1.86</v>
@@ -2664,7 +2664,7 @@
         <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,52 +3569,52 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q20">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
         <v>1.41</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z20">
         <v>3.19</v>
       </c>
       <c r="AA20">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AB20">
         <v>1.74</v>
       </c>
       <c r="AC20">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AD20">
         <v>1.23</v>
@@ -3623,10 +3623,10 @@
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="P23">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="Q23">
         <v>2.72</v>
       </c>
       <c r="R23">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S23">
         <v>1.44</v>
@@ -4079,7 +4079,7 @@
         <v>2.57</v>
       </c>
       <c r="U23">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V23">
         <v>1.36</v>
@@ -4091,25 +4091,25 @@
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z23">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="AA23">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB23">
         <v>1.66</v>
       </c>
       <c r="AC23">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="AD23">
         <v>1.2</v>
       </c>
       <c r="AE23">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
         <v>1.83</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="O24">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="P24">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="Q24">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="R24">
         <v>2.05</v>
@@ -4239,46 +4239,46 @@
         <v>1.42</v>
       </c>
       <c r="T24">
+        <v>2.65</v>
+      </c>
+      <c r="U24">
         <v>2.88</v>
-      </c>
-      <c r="U24">
-        <v>2.77</v>
       </c>
       <c r="V24">
         <v>1.37</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
         <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AA24">
         <v>2</v>
       </c>
       <c r="AB24">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC24">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AD24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE24">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
         <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,58 +4384,58 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="O25">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="Q25">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R25">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U25">
         <v>2.6</v>
       </c>
       <c r="V25">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
+        <v>1.08</v>
+      </c>
+      <c r="X25">
+        <v>1.01</v>
+      </c>
+      <c r="Y25">
+        <v>1.2</v>
+      </c>
+      <c r="Z25">
+        <v>3.74</v>
+      </c>
+      <c r="AA25">
+        <v>1.76</v>
+      </c>
+      <c r="AB25">
+        <v>2.08</v>
+      </c>
+      <c r="AC25">
+        <v>2.68</v>
+      </c>
+      <c r="AD25">
+        <v>1.39</v>
+      </c>
+      <c r="AE25">
         <v>1.11</v>
-      </c>
-      <c r="X25">
-        <v>1.05</v>
-      </c>
-      <c r="Y25">
-        <v>1.23</v>
-      </c>
-      <c r="Z25">
-        <v>4.16</v>
-      </c>
-      <c r="AA25">
-        <v>1.74</v>
-      </c>
-      <c r="AB25">
-        <v>2.05</v>
-      </c>
-      <c r="AC25">
-        <v>2.86</v>
-      </c>
-      <c r="AD25">
-        <v>1.37</v>
-      </c>
-      <c r="AE25">
-        <v>1.12</v>
       </c>
       <c r="AF25">
         <v>1.59</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
         <v>1.65</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.87</v>
+        <v>3.33</v>
       </c>
       <c r="O26">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q26">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="R26">
         <v>2.2</v>
@@ -4565,43 +4565,43 @@
         <v>1.39</v>
       </c>
       <c r="T26">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="V26">
         <v>1.39</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
         <v>1.9</v>
       </c>
       <c r="AC26">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="AD26">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
         <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG26">
         <v>2</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.81</v>
+        <v>3.85</v>
       </c>
       <c r="O27">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="Q27">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S27">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U27">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V27">
+        <v>1.36</v>
+      </c>
+      <c r="W27">
+        <v>1.03</v>
+      </c>
+      <c r="X27">
+        <v>1.03</v>
+      </c>
+      <c r="Y27">
         <v>1.33</v>
       </c>
-      <c r="W27">
-        <v>1.05</v>
-      </c>
-      <c r="X27">
-        <v>1.06</v>
-      </c>
-      <c r="Y27">
-        <v>1.36</v>
-      </c>
       <c r="Z27">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB27">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC27">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="Q32">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5546,43 +5546,43 @@
         <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="V32">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="AA32">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AB32">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AC32">
         <v>2.6</v>
       </c>
       <c r="AD32">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG32">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>2</v>
       </c>
       <c r="Q33">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="R33">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="S33">
+        <v>1.37</v>
+      </c>
+      <c r="T33">
+        <v>2.56</v>
+      </c>
+      <c r="U33">
+        <v>3.05</v>
+      </c>
+      <c r="V33">
         <v>1.36</v>
       </c>
-      <c r="T33">
-        <v>2.74</v>
-      </c>
-      <c r="U33">
-        <v>2.96</v>
-      </c>
-      <c r="V33">
-        <v>1.35</v>
-      </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB33">
         <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AD33">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
         <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,31 +5860,31 @@
         <v>2.6</v>
       </c>
       <c r="Q34">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
         <v>1.04</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
         <v>3.34</v>
@@ -5893,22 +5893,22 @@
         <v>1.87</v>
       </c>
       <c r="AB34">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC34">
         <v>3.14</v>
       </c>
       <c r="AD34">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
         <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
         <v>1.45</v>
@@ -6014,61 +6014,61 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="Q35">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T35">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U35">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="V35">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
         <v>3.75</v>
       </c>
       <c r="AA35">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AB35">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC35">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD35">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE35">
         <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
         <v>2.15</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,28 +6177,28 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O36">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q36">
         <v>4.2</v>
       </c>
       <c r="R36">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="S36">
         <v>1.47</v>
       </c>
       <c r="T36">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="U36">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="V36">
         <v>1.3</v>
@@ -6210,7 +6210,7 @@
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z36">
         <v>2.81</v>
@@ -6219,13 +6219,13 @@
         <v>2.23</v>
       </c>
       <c r="AB36">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC36">
         <v>3.98</v>
       </c>
       <c r="AD36">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
         <v>1.02</v>
@@ -6349,13 +6349,13 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R37">
         <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T37">
         <v>3.44</v>
@@ -6364,37 +6364,37 @@
         <v>2.2</v>
       </c>
       <c r="V37">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>4.87</v>
+        <v>4.89</v>
       </c>
       <c r="AA37">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB37">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC37">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AD37">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF37">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG37">
         <v>2.45</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,55 +6503,55 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.15</v>
       </c>
       <c r="P38">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="Q38">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R38">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U38">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V38">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z38">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA38">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AC38">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="AD38">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AE38">
         <v>1.25</v>
@@ -6560,7 +6560,7 @@
         <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6992,55 +6992,55 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="O41">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="Q41">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="R41">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
         <v>3.6</v>
       </c>
       <c r="U41">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="V41">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W41">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
         <v>4.33</v>
       </c>
       <c r="AA41">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AC41">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AD41">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE41">
         <v>1.14</v>
@@ -7049,7 +7049,7 @@
         <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK41">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P42">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="Q42">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="R42">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U42">
         <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W42">
         <v>1.08</v>
@@ -7188,10 +7188,10 @@
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA42">
         <v>1.67</v>
@@ -7200,19 +7200,19 @@
         <v>2.16</v>
       </c>
       <c r="AC42">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AD42">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
         <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O43">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="Q43">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="R43">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
+        <v>1.27</v>
+      </c>
+      <c r="T43">
+        <v>3.8</v>
+      </c>
+      <c r="U43">
+        <v>2.22</v>
+      </c>
+      <c r="V43">
+        <v>1.56</v>
+      </c>
+      <c r="W43">
+        <v>1.12</v>
+      </c>
+      <c r="X43">
+        <v>1.02</v>
+      </c>
+      <c r="Y43">
+        <v>1.14</v>
+      </c>
+      <c r="Z43">
+        <v>5.15</v>
+      </c>
+      <c r="AA43">
+        <v>1.57</v>
+      </c>
+      <c r="AB43">
+        <v>2.43</v>
+      </c>
+      <c r="AC43">
+        <v>2.4</v>
+      </c>
+      <c r="AD43">
+        <v>1.59</v>
+      </c>
+      <c r="AE43">
+        <v>1.24</v>
+      </c>
+      <c r="AF43">
+        <v>1.46</v>
+      </c>
+      <c r="AG43">
+        <v>2.55</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.25</v>
       </c>
-      <c r="T43">
-        <v>3.2</v>
-      </c>
-      <c r="U43">
-        <v>2.3</v>
-      </c>
-      <c r="V43">
-        <v>1.57</v>
-      </c>
-      <c r="W43">
-        <v>1.15</v>
-      </c>
-      <c r="X43">
-        <v>1.03</v>
-      </c>
-      <c r="Y43">
-        <v>1.2</v>
-      </c>
-      <c r="Z43">
-        <v>4.33</v>
-      </c>
-      <c r="AA43">
-        <v>1.62</v>
-      </c>
-      <c r="AB43">
-        <v>2.25</v>
-      </c>
-      <c r="AC43">
-        <v>2.2</v>
-      </c>
-      <c r="AD43">
-        <v>1.6</v>
-      </c>
-      <c r="AE43">
-        <v>1.18</v>
-      </c>
-      <c r="AF43">
-        <v>1.4</v>
-      </c>
-      <c r="AG43">
-        <v>2.45</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.24</v>
-      </c>
       <c r="AK43">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="O44">
-        <v>3.73</v>
+        <v>3.66</v>
       </c>
       <c r="P44">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="Q44">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="R44">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S44">
         <v>1.33</v>
@@ -7502,10 +7502,10 @@
         <v>3.2</v>
       </c>
       <c r="U44">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W44">
         <v>1.09</v>
@@ -7514,31 +7514,31 @@
         <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AA44">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB44">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC44">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="AD44">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE44">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG44">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.31</v>
       </c>
       <c r="AK44">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="O46">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="P46">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R46">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S46">
         <v>1.36</v>
@@ -7831,40 +7831,40 @@
         <v>2.82</v>
       </c>
       <c r="V46">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W46">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y46">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z46">
         <v>3</v>
       </c>
       <c r="AA46">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB46">
         <v>1.7</v>
       </c>
       <c r="AC46">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AD46">
         <v>1.25</v>
       </c>
       <c r="AE46">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF46">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG46">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK46">
         <v>1.44</v>
@@ -7970,58 +7970,58 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="O47">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P47">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q47">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="R47">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S47">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="U47">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V47">
         <v>1.36</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y47">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z47">
         <v>3.3</v>
       </c>
       <c r="AA47">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB47">
         <v>1.75</v>
       </c>
       <c r="AC47">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD47">
         <v>1.25</v>
       </c>
       <c r="AE47">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
         <v>1.75</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="O48">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="Q48">
+        <v>2.81</v>
+      </c>
+      <c r="R48">
+        <v>2.05</v>
+      </c>
+      <c r="S48">
+        <v>1.41</v>
+      </c>
+      <c r="T48">
+        <v>2.62</v>
+      </c>
+      <c r="U48">
         <v>2.88</v>
       </c>
-      <c r="R48">
-        <v>2.18</v>
-      </c>
-      <c r="S48">
+      <c r="V48">
         <v>1.39</v>
       </c>
-      <c r="T48">
-        <v>2.69</v>
-      </c>
-      <c r="U48">
-        <v>2.95</v>
-      </c>
-      <c r="V48">
-        <v>1.38</v>
-      </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA48">
         <v>1.98</v>
       </c>
       <c r="AB48">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC48">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AD48">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE48">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
         <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,52 +8459,52 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="O50">
+        <v>3.4</v>
+      </c>
+      <c r="P50">
         <v>3.2</v>
       </c>
-      <c r="P50">
-        <v>3.31</v>
-      </c>
       <c r="Q50">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R50">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T50">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="U50">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V50">
         <v>1.36</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y50">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z50">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="AA50">
         <v>2.1</v>
       </c>
       <c r="AB50">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC50">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AD50">
         <v>1.25</v>
@@ -8516,7 +8516,7 @@
         <v>1.83</v>
       </c>
       <c r="AG50">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK50">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="O51">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q51">
-        <v>3.52</v>
+        <v>3.9</v>
       </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T51">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="V51">
         <v>1.38</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y51">
+        <v>1.32</v>
+      </c>
+      <c r="Z51">
+        <v>2.99</v>
+      </c>
+      <c r="AA51">
+        <v>1.98</v>
+      </c>
+      <c r="AB51">
+        <v>1.78</v>
+      </c>
+      <c r="AC51">
+        <v>3.3</v>
+      </c>
+      <c r="AD51">
         <v>1.28</v>
       </c>
-      <c r="Z51">
-        <v>3.12</v>
-      </c>
-      <c r="AA51">
-        <v>1.88</v>
-      </c>
-      <c r="AB51">
-        <v>1.8</v>
-      </c>
-      <c r="AC51">
-        <v>3.5</v>
-      </c>
-      <c r="AD51">
-        <v>1.25</v>
-      </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG51">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AK51">
         <v>1.26</v>
@@ -8785,58 +8785,58 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="O52">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P52">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q52">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="R52">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S52">
         <v>1.36</v>
       </c>
       <c r="T52">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V52">
         <v>1.41</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA52">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB52">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC52">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="AD52">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
         <v>1.67</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AK52">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="O53">
         <v>3.8</v>
       </c>
       <c r="P53">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q53">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R53">
         <v>2.5</v>
@@ -8966,13 +8966,13 @@
         <v>1.18</v>
       </c>
       <c r="T53">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="U53">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V53">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W53">
         <v>1.17</v>
@@ -8981,16 +8981,16 @@
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z53">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AA53">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB53">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AC53">
         <v>1.97</v>
@@ -8999,29 +8999,29 @@
         <v>1.84</v>
       </c>
       <c r="AE53">
+        <v>1.35</v>
+      </c>
+      <c r="AF53">
+        <v>1.36</v>
+      </c>
+      <c r="AG53">
+        <v>2.88</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.21</v>
+      </c>
+      <c r="AK53">
         <v>1.29</v>
-      </c>
-      <c r="AF53">
-        <v>1.33</v>
-      </c>
-      <c r="AG53">
-        <v>2.98</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.26</v>
-      </c>
-      <c r="AK53">
-        <v>1.41</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.66</v>
+        <v>3.25</v>
       </c>
       <c r="O54">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q54">
-        <v>3.78</v>
+        <v>3.15</v>
       </c>
       <c r="R54">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S54">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="U54">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W54">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
         <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>3.96</v>
+        <v>3.65</v>
       </c>
       <c r="AA54">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB54">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AC54">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="AD54">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AG54">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AK54">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>2.8</v>
       </c>
       <c r="Q55">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R55">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S55">
+        <v>1.19</v>
+      </c>
+      <c r="T55">
+        <v>3.84</v>
+      </c>
+      <c r="U55">
+        <v>2.02</v>
+      </c>
+      <c r="V55">
+        <v>1.7</v>
+      </c>
+      <c r="W55">
         <v>1.2</v>
-      </c>
-      <c r="T55">
-        <v>4</v>
-      </c>
-      <c r="U55">
-        <v>1.97</v>
-      </c>
-      <c r="V55">
-        <v>1.77</v>
-      </c>
-      <c r="W55">
-        <v>1.19</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z55">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA55">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB55">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AC55">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD55">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE55">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AF55">
         <v>1.36</v>
       </c>
       <c r="AG55">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK55">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,22 +9446,22 @@
         <v>3.26</v>
       </c>
       <c r="Q56">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="R56">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="S56">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U56">
         <v>2.05</v>
       </c>
       <c r="V56">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W56">
         <v>1.18</v>
@@ -9470,16 +9470,16 @@
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA56">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB56">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AC56">
         <v>2.09</v>
@@ -9488,13 +9488,13 @@
         <v>1.76</v>
       </c>
       <c r="AE56">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF56">
         <v>1.39</v>
       </c>
       <c r="AG56">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK56">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10587,25 +10587,25 @@
         <v>7.65</v>
       </c>
       <c r="Q63">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R63">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="S63">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T63">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="U63">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V63">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="W63">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X63">
         <v>0</v>
@@ -10614,7 +10614,7 @@
         <v>1.02</v>
       </c>
       <c r="Z63">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="AA63">
         <v>1.21</v>
@@ -10632,10 +10632,10 @@
         <v>1.49</v>
       </c>
       <c r="AF63">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG63">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK63">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -11556,61 +11556,61 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O69">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P69">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q69">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="R69">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="S69">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T69">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="U69">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V69">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z69">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="AA69">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AB69">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AC69">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD69">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE69">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF69">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG69">
         <v>2.15</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="O70">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="P70">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="Q70">
         <v>4.2</v>
@@ -11737,7 +11737,7 @@
         <v>1.46</v>
       </c>
       <c r="T70">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U70">
         <v>3.26</v>
@@ -11758,13 +11758,13 @@
         <v>2.74</v>
       </c>
       <c r="AA70">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AB70">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC70">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="AD70">
         <v>1.22</v>
@@ -11891,55 +11891,55 @@
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T71">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U71">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V71">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W71">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y71">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z71">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB71">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC71">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD71">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE71">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF71">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG71">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AK71">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12054,25 +12054,25 @@
         <v>2.33</v>
       </c>
       <c r="Q72">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="R72">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S72">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U72">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V72">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W72">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X72">
         <v>1.03</v>
@@ -12084,25 +12084,25 @@
         <v>4.03</v>
       </c>
       <c r="AA72">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB72">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC72">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD72">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE72">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF72">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG72">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK72">
         <v>1.5</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O75">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P75">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q75">
         <v>3.8</v>
       </c>
       <c r="R75">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="S75">
         <v>1.29</v>
       </c>
       <c r="T75">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U75">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="V75">
         <v>1.53</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
         <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z75">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA75">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB75">
         <v>2.27</v>
       </c>
       <c r="AC75">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="AD75">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE75">
         <v>1.2</v>
       </c>
       <c r="AF75">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG75">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,25 +12860,25 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="O77">
-        <v>4.82</v>
+        <v>4.35</v>
       </c>
       <c r="P77">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q77">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R77">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S77">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="U77">
         <v>2.81</v>
@@ -12899,13 +12899,13 @@
         <v>3.44</v>
       </c>
       <c r="AA77">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AB77">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AC77">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AD77">
         <v>1.28</v>
@@ -12917,7 +12917,7 @@
         <v>2.16</v>
       </c>
       <c r="AG77">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AK77">
         <v>3.08</v>
@@ -13023,25 +13023,25 @@
         </is>
       </c>
       <c r="N78">
-        <v>6.25</v>
+        <v>4.6</v>
       </c>
       <c r="O78">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="P78">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="Q78">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="R78">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T78">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="U78">
         <v>2.48</v>
@@ -13056,28 +13056,28 @@
         <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
         <v>4.1</v>
       </c>
       <c r="AA78">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB78">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC78">
         <v>2.52</v>
       </c>
       <c r="AD78">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE78">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF78">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
         <v>2.12</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>2.01</v>
+        <v>1.19</v>
       </c>
       <c r="AK78">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13207,10 +13207,10 @@
         <v>2.91</v>
       </c>
       <c r="U79">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V79">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W79">
         <v>1.07</v>
@@ -13222,19 +13222,19 @@
         <v>1.24</v>
       </c>
       <c r="Z79">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AA79">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB79">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC79">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AD79">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE79">
         <v>1.08</v>
@@ -13243,7 +13243,7 @@
         <v>1.65</v>
       </c>
       <c r="AG79">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13358,10 +13358,10 @@
         <v>3.37</v>
       </c>
       <c r="Q80">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R80">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S80">
         <v>1.3</v>
@@ -13376,19 +13376,19 @@
         <v>1.44</v>
       </c>
       <c r="W80">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X80">
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z80">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AA80">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB80">
         <v>1.99</v>
@@ -13397,7 +13397,7 @@
         <v>2.78</v>
       </c>
       <c r="AD80">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE80">
         <v>1.09</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK80">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13675,28 +13675,28 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="O82">
         <v>3.45</v>
       </c>
       <c r="P82">
+        <v>3.1</v>
+      </c>
+      <c r="Q82">
+        <v>2.5</v>
+      </c>
+      <c r="R82">
+        <v>2.11</v>
+      </c>
+      <c r="S82">
+        <v>1.3</v>
+      </c>
+      <c r="T82">
         <v>3.2</v>
       </c>
-      <c r="Q82">
-        <v>2.64</v>
-      </c>
-      <c r="R82">
-        <v>2.2</v>
-      </c>
-      <c r="S82">
-        <v>1.32</v>
-      </c>
-      <c r="T82">
-        <v>3.13</v>
-      </c>
       <c r="U82">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V82">
         <v>1.44</v>
@@ -13708,31 +13708,31 @@
         <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z82">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="AA82">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB82">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC82">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="AD82">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE82">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG82">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P83">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="Q83">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="R83">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T83">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="U83">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V83">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W83">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z83">
-        <v>3.58</v>
+        <v>3.87</v>
       </c>
       <c r="AA83">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB83">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AC83">
         <v>2.78</v>
       </c>
       <c r="AD83">
+        <v>1.34</v>
+      </c>
+      <c r="AE83">
+        <v>1.1</v>
+      </c>
+      <c r="AF83">
+        <v>1.6</v>
+      </c>
+      <c r="AG83">
+        <v>2.2</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.25</v>
+      </c>
+      <c r="AK83">
         <v>1.38</v>
-      </c>
-      <c r="AE83">
-        <v>1.14</v>
-      </c>
-      <c r="AF83">
-        <v>1.62</v>
-      </c>
-      <c r="AG83">
-        <v>2.18</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.24</v>
-      </c>
-      <c r="AK83">
-        <v>1.4</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O84">
         <v>3.65</v>
       </c>
       <c r="P84">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="Q84">
-        <v>4.41</v>
+        <v>4</v>
       </c>
       <c r="R84">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S84">
         <v>1.3</v>
       </c>
       <c r="T84">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="U84">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="V84">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W84">
         <v>1.1</v>
@@ -14037,7 +14037,7 @@
         <v>1.18</v>
       </c>
       <c r="Z84">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="AA84">
         <v>1.75</v>
@@ -14046,7 +14046,7 @@
         <v>2</v>
       </c>
       <c r="AC84">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="AD84">
         <v>1.35</v>
@@ -14055,10 +14055,10 @@
         <v>1.13</v>
       </c>
       <c r="AF84">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG84">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="AK84">
         <v>1.19</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="O86">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P86">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q86">
         <v>3.38</v>
@@ -14345,13 +14345,13 @@
         <v>1.24</v>
       </c>
       <c r="T86">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="U86">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="V86">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W86">
         <v>1.12</v>
@@ -14360,7 +14360,7 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z86">
         <v>4.3</v>
@@ -14369,22 +14369,22 @@
         <v>1.62</v>
       </c>
       <c r="AB86">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC86">
         <v>2.64</v>
       </c>
       <c r="AD86">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE86">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF86">
         <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
         <v>1.32</v>
@@ -14490,34 +14490,34 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="O87">
         <v>3.25</v>
       </c>
       <c r="P87">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q87">
-        <v>3.25</v>
+        <v>3.66</v>
       </c>
       <c r="R87">
         <v>2.2</v>
       </c>
       <c r="S87">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T87">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="U87">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="V87">
         <v>1.4</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14526,19 +14526,19 @@
         <v>1.26</v>
       </c>
       <c r="Z87">
-        <v>3.28</v>
+        <v>3.62</v>
       </c>
       <c r="AA87">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB87">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC87">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD87">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE87">
         <v>1.08</v>
@@ -14547,7 +14547,7 @@
         <v>1.67</v>
       </c>
       <c r="AG87">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14726,7 +14726,7 @@
         <v>1.24</v>
       </c>
       <c r="AK88">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,55 +14816,55 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="O89">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P89">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="Q89">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="R89">
         <v>2.1</v>
       </c>
       <c r="S89">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T89">
+        <v>2.89</v>
+      </c>
+      <c r="U89">
         <v>2.8</v>
       </c>
-      <c r="U89">
-        <v>2.85</v>
-      </c>
       <c r="V89">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W89">
         <v>1.05</v>
       </c>
       <c r="X89">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z89">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA89">
         <v>1.96</v>
       </c>
       <c r="AB89">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC89">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AD89">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE89">
         <v>1.08</v>
@@ -14873,7 +14873,7 @@
         <v>1.75</v>
       </c>
       <c r="AG89">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK89">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,31 +14979,31 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O90">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P90">
-        <v>4.14</v>
+        <v>4.2</v>
       </c>
       <c r="Q90">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R90">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T90">
         <v>3.2</v>
       </c>
       <c r="U90">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V90">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W90">
         <v>1.06</v>
@@ -15012,16 +15012,16 @@
         <v>1.05</v>
       </c>
       <c r="Y90">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z90">
-        <v>3.57</v>
+        <v>3.7</v>
       </c>
       <c r="AA90">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AB90">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC90">
         <v>3.2</v>
@@ -15030,7 +15030,7 @@
         <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF90">
         <v>1.75</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK90">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="O91">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P91">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="Q91">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R91">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S91">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T91">
         <v>2.73</v>
       </c>
       <c r="U91">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V91">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W91">
         <v>1.04</v>
       </c>
       <c r="X91">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y91">
         <v>1.3</v>
       </c>
       <c r="Z91">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA91">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB91">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="AD91">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE91">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF91">
         <v>1.7</v>
       </c>
       <c r="AG91">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK91">
         <v>1.47</v>
@@ -15305,61 +15305,61 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="O92">
+        <v>3.3</v>
+      </c>
+      <c r="P92">
         <v>3.25</v>
       </c>
-      <c r="P92">
-        <v>2.97</v>
-      </c>
       <c r="Q92">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R92">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T92">
         <v>2.66</v>
       </c>
       <c r="U92">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V92">
         <v>1.35</v>
       </c>
       <c r="W92">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X92">
         <v>1.06</v>
       </c>
       <c r="Y92">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z92">
         <v>3.04</v>
       </c>
       <c r="AA92">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB92">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC92">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AD92">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF92">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG92">
         <v>1.91</v>
@@ -15378,7 +15378,7 @@
         <v>1.3</v>
       </c>
       <c r="AK92">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,31 +15468,31 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O93">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="P93">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="Q93">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="R93">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S93">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T93">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U93">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="V93">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W93">
         <v>1.05</v>
@@ -15501,28 +15501,28 @@
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z93">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AA93">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB93">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC93">
         <v>3.8</v>
       </c>
       <c r="AD93">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE93">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF93">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG93">
         <v>1.95</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AK93">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.68</v>
+        <v>2.62</v>
       </c>
       <c r="O94">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P94">
-        <v>4.77</v>
+        <v>2.5</v>
       </c>
       <c r="Q94">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R94">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S94">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T94">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U94">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="V94">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W94">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y94">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z94">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA94">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB94">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC94">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD94">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE94">
         <v>1.1</v>
       </c>
       <c r="AF94">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG94">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK94">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="O95">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P95">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="Q95">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R95">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S95">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T95">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="U95">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V95">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W95">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X95">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y95">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z95">
+        <v>3.25</v>
+      </c>
+      <c r="AA95">
+        <v>1.89</v>
+      </c>
+      <c r="AB95">
+        <v>1.8</v>
+      </c>
+      <c r="AC95">
         <v>3.4</v>
       </c>
-      <c r="AA95">
-        <v>1.87</v>
-      </c>
-      <c r="AB95">
-        <v>1.82</v>
-      </c>
-      <c r="AC95">
-        <v>3.1</v>
-      </c>
       <c r="AD95">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE95">
         <v>1.1</v>
       </c>
       <c r="AF95">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG95">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK95">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,28 +15957,28 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="O96">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="P96">
+        <v>3.41</v>
+      </c>
+      <c r="Q96">
+        <v>2.62</v>
+      </c>
+      <c r="R96">
+        <v>2.08</v>
+      </c>
+      <c r="S96">
+        <v>1.36</v>
+      </c>
+      <c r="T96">
         <v>3.01</v>
       </c>
-      <c r="Q96">
-        <v>3.1</v>
-      </c>
-      <c r="R96">
-        <v>2.1</v>
-      </c>
-      <c r="S96">
-        <v>1.4</v>
-      </c>
-      <c r="T96">
-        <v>3.02</v>
-      </c>
       <c r="U96">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="V96">
         <v>1.4</v>
@@ -15987,34 +15987,34 @@
         <v>1.08</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y96">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z96">
+        <v>3.34</v>
+      </c>
+      <c r="AA96">
+        <v>1.85</v>
+      </c>
+      <c r="AB96">
+        <v>1.85</v>
+      </c>
+      <c r="AC96">
         <v>3.3</v>
       </c>
-      <c r="AA96">
-        <v>1.89</v>
-      </c>
-      <c r="AB96">
-        <v>1.8</v>
-      </c>
-      <c r="AC96">
-        <v>3.2</v>
-      </c>
       <c r="AD96">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE96">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF96">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG96">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK96">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.94</v>
+        <v>2.17</v>
       </c>
       <c r="O97">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>2.34</v>
+        <v>2.93</v>
       </c>
       <c r="Q97">
+        <v>2.77</v>
+      </c>
+      <c r="R97">
+        <v>2.05</v>
+      </c>
+      <c r="S97">
+        <v>1.4</v>
+      </c>
+      <c r="T97">
+        <v>2.69</v>
+      </c>
+      <c r="U97">
         <v>3</v>
       </c>
-      <c r="R97">
-        <v>2.2</v>
-      </c>
-      <c r="S97">
+      <c r="V97">
+        <v>1.33</v>
+      </c>
+      <c r="W97">
+        <v>1.07</v>
+      </c>
+      <c r="X97">
+        <v>1</v>
+      </c>
+      <c r="Y97">
         <v>1.37</v>
       </c>
-      <c r="T97">
-        <v>3.03</v>
-      </c>
-      <c r="U97">
-        <v>2.7</v>
-      </c>
-      <c r="V97">
-        <v>1.39</v>
-      </c>
-      <c r="W97">
-        <v>1.04</v>
-      </c>
-      <c r="X97">
-        <v>1.05</v>
-      </c>
-      <c r="Y97">
-        <v>1.29</v>
-      </c>
       <c r="Z97">
-        <v>3.34</v>
+        <v>2.79</v>
       </c>
       <c r="AA97">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB97">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AC97">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD97">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE97">
         <v>1.07</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG97">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,61 +16283,61 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="O98">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="P98">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="Q98">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="R98">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S98">
         <v>1.36</v>
       </c>
       <c r="T98">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U98">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V98">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W98">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X98">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
         <v>1.3</v>
       </c>
       <c r="Z98">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AA98">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB98">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC98">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD98">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE98">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF98">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG98">
         <v>1.85</v>
@@ -16356,7 +16356,7 @@
         <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16772,16 +16772,16 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="O101">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P101">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="Q101">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R101">
         <v>2.2</v>
@@ -16790,40 +16790,40 @@
         <v>1.36</v>
       </c>
       <c r="T101">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U101">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="V101">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W101">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
         <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z101">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA101">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB101">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC101">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AD101">
         <v>1.3</v>
       </c>
       <c r="AE101">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF101">
         <v>1.75</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,34 +16935,34 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O102">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="P102">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="Q102">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R102">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T102">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U102">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="V102">
         <v>1.41</v>
       </c>
       <c r="W102">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
         <v>1.03</v>
@@ -16971,28 +16971,28 @@
         <v>1.28</v>
       </c>
       <c r="Z102">
-        <v>3.3</v>
+        <v>3.57</v>
       </c>
       <c r="AA102">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB102">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AC102">
         <v>3.4</v>
       </c>
       <c r="AD102">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE102">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF102">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG102">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK102">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="O103">
-        <v>3.54</v>
+        <v>5</v>
       </c>
       <c r="P103">
-        <v>3.22</v>
+        <v>8.5</v>
       </c>
       <c r="Q103">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="S103">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T103">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="U103">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="V103">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W103">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X103">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z103">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA103">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AB103">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="AC103">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD103">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE103">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AG103">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AK103">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,31 +17261,31 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="O104">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="P104">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="Q104">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R104">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S104">
         <v>1.42</v>
       </c>
       <c r="T104">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U104">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="V104">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W104">
         <v>1.03</v>
@@ -17294,31 +17294,31 @@
         <v>1.06</v>
       </c>
       <c r="Y104">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z104">
-        <v>3.39</v>
+        <v>3.19</v>
       </c>
       <c r="AA104">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB104">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AC104">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD104">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE104">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF104">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG104">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AK104">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.31</v>
+        <v>2.61</v>
       </c>
       <c r="O105">
-        <v>5.2</v>
+        <v>3.15</v>
       </c>
       <c r="P105">
-        <v>8.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q105">
-        <v>1.79</v>
+        <v>3.05</v>
       </c>
       <c r="R105">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="S105">
+        <v>1.42</v>
+      </c>
+      <c r="T105">
+        <v>2.65</v>
+      </c>
+      <c r="U105">
+        <v>3.04</v>
+      </c>
+      <c r="V105">
+        <v>1.33</v>
+      </c>
+      <c r="W105">
+        <v>1.07</v>
+      </c>
+      <c r="X105">
+        <v>1.02</v>
+      </c>
+      <c r="Y105">
+        <v>1.32</v>
+      </c>
+      <c r="Z105">
+        <v>3</v>
+      </c>
+      <c r="AA105">
+        <v>2.17</v>
+      </c>
+      <c r="AB105">
+        <v>1.75</v>
+      </c>
+      <c r="AC105">
+        <v>3.95</v>
+      </c>
+      <c r="AD105">
+        <v>1.25</v>
+      </c>
+      <c r="AE105">
+        <v>1.03</v>
+      </c>
+      <c r="AF105">
+        <v>1.8</v>
+      </c>
+      <c r="AG105">
+        <v>1.9</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
         <v>1.29</v>
       </c>
-      <c r="T105">
-        <v>3.15</v>
-      </c>
-      <c r="U105">
-        <v>2.4</v>
-      </c>
-      <c r="V105">
-        <v>1.52</v>
-      </c>
-      <c r="W105">
-        <v>1.11</v>
-      </c>
-      <c r="X105">
-        <v>1.04</v>
-      </c>
-      <c r="Y105">
-        <v>1.21</v>
-      </c>
-      <c r="Z105">
-        <v>4.37</v>
-      </c>
-      <c r="AA105">
-        <v>1.61</v>
-      </c>
-      <c r="AB105">
-        <v>2.15</v>
-      </c>
-      <c r="AC105">
-        <v>2.55</v>
-      </c>
-      <c r="AD105">
-        <v>1.46</v>
-      </c>
-      <c r="AE105">
-        <v>1.14</v>
-      </c>
-      <c r="AF105">
-        <v>1.91</v>
-      </c>
-      <c r="AG105">
-        <v>1.8</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.15</v>
-      </c>
       <c r="AK105">
-        <v>3.25</v>
+        <v>1.42</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,65 +17587,65 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="O106">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="Q106">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="R106">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S106">
+        <v>1.36</v>
+      </c>
+      <c r="T106">
+        <v>2.88</v>
+      </c>
+      <c r="U106">
+        <v>2.62</v>
+      </c>
+      <c r="V106">
         <v>1.44</v>
       </c>
-      <c r="T106">
-        <v>2.53</v>
-      </c>
-      <c r="U106">
-        <v>3.04</v>
-      </c>
-      <c r="V106">
-        <v>1.34</v>
-      </c>
       <c r="W106">
+        <v>1.08</v>
+      </c>
+      <c r="X106">
         <v>1.05</v>
       </c>
-      <c r="X106">
-        <v>1.06</v>
-      </c>
       <c r="Y106">
+        <v>1.31</v>
+      </c>
+      <c r="Z106">
+        <v>3.05</v>
+      </c>
+      <c r="AA106">
+        <v>1.85</v>
+      </c>
+      <c r="AB106">
+        <v>1.9</v>
+      </c>
+      <c r="AC106">
+        <v>3.1</v>
+      </c>
+      <c r="AD106">
         <v>1.33</v>
       </c>
-      <c r="Z106">
-        <v>3.1</v>
-      </c>
-      <c r="AA106">
+      <c r="AE106">
+        <v>1.07</v>
+      </c>
+      <c r="AF106">
+        <v>1.7</v>
+      </c>
+      <c r="AG106">
         <v>2.05</v>
       </c>
-      <c r="AB106">
-        <v>1.66</v>
-      </c>
-      <c r="AC106">
-        <v>3.8</v>
-      </c>
-      <c r="AD106">
-        <v>1.26</v>
-      </c>
-      <c r="AE106">
-        <v>1.04</v>
-      </c>
-      <c r="AF106">
-        <v>1.81</v>
-      </c>
-      <c r="AG106">
-        <v>1.95</v>
-      </c>
       <c r="AH106" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK106">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>3.17</v>
+        <v>2.98</v>
       </c>
       <c r="O107">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="P107">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q107">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="R107">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S107">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T107">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U107">
         <v>2.77</v>
       </c>
       <c r="V107">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X107">
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z107">
-        <v>3.44</v>
+        <v>3.71</v>
       </c>
       <c r="AA107">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB107">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC107">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD107">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG107">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK107">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="O108">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>4.18</v>
+        <v>3.7</v>
       </c>
       <c r="Q108">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R108">
         <v>2.09</v>
       </c>
       <c r="S108">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T108">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U108">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V108">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W108">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X108">
         <v>1.05</v>
       </c>
       <c r="Y108">
+        <v>1.29</v>
+      </c>
+      <c r="Z108">
+        <v>3.53</v>
+      </c>
+      <c r="AA108">
+        <v>1.89</v>
+      </c>
+      <c r="AB108">
+        <v>1.84</v>
+      </c>
+      <c r="AC108">
+        <v>3.1</v>
+      </c>
+      <c r="AD108">
         <v>1.28</v>
-      </c>
-      <c r="Z108">
-        <v>3.45</v>
-      </c>
-      <c r="AA108">
-        <v>1.79</v>
-      </c>
-      <c r="AB108">
-        <v>1.93</v>
-      </c>
-      <c r="AC108">
-        <v>3.24</v>
-      </c>
-      <c r="AD108">
-        <v>1.33</v>
       </c>
       <c r="AE108">
         <v>1.11</v>
       </c>
       <c r="AF108">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
         <v>1.85</v>
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="O109">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P109">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="Q109">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R109">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S109">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="T109">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="U109">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V109">
         <v>1.29</v>
       </c>
       <c r="W109">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X109">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y109">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z109">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AA109">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB109">
         <v>1.53</v>
       </c>
       <c r="AC109">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="AD109">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE109">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF109">
         <v>1.95</v>
       </c>
       <c r="AG109">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK109">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,58 +18239,58 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="O110">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P110">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q110">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R110">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="U110">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V110">
         <v>1.5</v>
       </c>
       <c r="W110">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X110">
         <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z110">
         <v>4</v>
       </c>
       <c r="AA110">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB110">
         <v>2.1</v>
       </c>
       <c r="AC110">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD110">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE110">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF110">
         <v>1.6</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.48</v>
+        <v>1.67</v>
       </c>
       <c r="O111">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P111">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="Q111">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="R111">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="S111">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T111">
+        <v>2.94</v>
+      </c>
+      <c r="U111">
         <v>2.65</v>
       </c>
-      <c r="U111">
-        <v>3</v>
-      </c>
       <c r="V111">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X111">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y111">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z111">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AA111">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB111">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AC111">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD111">
+        <v>1.33</v>
+      </c>
+      <c r="AE111">
+        <v>1.11</v>
+      </c>
+      <c r="AF111">
+        <v>1.78</v>
+      </c>
+      <c r="AG111">
+        <v>1.9</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
         <v>1.18</v>
       </c>
-      <c r="AE111">
-        <v>1.06</v>
-      </c>
-      <c r="AF111">
-        <v>1.85</v>
-      </c>
-      <c r="AG111">
-        <v>1.8</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.36</v>
-      </c>
       <c r="AK111">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="O112">
-        <v>3.88</v>
+        <v>3.15</v>
       </c>
       <c r="P112">
-        <v>4.84</v>
+        <v>2.66</v>
       </c>
       <c r="Q112">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="R112">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S112">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T112">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U112">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="V112">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W112">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z112">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="AA112">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AB112">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC112">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD112">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE112">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF112">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG112">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AK112">
-        <v>2.23</v>
+        <v>1.47</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="O113">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P113">
-        <v>4.32</v>
+        <v>3.03</v>
       </c>
       <c r="Q113">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="R113">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S113">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T113">
         <v>2.77</v>
       </c>
       <c r="U113">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V113">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W113">
+        <v>1.06</v>
+      </c>
+      <c r="X113">
         <v>1.05</v>
       </c>
-      <c r="X113">
-        <v>1.03</v>
-      </c>
       <c r="Y113">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z113">
         <v>3.6</v>
       </c>
       <c r="AA113">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB113">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC113">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AD113">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE113">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF113">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG113">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK113">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O114">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="P114">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q114">
+        <v>3.1</v>
+      </c>
+      <c r="R114">
+        <v>1.92</v>
+      </c>
+      <c r="S114">
+        <v>1.48</v>
+      </c>
+      <c r="T114">
         <v>2.75</v>
       </c>
-      <c r="R114">
-        <v>2.03</v>
-      </c>
-      <c r="S114">
-        <v>1.36</v>
-      </c>
-      <c r="T114">
-        <v>2.77</v>
-      </c>
       <c r="U114">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="V114">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W114">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X114">
         <v>1.05</v>
       </c>
       <c r="Y114">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z114">
-        <v>3.52</v>
+        <v>2.66</v>
       </c>
       <c r="AA114">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB114">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC114">
-        <v>3.18</v>
+        <v>3.65</v>
       </c>
       <c r="AD114">
+        <v>1.2</v>
+      </c>
+      <c r="AE114">
+        <v>1.04</v>
+      </c>
+      <c r="AF114">
+        <v>1.88</v>
+      </c>
+      <c r="AG114">
+        <v>1.8</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
         <v>1.3</v>
       </c>
-      <c r="AE114">
-        <v>1.06</v>
-      </c>
-      <c r="AF114">
-        <v>1.7</v>
-      </c>
-      <c r="AG114">
-        <v>2.05</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.44</v>
-      </c>
       <c r="AK114">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,61 +19054,61 @@
         </is>
       </c>
       <c r="N115">
+        <v>1.63</v>
+      </c>
+      <c r="O115">
+        <v>4</v>
+      </c>
+      <c r="P115">
+        <v>4.7</v>
+      </c>
+      <c r="Q115">
+        <v>2.1</v>
+      </c>
+      <c r="R115">
         <v>2.26</v>
       </c>
-      <c r="O115">
-        <v>3.4</v>
-      </c>
-      <c r="P115">
-        <v>3.03</v>
-      </c>
-      <c r="Q115">
-        <v>2.63</v>
-      </c>
-      <c r="R115">
-        <v>2.12</v>
-      </c>
       <c r="S115">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T115">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U115">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="V115">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W115">
         <v>1.08</v>
       </c>
       <c r="X115">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y115">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z115">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AA115">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AB115">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AC115">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD115">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE115">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF115">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG115">
         <v>2.05</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK115">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19706,55 +19706,55 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="O119">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="P119">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="Q119">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="R119">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S119">
         <v>1.2</v>
       </c>
       <c r="T119">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U119">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V119">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W119">
         <v>1.17</v>
       </c>
       <c r="X119">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z119">
-        <v>5.84</v>
+        <v>5.9</v>
       </c>
       <c r="AA119">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB119">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC119">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AD119">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE119">
         <v>1.25</v>
@@ -19763,7 +19763,7 @@
         <v>1.44</v>
       </c>
       <c r="AG119">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK119">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,25 +19869,25 @@
         </is>
       </c>
       <c r="N120">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="O120">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P120">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q120">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R120">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="S120">
         <v>1.2</v>
       </c>
       <c r="T120">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="U120">
         <v>2.01</v>
@@ -19899,34 +19899,34 @@
         <v>1.18</v>
       </c>
       <c r="X120">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z120">
-        <v>6.17</v>
+        <v>5.55</v>
       </c>
       <c r="AA120">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB120">
         <v>2.7</v>
       </c>
       <c r="AC120">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD120">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE120">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AF120">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG120">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK120">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20032,34 +20032,34 @@
         </is>
       </c>
       <c r="N121">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="O121">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P121">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q121">
         <v>3.8</v>
       </c>
       <c r="R121">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="S121">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T121">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="U121">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V121">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="W121">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X121">
         <v>1</v>
@@ -20068,28 +20068,28 @@
         <v>1.01</v>
       </c>
       <c r="Z121">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA121">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AB121">
-        <v>3.8</v>
+        <v>4.12</v>
       </c>
       <c r="AC121">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AD121">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AE121">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AF121">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AG121">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK121">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="O123">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P123">
-        <v>8.550000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="O125">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P125">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,25 +21010,25 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O127">
         <v>3.6</v>
       </c>
       <c r="P127">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q127">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="R127">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S127">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T127">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U127">
         <v>2.38</v>
@@ -21037,28 +21037,28 @@
         <v>1.53</v>
       </c>
       <c r="W127">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
         <v>1.15</v>
       </c>
       <c r="Z127">
-        <v>3.13</v>
+        <v>4.2</v>
       </c>
       <c r="AA127">
         <v>1.6</v>
       </c>
       <c r="AB127">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC127">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="AD127">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE127">
         <v>1.15</v>
@@ -21083,7 +21083,7 @@
         <v>1.22</v>
       </c>
       <c r="AK127">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21173,58 +21173,58 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="O128">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="P128">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q128">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R128">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S128">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T128">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U128">
         <v>3.2</v>
       </c>
       <c r="V128">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W128">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X128">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y128">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z128">
-        <v>3.11</v>
+        <v>2.89</v>
       </c>
       <c r="AA128">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB128">
         <v>1.65</v>
       </c>
       <c r="AC128">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD128">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE128">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF128">
         <v>1.85</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK128">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,55 +21336,55 @@
         </is>
       </c>
       <c r="N129">
-        <v>4.94</v>
+        <v>5.25</v>
       </c>
       <c r="O129">
-        <v>4.46</v>
+        <v>4.65</v>
       </c>
       <c r="P129">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="Q129">
         <v>5</v>
       </c>
       <c r="R129">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S129">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="U129">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="V129">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="W129">
         <v>1.18</v>
       </c>
       <c r="X129">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z129">
-        <v>6.28</v>
+        <v>6.5</v>
       </c>
       <c r="AA129">
         <v>1.44</v>
       </c>
       <c r="AB129">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="AC129">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD129">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE129">
         <v>1.33</v>
@@ -21393,7 +21393,7 @@
         <v>1.49</v>
       </c>
       <c r="AG129">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>2.53</v>
+        <v>1.2</v>
       </c>
       <c r="AK129">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="O132">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P132">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="Q132">
         <v>2.08</v>
@@ -21843,13 +21843,13 @@
         <v>1.32</v>
       </c>
       <c r="T132">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U132">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V132">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W132">
         <v>1.05</v>
@@ -21858,16 +21858,16 @@
         <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z132">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AA132">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB132">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AC132">
         <v>2.88</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK132">
         <v>2.34</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O133">
-        <v>4.27</v>
+        <v>3.85</v>
       </c>
       <c r="P133">
-        <v>5.09</v>
+        <v>4.6</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22154,13 +22154,13 @@
         <v>1.36</v>
       </c>
       <c r="O134">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P134">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Q134">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R134">
         <v>2.5</v>
@@ -22169,22 +22169,22 @@
         <v>1.28</v>
       </c>
       <c r="T134">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U134">
         <v>2.29</v>
       </c>
       <c r="V134">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W134">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X134">
         <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z134">
         <v>4.5</v>
@@ -22196,19 +22196,19 @@
         <v>2.24</v>
       </c>
       <c r="AC134">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD134">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE134">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF134">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG134">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK134">
         <v>2.97</v>
@@ -22326,22 +22326,22 @@
         <v>2.6</v>
       </c>
       <c r="R135">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="S135">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T135">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="U135">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V135">
         <v>1.53</v>
       </c>
       <c r="W135">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X135">
         <v>1.03</v>
@@ -22353,22 +22353,22 @@
         <v>4.45</v>
       </c>
       <c r="AA135">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB135">
         <v>2.22</v>
       </c>
       <c r="AC135">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD135">
         <v>1.46</v>
       </c>
       <c r="AE135">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF135">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG135">
         <v>2.42</v>
@@ -22387,7 +22387,7 @@
         <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,52 +22477,52 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O136">
         <v>3.2</v>
       </c>
       <c r="P136">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q136">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="R136">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S136">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T136">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U136">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="V136">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W136">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z136">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="AA136">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB136">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC136">
-        <v>3.36</v>
+        <v>3.04</v>
       </c>
       <c r="AD136">
         <v>1.29</v>
@@ -22531,10 +22531,10 @@
         <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK136">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,55 +22640,55 @@
         </is>
       </c>
       <c r="N137">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="O137">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="P137">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q137">
         <v>3.75</v>
       </c>
       <c r="R137">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S137">
         <v>1.25</v>
       </c>
       <c r="T137">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U137">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="V137">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W137">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z137">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA137">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AB137">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AC137">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AD137">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE137">
         <v>1.16</v>
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="O138">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P138">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="Q138">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="R138">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S138">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T138">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U138">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V138">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W138">
         <v>1.07</v>
       </c>
       <c r="X138">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y138">
         <v>1.15</v>
       </c>
       <c r="Z138">
-        <v>4.21</v>
+        <v>4.5</v>
       </c>
       <c r="AA138">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AB138">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AC138">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="AD138">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE138">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF138">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG138">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK138">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="O139">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P139">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q139">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="R139">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S139">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T139">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="U139">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V139">
         <v>1.4</v>
       </c>
       <c r="W139">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X139">
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z139">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA139">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AB139">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC139">
         <v>3.35</v>
       </c>
       <c r="AD139">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE139">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF139">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG139">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK139">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U147">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V147">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X147">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z147">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE147">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF147">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK147">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25094,34 +25094,34 @@
         <v>3.7</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T152">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V152">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X152">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z152">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA152">
         <v>1.98</v>
@@ -25130,19 +25130,19 @@
         <v>1.83</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25257,55 +25257,55 @@
         <v>2.63</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O155">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P155">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Q155">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R155">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S155">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T155">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U155">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V155">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W155">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X155">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y155">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z155">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC155">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD155">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE155">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF155">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG155">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK155">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="O156">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P156">
-        <v>3.1</v>
+        <v>4.68</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X156">
         <v>0</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="O157">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P157">
-        <v>4.68</v>
+        <v>2.88</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R157">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S157">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T157">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U157">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V157">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W157">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X157">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z157">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC157">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD157">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE157">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF157">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG157">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK157">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="O199">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P199">
-        <v>5.93</v>
+        <v>4.4</v>
       </c>
       <c r="Q199">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="R199">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="S199">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T199">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="U199">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="V199">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W199">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X199">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y199">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Z199">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA199">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AB199">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AC199">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AD199">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE199">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF199">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AG199">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK199">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O200">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="P200">
-        <v>4.4</v>
+        <v>4.66</v>
       </c>
       <c r="Q200">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="R200">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="S200">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T200">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U200">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="V200">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W200">
         <v>1.03</v>
       </c>
       <c r="X200">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y200">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="Z200">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA200">
         <v>2.7</v>
       </c>
       <c r="AB200">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC200">
-        <v>5.2</v>
+        <v>5.55</v>
       </c>
       <c r="AD200">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE200">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF200">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="AG200">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AK200">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="O201">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="P201">
-        <v>4.66</v>
+        <v>5.93</v>
       </c>
       <c r="Q201">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="R201">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="S201">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T201">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U201">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="V201">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W201">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X201">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y201">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z201">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA201">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AB201">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AC201">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="AD201">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE201">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF201">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AG201">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK201">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -35230,10 +35230,10 @@
         <v>0</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC214">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q231">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O3">
         <v>3.75</v>
       </c>
       <c r="P3">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -970,16 +970,16 @@
         <v>2.41</v>
       </c>
       <c r="Q4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R4">
         <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
         <v>2.5</v>
@@ -994,10 +994,10 @@
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AA4">
         <v>1.72</v>
@@ -1133,10 +1133,10 @@
         <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>4.2</v>
+        <v>4.54</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S5">
         <v>1.28</v>
@@ -1145,28 +1145,28 @@
         <v>3.12</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AA5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <v>2.62</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O29">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="P29">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="Q29">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R29">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
         <v>1.37</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U29">
         <v>2.55</v>
       </c>
       <c r="V29">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
         <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA29">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
-        <v>3.17</v>
+        <v>2.94</v>
       </c>
       <c r="AD29">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG29">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK29">
         <v>1.83</v>
@@ -5199,46 +5199,46 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="O30">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="P30">
-        <v>3.19</v>
+        <v>2.82</v>
       </c>
       <c r="Q30">
         <v>2.78</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S30">
         <v>1.45</v>
       </c>
       <c r="T30">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U30">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="V30">
         <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="AA30">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB30">
         <v>1.68</v>
@@ -5250,10 +5250,10 @@
         <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG30">
         <v>1.85</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="O31">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="P31">
         <v>1.91</v>
       </c>
       <c r="Q31">
-        <v>5.24</v>
+        <v>4.8</v>
       </c>
       <c r="R31">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="S31">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="T31">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U31">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="V31">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
         <v>1.01</v>
       </c>
       <c r="X31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
         <v>1.49</v>
       </c>
       <c r="Z31">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AA31">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AB31">
         <v>1.52</v>
       </c>
       <c r="AC31">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AD31">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6838,10 +6838,10 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -6850,10 +6850,10 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W40">
         <v>0</v>
@@ -6862,31 +6862,31 @@
         <v>0</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -10913,10 +10913,10 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -10925,10 +10925,10 @@
         <v>0</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W65">
         <v>0</v>
@@ -10943,25 +10943,25 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12217,10 +12217,10 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S73">
         <v>0</v>
@@ -12229,10 +12229,10 @@
         <v>0</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W73">
         <v>0</v>
@@ -12247,25 +12247,25 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,10 +12380,10 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -12392,10 +12392,10 @@
         <v>0</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W74">
         <v>0</v>
@@ -12404,31 +12404,31 @@
         <v>0</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE74">
         <v>0</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,52 +15631,52 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O94">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P94">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="Q94">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R94">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S94">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U94">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V94">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X94">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y94">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z94">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AA94">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB94">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC94">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AD94">
         <v>1.28</v>
@@ -15685,10 +15685,10 @@
         <v>1.1</v>
       </c>
       <c r="AF94">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG94">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK94">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="O95">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P95">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="Q95">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="R95">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="S95">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T95">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="U95">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V95">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W95">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X95">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y95">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="Z95">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="AA95">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AB95">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC95">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="AD95">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE95">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF95">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG95">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK95">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,65 +15957,65 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="O96">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P96">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="Q96">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="R96">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S96">
         <v>1.36</v>
       </c>
       <c r="T96">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="U96">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V96">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
+        <v>1.3</v>
+      </c>
+      <c r="Z96">
+        <v>3.08</v>
+      </c>
+      <c r="AA96">
+        <v>1.98</v>
+      </c>
+      <c r="AB96">
+        <v>1.78</v>
+      </c>
+      <c r="AC96">
+        <v>3.34</v>
+      </c>
+      <c r="AD96">
+        <v>1.24</v>
+      </c>
+      <c r="AE96">
         <v>1.05</v>
       </c>
-      <c r="Y96">
-        <v>1.24</v>
-      </c>
-      <c r="Z96">
-        <v>3.34</v>
-      </c>
-      <c r="AA96">
+      <c r="AF96">
+        <v>1.8</v>
+      </c>
+      <c r="AG96">
         <v>1.85</v>
       </c>
-      <c r="AB96">
-        <v>1.85</v>
-      </c>
-      <c r="AC96">
-        <v>3.3</v>
-      </c>
-      <c r="AD96">
-        <v>1.33</v>
-      </c>
-      <c r="AE96">
-        <v>1.1</v>
-      </c>
-      <c r="AF96">
-        <v>1.73</v>
-      </c>
-      <c r="AG96">
-        <v>1.98</v>
-      </c>
       <c r="AH96" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK96">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,80 +16120,80 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="O97">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P97">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="Q97">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="R97">
+        <v>2.2</v>
+      </c>
+      <c r="S97">
+        <v>1.33</v>
+      </c>
+      <c r="T97">
+        <v>3</v>
+      </c>
+      <c r="U97">
+        <v>2.61</v>
+      </c>
+      <c r="V97">
+        <v>1.41</v>
+      </c>
+      <c r="W97">
+        <v>1.08</v>
+      </c>
+      <c r="X97">
+        <v>1.05</v>
+      </c>
+      <c r="Y97">
+        <v>1.25</v>
+      </c>
+      <c r="Z97">
+        <v>3.34</v>
+      </c>
+      <c r="AA97">
+        <v>1.88</v>
+      </c>
+      <c r="AB97">
+        <v>1.85</v>
+      </c>
+      <c r="AC97">
+        <v>3.08</v>
+      </c>
+      <c r="AD97">
+        <v>1.28</v>
+      </c>
+      <c r="AE97">
+        <v>1.1</v>
+      </c>
+      <c r="AF97">
+        <v>1.7</v>
+      </c>
+      <c r="AG97">
         <v>2.05</v>
       </c>
-      <c r="S97">
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <v>1.3</v>
+      </c>
+      <c r="AK97">
         <v>1.4</v>
-      </c>
-      <c r="T97">
-        <v>2.69</v>
-      </c>
-      <c r="U97">
-        <v>3</v>
-      </c>
-      <c r="V97">
-        <v>1.33</v>
-      </c>
-      <c r="W97">
-        <v>1.07</v>
-      </c>
-      <c r="X97">
-        <v>1</v>
-      </c>
-      <c r="Y97">
-        <v>1.37</v>
-      </c>
-      <c r="Z97">
-        <v>2.79</v>
-      </c>
-      <c r="AA97">
-        <v>2.1</v>
-      </c>
-      <c r="AB97">
-        <v>1.65</v>
-      </c>
-      <c r="AC97">
-        <v>3.74</v>
-      </c>
-      <c r="AD97">
-        <v>1.19</v>
-      </c>
-      <c r="AE97">
-        <v>1.07</v>
-      </c>
-      <c r="AF97">
-        <v>1.83</v>
-      </c>
-      <c r="AG97">
-        <v>1.91</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.26</v>
-      </c>
-      <c r="AK97">
-        <v>1.49</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="O98">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P98">
-        <v>4.2</v>
+        <v>3.41</v>
       </c>
       <c r="Q98">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="R98">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S98">
         <v>1.36</v>
       </c>
       <c r="T98">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="U98">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V98">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W98">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y98">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z98">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AA98">
+        <v>1.85</v>
+      </c>
+      <c r="AB98">
+        <v>1.85</v>
+      </c>
+      <c r="AC98">
+        <v>3.3</v>
+      </c>
+      <c r="AD98">
+        <v>1.33</v>
+      </c>
+      <c r="AE98">
+        <v>1.1</v>
+      </c>
+      <c r="AF98">
+        <v>1.73</v>
+      </c>
+      <c r="AG98">
         <v>1.98</v>
       </c>
-      <c r="AB98">
-        <v>1.78</v>
-      </c>
-      <c r="AC98">
-        <v>3.34</v>
-      </c>
-      <c r="AD98">
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
         <v>1.24</v>
       </c>
-      <c r="AE98">
-        <v>1.05</v>
-      </c>
-      <c r="AF98">
-        <v>1.8</v>
-      </c>
-      <c r="AG98">
-        <v>1.85</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.29</v>
-      </c>
       <c r="AK98">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="O100">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="P100">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q100">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="R100">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S100">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T100">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U100">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V100">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="W100">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
         <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z100">
-        <v>4.25</v>
+        <v>4.66</v>
       </c>
       <c r="AA100">
         <v>1.62</v>
       </c>
       <c r="AB100">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="AC100">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD100">
         <v>1.5</v>
       </c>
       <c r="AE100">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF100">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG100">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK100">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="O111">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="P111">
-        <v>5</v>
+        <v>2.66</v>
       </c>
       <c r="Q111">
-        <v>2.17</v>
+        <v>3.2</v>
       </c>
       <c r="R111">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="S111">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T111">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U111">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W111">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z111">
+        <v>3.15</v>
+      </c>
+      <c r="AA111">
+        <v>1.86</v>
+      </c>
+      <c r="AB111">
+        <v>1.88</v>
+      </c>
+      <c r="AC111">
         <v>3.25</v>
-      </c>
-      <c r="AA111">
-        <v>1.83</v>
-      </c>
-      <c r="AB111">
-        <v>1.95</v>
-      </c>
-      <c r="AC111">
-        <v>2.9</v>
       </c>
       <c r="AD111">
         <v>1.33</v>
       </c>
       <c r="AE111">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF111">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG111">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AK111">
-        <v>2.06</v>
+        <v>1.47</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="O112">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P112">
-        <v>2.66</v>
+        <v>3.03</v>
       </c>
       <c r="Q112">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="R112">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S112">
+        <v>1.35</v>
+      </c>
+      <c r="T112">
+        <v>2.77</v>
+      </c>
+      <c r="U112">
+        <v>2.88</v>
+      </c>
+      <c r="V112">
         <v>1.36</v>
       </c>
-      <c r="T112">
-        <v>2.9</v>
-      </c>
-      <c r="U112">
-        <v>2.75</v>
-      </c>
-      <c r="V112">
-        <v>1.39</v>
-      </c>
       <c r="W112">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y112">
         <v>1.29</v>
       </c>
       <c r="Z112">
+        <v>3.6</v>
+      </c>
+      <c r="AA112">
+        <v>1.87</v>
+      </c>
+      <c r="AB112">
+        <v>1.8</v>
+      </c>
+      <c r="AC112">
         <v>3.15</v>
       </c>
-      <c r="AA112">
-        <v>1.86</v>
-      </c>
-      <c r="AB112">
-        <v>1.88</v>
-      </c>
-      <c r="AC112">
-        <v>3.25</v>
-      </c>
       <c r="AD112">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE112">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG112">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AK112">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,65 +18728,65 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="O113">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P113">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q113">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R113">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="S113">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="T113">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U113">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="V113">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W113">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X113">
         <v>1.05</v>
       </c>
       <c r="Y113">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z113">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="AA113">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AB113">
+        <v>1.65</v>
+      </c>
+      <c r="AC113">
+        <v>3.65</v>
+      </c>
+      <c r="AD113">
+        <v>1.2</v>
+      </c>
+      <c r="AE113">
+        <v>1.04</v>
+      </c>
+      <c r="AF113">
+        <v>1.88</v>
+      </c>
+      <c r="AG113">
         <v>1.8</v>
       </c>
-      <c r="AC113">
-        <v>3.15</v>
-      </c>
-      <c r="AD113">
-        <v>1.29</v>
-      </c>
-      <c r="AE113">
-        <v>1.07</v>
-      </c>
-      <c r="AF113">
-        <v>1.71</v>
-      </c>
-      <c r="AG113">
-        <v>1.99</v>
-      </c>
       <c r="AH113" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O114">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="P114">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q114">
-        <v>3.1</v>
+        <v>2.17</v>
       </c>
       <c r="R114">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="S114">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="T114">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="U114">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="V114">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W114">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
         <v>1.05</v>
       </c>
       <c r="Y114">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z114">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="AA114">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB114">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC114">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="AD114">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE114">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF114">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG114">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK114">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="O156">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P156">
-        <v>4.68</v>
+        <v>2.88</v>
       </c>
       <c r="Q156">
-        <v>2.19</v>
+        <v>2.85</v>
       </c>
       <c r="R156">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="S156">
+        <v>1.4</v>
+      </c>
+      <c r="T156">
+        <v>2.6</v>
+      </c>
+      <c r="U156">
+        <v>2.88</v>
+      </c>
+      <c r="V156">
+        <v>1.33</v>
+      </c>
+      <c r="W156">
+        <v>1.06</v>
+      </c>
+      <c r="X156">
+        <v>1.02</v>
+      </c>
+      <c r="Y156">
         <v>1.31</v>
       </c>
-      <c r="T156">
-        <v>2.97</v>
-      </c>
-      <c r="U156">
-        <v>2.5</v>
-      </c>
-      <c r="V156">
-        <v>1.43</v>
-      </c>
-      <c r="W156">
-        <v>1.1</v>
-      </c>
-      <c r="X156">
-        <v>0</v>
-      </c>
-      <c r="Y156">
-        <v>1.19</v>
-      </c>
       <c r="Z156">
-        <v>3.8</v>
+        <v>2.92</v>
       </c>
       <c r="AA156">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB156">
-        <v>2.01</v>
+        <v>1.69</v>
       </c>
       <c r="AC156">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD156">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE156">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF156">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AG156">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>2.06</v>
+        <v>1.52</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="O157">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P157">
-        <v>2.88</v>
+        <v>4.68</v>
       </c>
       <c r="Q157">
-        <v>2.85</v>
+        <v>2.19</v>
       </c>
       <c r="R157">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="S157">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T157">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="U157">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V157">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W157">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X157">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y157">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="Z157">
-        <v>2.92</v>
+        <v>3.8</v>
       </c>
       <c r="AA157">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AB157">
+        <v>2.01</v>
+      </c>
+      <c r="AC157">
+        <v>2.7</v>
+      </c>
+      <c r="AD157">
+        <v>1.36</v>
+      </c>
+      <c r="AE157">
+        <v>1.11</v>
+      </c>
+      <c r="AF157">
         <v>1.69</v>
       </c>
-      <c r="AC157">
-        <v>3.5</v>
-      </c>
-      <c r="AD157">
-        <v>1.22</v>
-      </c>
-      <c r="AE157">
-        <v>1.05</v>
-      </c>
-      <c r="AF157">
-        <v>1.78</v>
-      </c>
       <c r="AG157">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK157">
-        <v>1.52</v>
+        <v>2.06</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -30464,19 +30464,19 @@
         </is>
       </c>
       <c r="N185">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="O185">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P185">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q185">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="R185">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="S185">
         <v>1.14</v>
@@ -30509,10 +30509,10 @@
         <v>3.08</v>
       </c>
       <c r="AC185">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD185">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AE185">
         <v>1.34</v>
@@ -30534,7 +30534,7 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK185">
         <v>1.33</v>
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="O197">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P197">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O198">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P198">
-        <v>4.59</v>
+        <v>4.4</v>
       </c>
       <c r="Q198">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R198">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="S198">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T198">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="U198">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="V198">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W198">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X198">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y198">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Z198">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AA198">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="AB198">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC198">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD198">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE198">
         <v>1.03</v>
       </c>
       <c r="AF198">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG198">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK198">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32746,31 +32746,31 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O199">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P199">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q199">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R199">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="S199">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="T199">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U199">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="V199">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W199">
         <v>1.03</v>
@@ -32779,16 +32779,16 @@
         <v>1.1</v>
       </c>
       <c r="Y199">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="Z199">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AA199">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AB199">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC199">
         <v>5.2</v>
@@ -32800,10 +32800,10 @@
         <v>1.02</v>
       </c>
       <c r="AF199">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG199">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>1.13</v>
       </c>
       <c r="AK199">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="O200">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="P200">
-        <v>4.66</v>
+        <v>5.25</v>
       </c>
       <c r="Q200">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="R200">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="S200">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T200">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U200">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="V200">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W200">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X200">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y200">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z200">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AA200">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AB200">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC200">
-        <v>5.55</v>
+        <v>5.12</v>
       </c>
       <c r="AD200">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE200">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF200">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG200">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK200">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="O201">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P201">
-        <v>5.93</v>
+        <v>4.9</v>
       </c>
       <c r="Q201">
-        <v>2.35</v>
+        <v>2.68</v>
       </c>
       <c r="R201">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="S201">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="T201">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="U201">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="V201">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W201">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X201">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y201">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="Z201">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AA201">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AB201">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AC201">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AD201">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE201">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF201">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AG201">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK201">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="O220">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P220">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,64 +40570,64 @@
         </is>
       </c>
       <c r="N247">
-        <v>2.61</v>
+        <v>1.77</v>
       </c>
       <c r="O247">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="P247">
-        <v>2.51</v>
+        <v>3.75</v>
       </c>
       <c r="Q247">
-        <v>3.32</v>
+        <v>2.29</v>
       </c>
       <c r="R247">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S247">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T247">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="U247">
-        <v>3.02</v>
+        <v>2.41</v>
       </c>
       <c r="V247">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W247">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X247">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y247">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="Z247">
-        <v>3.22</v>
+        <v>3.92</v>
       </c>
       <c r="AA247">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AB247">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC247">
-        <v>3.56</v>
+        <v>2.66</v>
       </c>
       <c r="AD247">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AE247">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF247">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG247">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK247">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,80 +40733,80 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.77</v>
+        <v>2.61</v>
       </c>
       <c r="O248">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="P248">
-        <v>3.75</v>
+        <v>2.51</v>
       </c>
       <c r="Q248">
-        <v>2.29</v>
+        <v>3.32</v>
       </c>
       <c r="R248">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="S248">
+        <v>1.4</v>
+      </c>
+      <c r="T248">
+        <v>2.62</v>
+      </c>
+      <c r="U248">
+        <v>3.02</v>
+      </c>
+      <c r="V248">
+        <v>1.36</v>
+      </c>
+      <c r="W248">
+        <v>1.04</v>
+      </c>
+      <c r="X248">
+        <v>1.02</v>
+      </c>
+      <c r="Y248">
+        <v>1.32</v>
+      </c>
+      <c r="Z248">
+        <v>3.22</v>
+      </c>
+      <c r="AA248">
+        <v>2.05</v>
+      </c>
+      <c r="AB248">
+        <v>1.75</v>
+      </c>
+      <c r="AC248">
+        <v>3.56</v>
+      </c>
+      <c r="AD248">
+        <v>1.24</v>
+      </c>
+      <c r="AE248">
+        <v>1.05</v>
+      </c>
+      <c r="AF248">
+        <v>1.75</v>
+      </c>
+      <c r="AG248">
+        <v>1.92</v>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ248">
         <v>1.28</v>
       </c>
-      <c r="T248">
-        <v>3.15</v>
-      </c>
-      <c r="U248">
-        <v>2.41</v>
-      </c>
-      <c r="V248">
-        <v>1.47</v>
-      </c>
-      <c r="W248">
-        <v>1.08</v>
-      </c>
-      <c r="X248">
-        <v>1.03</v>
-      </c>
-      <c r="Y248">
-        <v>1.18</v>
-      </c>
-      <c r="Z248">
-        <v>3.92</v>
-      </c>
-      <c r="AA248">
-        <v>1.75</v>
-      </c>
-      <c r="AB248">
-        <v>1.93</v>
-      </c>
-      <c r="AC248">
-        <v>2.66</v>
-      </c>
-      <c r="AD248">
-        <v>1.37</v>
-      </c>
-      <c r="AE248">
-        <v>1.16</v>
-      </c>
-      <c r="AF248">
-        <v>1.62</v>
-      </c>
-      <c r="AG248">
-        <v>2.15</v>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ248">
-        <v>1.2</v>
-      </c>
       <c r="AK248">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,80 +42689,80 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O260">
-        <v>4.09</v>
+        <v>3.95</v>
       </c>
       <c r="P260">
-        <v>4.68</v>
+        <v>3.1</v>
       </c>
       <c r="Q260">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="R260">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S260">
+        <v>1.2</v>
+      </c>
+      <c r="T260">
+        <v>4</v>
+      </c>
+      <c r="U260">
+        <v>2</v>
+      </c>
+      <c r="V260">
+        <v>1.67</v>
+      </c>
+      <c r="W260">
+        <v>1.14</v>
+      </c>
+      <c r="X260">
+        <v>1.02</v>
+      </c>
+      <c r="Y260">
+        <v>1.12</v>
+      </c>
+      <c r="Z260">
+        <v>5.75</v>
+      </c>
+      <c r="AA260">
+        <v>1.46</v>
+      </c>
+      <c r="AB260">
+        <v>2.63</v>
+      </c>
+      <c r="AC260">
+        <v>2.05</v>
+      </c>
+      <c r="AD260">
+        <v>1.66</v>
+      </c>
+      <c r="AE260">
+        <v>1.26</v>
+      </c>
+      <c r="AF260">
+        <v>1.4</v>
+      </c>
+      <c r="AG260">
+        <v>2.75</v>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ260">
         <v>1.25</v>
       </c>
-      <c r="T260">
-        <v>3.45</v>
-      </c>
-      <c r="U260">
-        <v>2.3</v>
-      </c>
-      <c r="V260">
-        <v>1.6</v>
-      </c>
-      <c r="W260">
-        <v>1.15</v>
-      </c>
-      <c r="X260">
-        <v>1.01</v>
-      </c>
-      <c r="Y260">
-        <v>1.16</v>
-      </c>
-      <c r="Z260">
-        <v>4.9</v>
-      </c>
-      <c r="AA260">
-        <v>1.58</v>
-      </c>
-      <c r="AB260">
-        <v>2.2</v>
-      </c>
-      <c r="AC260">
-        <v>2.4</v>
-      </c>
-      <c r="AD260">
-        <v>1.48</v>
-      </c>
-      <c r="AE260">
-        <v>1.22</v>
-      </c>
-      <c r="AF260">
+      <c r="AK260">
         <v>1.65</v>
-      </c>
-      <c r="AG260">
-        <v>2.15</v>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ260">
-        <v>1.24</v>
-      </c>
-      <c r="AK260">
-        <v>2.1</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,64 +42852,64 @@
         </is>
       </c>
       <c r="N261">
+        <v>1.75</v>
+      </c>
+      <c r="O261">
+        <v>4.09</v>
+      </c>
+      <c r="P261">
+        <v>4.68</v>
+      </c>
+      <c r="Q261">
+        <v>2.15</v>
+      </c>
+      <c r="R261">
+        <v>2.38</v>
+      </c>
+      <c r="S261">
+        <v>1.25</v>
+      </c>
+      <c r="T261">
+        <v>3.45</v>
+      </c>
+      <c r="U261">
+        <v>2.3</v>
+      </c>
+      <c r="V261">
+        <v>1.6</v>
+      </c>
+      <c r="W261">
+        <v>1.15</v>
+      </c>
+      <c r="X261">
+        <v>1.01</v>
+      </c>
+      <c r="Y261">
+        <v>1.16</v>
+      </c>
+      <c r="Z261">
+        <v>4.9</v>
+      </c>
+      <c r="AA261">
+        <v>1.58</v>
+      </c>
+      <c r="AB261">
         <v>2.2</v>
       </c>
-      <c r="O261">
-        <v>3.95</v>
-      </c>
-      <c r="P261">
-        <v>3.1</v>
-      </c>
-      <c r="Q261">
-        <v>2.45</v>
-      </c>
-      <c r="R261">
+      <c r="AC261">
         <v>2.4</v>
       </c>
-      <c r="S261">
-        <v>1.2</v>
-      </c>
-      <c r="T261">
-        <v>4</v>
-      </c>
-      <c r="U261">
-        <v>2</v>
-      </c>
-      <c r="V261">
-        <v>1.67</v>
-      </c>
-      <c r="W261">
-        <v>1.14</v>
-      </c>
-      <c r="X261">
-        <v>1.02</v>
-      </c>
-      <c r="Y261">
-        <v>1.12</v>
-      </c>
-      <c r="Z261">
-        <v>5.75</v>
-      </c>
-      <c r="AA261">
-        <v>1.46</v>
-      </c>
-      <c r="AB261">
-        <v>2.63</v>
-      </c>
-      <c r="AC261">
-        <v>2.05</v>
-      </c>
       <c r="AD261">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AE261">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF261">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AG261">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK261">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AL261">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="O96">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q96">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R96">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S96">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T96">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U96">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="V96">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W96">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y96">
+        <v>1.25</v>
+      </c>
+      <c r="Z96">
+        <v>3.34</v>
+      </c>
+      <c r="AA96">
+        <v>1.88</v>
+      </c>
+      <c r="AB96">
+        <v>1.85</v>
+      </c>
+      <c r="AC96">
+        <v>3.08</v>
+      </c>
+      <c r="AD96">
+        <v>1.28</v>
+      </c>
+      <c r="AE96">
+        <v>1.1</v>
+      </c>
+      <c r="AF96">
+        <v>1.7</v>
+      </c>
+      <c r="AG96">
+        <v>2.05</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
         <v>1.3</v>
       </c>
-      <c r="Z96">
-        <v>3.08</v>
-      </c>
-      <c r="AA96">
-        <v>1.98</v>
-      </c>
-      <c r="AB96">
-        <v>1.78</v>
-      </c>
-      <c r="AC96">
-        <v>3.34</v>
-      </c>
-      <c r="AD96">
-        <v>1.24</v>
-      </c>
-      <c r="AE96">
-        <v>1.05</v>
-      </c>
-      <c r="AF96">
-        <v>1.8</v>
-      </c>
-      <c r="AG96">
-        <v>1.85</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.29</v>
-      </c>
       <c r="AK96">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,31 +16120,31 @@
         </is>
       </c>
       <c r="N97">
+        <v>2.06</v>
+      </c>
+      <c r="O97">
+        <v>3.35</v>
+      </c>
+      <c r="P97">
+        <v>3.41</v>
+      </c>
+      <c r="Q97">
         <v>2.62</v>
       </c>
-      <c r="O97">
-        <v>3.5</v>
-      </c>
-      <c r="P97">
-        <v>2.5</v>
-      </c>
-      <c r="Q97">
-        <v>3.2</v>
-      </c>
       <c r="R97">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S97">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="U97">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="V97">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W97">
         <v>1.08</v>
@@ -16153,47 +16153,47 @@
         <v>1.05</v>
       </c>
       <c r="Y97">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z97">
         <v>3.34</v>
       </c>
       <c r="AA97">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB97">
         <v>1.85</v>
       </c>
       <c r="AC97">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD97">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE97">
         <v>1.1</v>
       </c>
       <c r="AF97">
+        <v>1.73</v>
+      </c>
+      <c r="AG97">
+        <v>1.98</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <v>1.24</v>
+      </c>
+      <c r="AK97">
         <v>1.7</v>
-      </c>
-      <c r="AG97">
-        <v>2.05</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.3</v>
-      </c>
-      <c r="AK97">
-        <v>1.4</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,65 +16283,65 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="O98">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P98">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="Q98">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="R98">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S98">
         <v>1.36</v>
       </c>
       <c r="T98">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="U98">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V98">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W98">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X98">
+        <v>1.01</v>
+      </c>
+      <c r="Y98">
+        <v>1.3</v>
+      </c>
+      <c r="Z98">
+        <v>3.08</v>
+      </c>
+      <c r="AA98">
+        <v>1.98</v>
+      </c>
+      <c r="AB98">
+        <v>1.78</v>
+      </c>
+      <c r="AC98">
+        <v>3.34</v>
+      </c>
+      <c r="AD98">
+        <v>1.24</v>
+      </c>
+      <c r="AE98">
         <v>1.05</v>
       </c>
-      <c r="Y98">
-        <v>1.24</v>
-      </c>
-      <c r="Z98">
-        <v>3.34</v>
-      </c>
-      <c r="AA98">
+      <c r="AF98">
+        <v>1.8</v>
+      </c>
+      <c r="AG98">
         <v>1.85</v>
       </c>
-      <c r="AB98">
-        <v>1.85</v>
-      </c>
-      <c r="AC98">
-        <v>3.3</v>
-      </c>
-      <c r="AD98">
-        <v>1.33</v>
-      </c>
-      <c r="AE98">
-        <v>1.1</v>
-      </c>
-      <c r="AF98">
-        <v>1.73</v>
-      </c>
-      <c r="AG98">
-        <v>1.98</v>
-      </c>
       <c r="AH98" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK98">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O113">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="P113">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q113">
-        <v>3.1</v>
+        <v>2.17</v>
       </c>
       <c r="R113">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="S113">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="T113">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="U113">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="V113">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X113">
         <v>1.05</v>
       </c>
       <c r="Y113">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z113">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="AA113">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AB113">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC113">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="AD113">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF113">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG113">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK113">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="O114">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="P114">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q114">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="R114">
-        <v>2.39</v>
+        <v>1.92</v>
       </c>
       <c r="S114">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="T114">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="U114">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="V114">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X114">
         <v>1.05</v>
       </c>
       <c r="Y114">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z114">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="AA114">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB114">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC114">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="AD114">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE114">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF114">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG114">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK114">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -36984,61 +36984,61 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="O225">
+        <v>3.25</v>
+      </c>
+      <c r="P225">
+        <v>3.35</v>
+      </c>
+      <c r="Q225">
+        <v>2.43</v>
+      </c>
+      <c r="R225">
+        <v>1.95</v>
+      </c>
+      <c r="S225">
+        <v>1.5</v>
+      </c>
+      <c r="T225">
+        <v>2.44</v>
+      </c>
+      <c r="U225">
         <v>3.16</v>
       </c>
-      <c r="P225">
-        <v>3.85</v>
-      </c>
-      <c r="Q225">
-        <v>2.58</v>
-      </c>
-      <c r="R225">
-        <v>2.09</v>
-      </c>
-      <c r="S225">
-        <v>1.47</v>
-      </c>
-      <c r="T225">
-        <v>2.59</v>
-      </c>
-      <c r="U225">
-        <v>3.4</v>
-      </c>
       <c r="V225">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W225">
         <v>1.02</v>
       </c>
       <c r="X225">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y225">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z225">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA225">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AB225">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC225">
         <v>4.4</v>
       </c>
       <c r="AD225">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE225">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF225">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG225">
         <v>1.73</v>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK225">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37156,16 +37156,16 @@
         <v>4.26</v>
       </c>
       <c r="Q226">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R226">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="S226">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T226">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U226">
         <v>3.52</v>
@@ -37174,37 +37174,37 @@
         <v>1.23</v>
       </c>
       <c r="W226">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X226">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y226">
         <v>1.49</v>
       </c>
       <c r="Z226">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="AA226">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AB226">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AC226">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="AD226">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE226">
         <v>1.01</v>
       </c>
       <c r="AF226">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG226">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK226">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>2.5</v>
       </c>
       <c r="AA239">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB239">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39429,46 +39429,46 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O240">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="P240">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="Q240">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="R240">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S240">
         <v>1.59</v>
       </c>
       <c r="T240">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="U240">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="V240">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W240">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X240">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y240">
         <v>1.53</v>
       </c>
       <c r="Z240">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA240">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="AB240">
         <v>1.36</v>
@@ -39477,16 +39477,16 @@
         <v>5.75</v>
       </c>
       <c r="AD240">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE240">
         <v>1.03</v>
       </c>
       <c r="AF240">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="AG240">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,64 +41711,64 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="O254">
         <v>3.66</v>
       </c>
       <c r="P254">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="Q254">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R254">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S254">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T254">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U254">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V254">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W254">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X254">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y254">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z254">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AA254">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB254">
         <v>2.05</v>
       </c>
       <c r="AC254">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AD254">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE254">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF254">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG254">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK254">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G255">
@@ -41874,64 +41874,64 @@
         </is>
       </c>
       <c r="N255">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="O255">
         <v>3.66</v>
       </c>
       <c r="P255">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AA255">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB255">
         <v>2.05</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="O266">
+        <v>5.08</v>
+      </c>
+      <c r="P266">
+        <v>7.43</v>
+      </c>
+      <c r="Q266">
+        <v>1.94</v>
+      </c>
+      <c r="R266">
+        <v>2.73</v>
+      </c>
+      <c r="S266">
+        <v>1.22</v>
+      </c>
+      <c r="T266">
         <v>4.1</v>
       </c>
-      <c r="P266">
-        <v>4.58</v>
-      </c>
-      <c r="Q266">
-        <v>2.15</v>
-      </c>
-      <c r="R266">
-        <v>2.3</v>
-      </c>
-      <c r="S266">
-        <v>1.28</v>
-      </c>
-      <c r="T266">
-        <v>3.3</v>
-      </c>
       <c r="U266">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="V266">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W266">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X266">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y266">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z266">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA266">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AB266">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AC266">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="AD266">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AE266">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF266">
         <v>1.55</v>
       </c>
       <c r="AG266">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK266">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,64 +43830,64 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="O267">
-        <v>5.08</v>
+        <v>4.1</v>
       </c>
       <c r="P267">
-        <v>7.43</v>
+        <v>4.58</v>
       </c>
       <c r="Q267">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="R267">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="S267">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T267">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="U267">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="V267">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="W267">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X267">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y267">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z267">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA267">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AB267">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC267">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="AD267">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AE267">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF267">
         <v>1.55</v>
       </c>
       <c r="AG267">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK267">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="O271">
-        <v>4.16</v>
+        <v>4.84</v>
       </c>
       <c r="P271">
-        <v>4.83</v>
+        <v>5.46</v>
       </c>
       <c r="Q271">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="R271">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="S271">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T271">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U271">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V271">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W271">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X271">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y271">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z271">
-        <v>5.51</v>
+        <v>5.64</v>
       </c>
       <c r="AA271">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB271">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AC271">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AD271">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AE271">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF271">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AG271">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK271">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,80 +44645,80 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="O272">
-        <v>4.84</v>
+        <v>4.16</v>
       </c>
       <c r="P272">
-        <v>5.46</v>
+        <v>4.83</v>
       </c>
       <c r="Q272">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="R272">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="S272">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T272">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U272">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V272">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W272">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X272">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y272">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z272">
-        <v>5.64</v>
+        <v>5.51</v>
       </c>
       <c r="AA272">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB272">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC272">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AD272">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AE272">
+        <v>1.25</v>
+      </c>
+      <c r="AF272">
+        <v>1.44</v>
+      </c>
+      <c r="AG272">
+        <v>2.65</v>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ272">
         <v>1.3</v>
       </c>
-      <c r="AF272">
-        <v>1.49</v>
-      </c>
-      <c r="AG272">
-        <v>2.45</v>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ272">
-        <v>1.18</v>
-      </c>
       <c r="AK272">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AL272">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P24">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q24">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S24">
+        <v>1.38</v>
+      </c>
+      <c r="T24">
+        <v>2.65</v>
+      </c>
+      <c r="U24">
+        <v>2.94</v>
+      </c>
+      <c r="V24">
         <v>1.37</v>
       </c>
-      <c r="T24">
-        <v>2.78</v>
-      </c>
-      <c r="U24">
-        <v>2.75</v>
-      </c>
-      <c r="V24">
-        <v>1.4</v>
-      </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
-        <v>3.44</v>
+        <v>2.95</v>
       </c>
       <c r="AA24">
+        <v>1.95</v>
+      </c>
+      <c r="AB24">
+        <v>1.73</v>
+      </c>
+      <c r="AC24">
+        <v>3.5</v>
+      </c>
+      <c r="AD24">
+        <v>1.24</v>
+      </c>
+      <c r="AE24">
+        <v>1.09</v>
+      </c>
+      <c r="AF24">
         <v>1.8</v>
       </c>
-      <c r="AB24">
-        <v>1.96</v>
-      </c>
-      <c r="AC24">
-        <v>3.1</v>
-      </c>
-      <c r="AD24">
-        <v>1.32</v>
-      </c>
-      <c r="AE24">
-        <v>1.14</v>
-      </c>
-      <c r="AF24">
-        <v>1.65</v>
-      </c>
       <c r="AG24">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.1</v>
+        <v>3.33</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q25">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R25">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="U25">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1.03</v>
       </c>
       <c r="Y25">
+        <v>1.25</v>
+      </c>
+      <c r="Z25">
+        <v>3.38</v>
+      </c>
+      <c r="AA25">
+        <v>1.85</v>
+      </c>
+      <c r="AB25">
+        <v>1.85</v>
+      </c>
+      <c r="AC25">
+        <v>3.05</v>
+      </c>
+      <c r="AD25">
         <v>1.33</v>
       </c>
-      <c r="Z25">
-        <v>2.9</v>
-      </c>
-      <c r="AA25">
-        <v>2.14</v>
-      </c>
-      <c r="AB25">
-        <v>1.72</v>
-      </c>
-      <c r="AC25">
-        <v>3.54</v>
-      </c>
-      <c r="AD25">
-        <v>1.22</v>
-      </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AG25">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O26">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q26">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="U26">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z26">
-        <v>2.95</v>
+        <v>3.44</v>
       </c>
       <c r="AA26">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AC26">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.33</v>
+        <v>4.1</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q27">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="AA27">
+        <v>2.14</v>
+      </c>
+      <c r="AB27">
+        <v>1.72</v>
+      </c>
+      <c r="AC27">
+        <v>3.54</v>
+      </c>
+      <c r="AD27">
+        <v>1.22</v>
+      </c>
+      <c r="AE27">
+        <v>1.06</v>
+      </c>
+      <c r="AF27">
+        <v>1.89</v>
+      </c>
+      <c r="AG27">
         <v>1.85</v>
       </c>
-      <c r="AB27">
-        <v>1.85</v>
-      </c>
-      <c r="AC27">
-        <v>3.05</v>
-      </c>
-      <c r="AD27">
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.33</v>
       </c>
-      <c r="AE27">
-        <v>1.11</v>
-      </c>
-      <c r="AF27">
-        <v>1.73</v>
-      </c>
-      <c r="AG27">
-        <v>2</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.3</v>
-      </c>
       <c r="AK27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="O32">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q32">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="R32">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T32">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W32">
+        <v>1.05</v>
+      </c>
+      <c r="X32">
         <v>1.06</v>
       </c>
-      <c r="X32">
+      <c r="Y32">
+        <v>1.3</v>
+      </c>
+      <c r="Z32">
+        <v>3.08</v>
+      </c>
+      <c r="AA32">
+        <v>2</v>
+      </c>
+      <c r="AB32">
+        <v>1.75</v>
+      </c>
+      <c r="AC32">
+        <v>3.55</v>
+      </c>
+      <c r="AD32">
+        <v>1.25</v>
+      </c>
+      <c r="AE32">
         <v>1.03</v>
       </c>
-      <c r="Y32">
+      <c r="AF32">
+        <v>1.8</v>
+      </c>
+      <c r="AG32">
+        <v>1.91</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.24</v>
       </c>
-      <c r="Z32">
-        <v>3.52</v>
-      </c>
-      <c r="AA32">
-        <v>1.9</v>
-      </c>
-      <c r="AB32">
-        <v>1.88</v>
-      </c>
-      <c r="AC32">
-        <v>3.4</v>
-      </c>
-      <c r="AD32">
-        <v>1.32</v>
-      </c>
-      <c r="AE32">
-        <v>1.06</v>
-      </c>
-      <c r="AF32">
-        <v>1.64</v>
-      </c>
-      <c r="AG32">
-        <v>2.08</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.26</v>
-      </c>
       <c r="AK32">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.32</v>
+        <v>1.9</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="P33">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="Q33">
-        <v>3.75</v>
+        <v>2.64</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U33">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z33">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AB33">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG33">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
         <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U34">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W34">
         <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="AA34">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AB34">
+        <v>1.74</v>
+      </c>
+      <c r="AC34">
+        <v>3.2</v>
+      </c>
+      <c r="AD34">
+        <v>1.36</v>
+      </c>
+      <c r="AE34">
+        <v>1.08</v>
+      </c>
+      <c r="AF34">
+        <v>1.62</v>
+      </c>
+      <c r="AG34">
         <v>2.1</v>
       </c>
-      <c r="AC34">
-        <v>2.6</v>
-      </c>
-      <c r="AD34">
-        <v>1.44</v>
-      </c>
-      <c r="AE34">
-        <v>1.11</v>
-      </c>
-      <c r="AF34">
-        <v>1.55</v>
-      </c>
-      <c r="AG34">
-        <v>2.25</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P35">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U35">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="AA35">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB35">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AC35">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG35">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P53">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q53">
-        <v>3.24</v>
+        <v>4.01</v>
       </c>
       <c r="R53">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S53">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="T53">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="U53">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="V53">
+        <v>1.44</v>
+      </c>
+      <c r="W53">
+        <v>1.07</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>1.25</v>
+      </c>
+      <c r="Z53">
+        <v>3.65</v>
+      </c>
+      <c r="AA53">
         <v>1.73</v>
       </c>
-      <c r="W53">
-        <v>1.16</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.12</v>
-      </c>
-      <c r="Z53">
-        <v>6.14</v>
-      </c>
-      <c r="AA53">
-        <v>1.42</v>
-      </c>
       <c r="AB53">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC53">
-        <v>1.95</v>
+        <v>2.78</v>
       </c>
       <c r="AD53">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="AE53">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AG53">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AK53">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="O54">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Q54">
-        <v>4.01</v>
+        <v>3.24</v>
       </c>
       <c r="R54">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S54">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="T54">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="U54">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="V54">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="Z54">
-        <v>3.65</v>
+        <v>6.14</v>
       </c>
       <c r="AA54">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AB54">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="AC54">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
       <c r="AD54">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AE54">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AF54">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AG54">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AK54">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.24</v>
+        <v>1.43</v>
       </c>
       <c r="O60">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="P60">
-        <v>2.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q60">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF60">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK60">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="O61">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>6.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P62">
-        <v>2.37</v>
+        <v>5.9</v>
       </c>
       <c r="Q62">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="R62">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="S62">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T62">
-        <v>3.12</v>
+        <v>4.75</v>
       </c>
       <c r="U62">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="V62">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="W62">
+        <v>1.18</v>
+      </c>
+      <c r="X62">
+        <v>1</v>
+      </c>
+      <c r="Y62">
+        <v>1.06</v>
+      </c>
+      <c r="Z62">
+        <v>7.1</v>
+      </c>
+      <c r="AA62">
+        <v>1.28</v>
+      </c>
+      <c r="AB62">
+        <v>3.34</v>
+      </c>
+      <c r="AC62">
+        <v>1.73</v>
+      </c>
+      <c r="AD62">
+        <v>2.1</v>
+      </c>
+      <c r="AE62">
+        <v>1.48</v>
+      </c>
+      <c r="AF62">
+        <v>1.44</v>
+      </c>
+      <c r="AG62">
+        <v>2.5</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.07</v>
       </c>
-      <c r="X62">
-        <v>1.02</v>
-      </c>
-      <c r="Y62">
-        <v>1.15</v>
-      </c>
-      <c r="Z62">
-        <v>4.25</v>
-      </c>
-      <c r="AA62">
-        <v>1.67</v>
-      </c>
-      <c r="AB62">
-        <v>2.15</v>
-      </c>
-      <c r="AC62">
-        <v>2.62</v>
-      </c>
-      <c r="AD62">
-        <v>1.48</v>
-      </c>
-      <c r="AE62">
-        <v>1.17</v>
-      </c>
-      <c r="AF62">
-        <v>1.51</v>
-      </c>
-      <c r="AG62">
-        <v>2.36</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.24</v>
-      </c>
       <c r="AK62">
-        <v>1.43</v>
+        <v>3.3</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="O63">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P63">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="Q63">
-        <v>3.87</v>
+        <v>3.1</v>
       </c>
       <c r="R63">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="S63">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="T63">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U63">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="V63">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="W63">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z63">
-        <v>6</v>
+        <v>3.58</v>
       </c>
       <c r="AA63">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB63">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC63">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AD63">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AE63">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF63">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AK63">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="O64">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="Q64">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="T64">
-        <v>4.65</v>
+        <v>3.25</v>
       </c>
       <c r="U64">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="V64">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="W64">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="Z64">
-        <v>7.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA64">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AB64">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC64">
-        <v>1.76</v>
+        <v>2.49</v>
       </c>
       <c r="AD64">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AE64">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG64">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AK64">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="O67">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q67">
-        <v>3.06</v>
+        <v>4.97</v>
       </c>
       <c r="R67">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="S67">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="T67">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="U67">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="V67">
+        <v>1.29</v>
+      </c>
+      <c r="W67">
+        <v>1</v>
+      </c>
+      <c r="X67">
+        <v>1.03</v>
+      </c>
+      <c r="Y67">
+        <v>1.38</v>
+      </c>
+      <c r="Z67">
+        <v>2.62</v>
+      </c>
+      <c r="AA67">
+        <v>2.28</v>
+      </c>
+      <c r="AB67">
+        <v>1.53</v>
+      </c>
+      <c r="AC67">
+        <v>4.5</v>
+      </c>
+      <c r="AD67">
+        <v>1.14</v>
+      </c>
+      <c r="AE67">
+        <v>1.05</v>
+      </c>
+      <c r="AF67">
+        <v>2.03</v>
+      </c>
+      <c r="AG67">
+        <v>1.69</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>1.27</v>
+      </c>
+      <c r="AK67">
         <v>1.22</v>
-      </c>
-      <c r="W67">
-        <v>1.02</v>
-      </c>
-      <c r="X67">
-        <v>1.07</v>
-      </c>
-      <c r="Y67">
-        <v>1.51</v>
-      </c>
-      <c r="Z67">
-        <v>2.39</v>
-      </c>
-      <c r="AA67">
-        <v>2.52</v>
-      </c>
-      <c r="AB67">
-        <v>1.41</v>
-      </c>
-      <c r="AC67">
-        <v>5.5</v>
-      </c>
-      <c r="AD67">
-        <v>1.11</v>
-      </c>
-      <c r="AE67">
-        <v>1.01</v>
-      </c>
-      <c r="AF67">
-        <v>2.15</v>
-      </c>
-      <c r="AG67">
-        <v>1.64</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.33</v>
-      </c>
-      <c r="AK67">
-        <v>1.51</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="O68">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P68">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="Q68">
-        <v>4.97</v>
+        <v>3.06</v>
       </c>
       <c r="R68">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="S68">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="T68">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="U68">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="V68">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W68">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y68">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Z68">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="AA68">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="AB68">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AC68">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AD68">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF68">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AG68">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK68">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12703,16 +12703,16 @@
         <v>3.43</v>
       </c>
       <c r="P76">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="Q76">
         <v>2.65</v>
       </c>
       <c r="R76">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S76">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T76">
         <v>2.9</v>
@@ -12730,22 +12730,22 @@
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA76">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB76">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC76">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD76">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE76">
         <v>1.08</v>
@@ -12754,7 +12754,7 @@
         <v>1.7</v>
       </c>
       <c r="AG76">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,37 +14816,37 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="O89">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q89">
-        <v>2.45</v>
+        <v>2.89</v>
       </c>
       <c r="R89">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U89">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V89">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W89">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y89">
         <v>1.3</v>
@@ -14855,25 +14855,25 @@
         <v>3.08</v>
       </c>
       <c r="AA89">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB89">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC89">
         <v>3.5</v>
       </c>
       <c r="AD89">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE89">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF89">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG89">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK89">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="O90">
+        <v>3.6</v>
+      </c>
+      <c r="P90">
+        <v>4.2</v>
+      </c>
+      <c r="Q90">
+        <v>2.31</v>
+      </c>
+      <c r="R90">
+        <v>2.1</v>
+      </c>
+      <c r="S90">
+        <v>1.34</v>
+      </c>
+      <c r="T90">
+        <v>3</v>
+      </c>
+      <c r="U90">
+        <v>2.62</v>
+      </c>
+      <c r="V90">
+        <v>1.42</v>
+      </c>
+      <c r="W90">
+        <v>1.06</v>
+      </c>
+      <c r="X90">
+        <v>1.05</v>
+      </c>
+      <c r="Y90">
+        <v>1.27</v>
+      </c>
+      <c r="Z90">
         <v>3.4</v>
       </c>
-      <c r="P90">
-        <v>2.89</v>
-      </c>
-      <c r="Q90">
+      <c r="AA90">
+        <v>1.84</v>
+      </c>
+      <c r="AB90">
+        <v>1.95</v>
+      </c>
+      <c r="AC90">
         <v>3</v>
       </c>
-      <c r="R90">
-        <v>1.96</v>
-      </c>
-      <c r="S90">
-        <v>1.36</v>
-      </c>
-      <c r="T90">
-        <v>2.7</v>
-      </c>
-      <c r="U90">
-        <v>3</v>
-      </c>
-      <c r="V90">
-        <v>1.35</v>
-      </c>
-      <c r="W90">
-        <v>1.04</v>
-      </c>
-      <c r="X90">
-        <v>1</v>
-      </c>
-      <c r="Y90">
-        <v>1.31</v>
-      </c>
-      <c r="Z90">
-        <v>3.07</v>
-      </c>
-      <c r="AA90">
-        <v>2.1</v>
-      </c>
-      <c r="AB90">
-        <v>1.67</v>
-      </c>
-      <c r="AC90">
-        <v>3.83</v>
-      </c>
       <c r="AD90">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF90">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG90">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,61 +15142,61 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="Q91">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R91">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
         <v>1.36</v>
       </c>
       <c r="T91">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U91">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W91">
         <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z91">
         <v>3.3</v>
       </c>
       <c r="AA91">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB91">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC91">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD91">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE91">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF91">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
         <v>2</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK91">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O92">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P92">
         <v>3.2</v>
       </c>
       <c r="Q92">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="R92">
         <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T92">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="U92">
         <v>2.8</v>
       </c>
       <c r="V92">
+        <v>1.38</v>
+      </c>
+      <c r="W92">
+        <v>1.03</v>
+      </c>
+      <c r="X92">
+        <v>1.01</v>
+      </c>
+      <c r="Y92">
         <v>1.35</v>
       </c>
-      <c r="W92">
-        <v>1.05</v>
-      </c>
-      <c r="X92">
-        <v>1.06</v>
-      </c>
-      <c r="Y92">
-        <v>1.3</v>
-      </c>
       <c r="Z92">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA92">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AB92">
         <v>1.73</v>
       </c>
       <c r="AC92">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD92">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF92">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG92">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="O93">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P93">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q93">
-        <v>2.31</v>
+        <v>3.1</v>
       </c>
       <c r="R93">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T93">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="U93">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V93">
         <v>1.42</v>
       </c>
       <c r="W93">
+        <v>1.04</v>
+      </c>
+      <c r="X93">
+        <v>1.01</v>
+      </c>
+      <c r="Y93">
+        <v>1.24</v>
+      </c>
+      <c r="Z93">
+        <v>3.34</v>
+      </c>
+      <c r="AA93">
+        <v>1.88</v>
+      </c>
+      <c r="AB93">
+        <v>1.85</v>
+      </c>
+      <c r="AC93">
+        <v>3.19</v>
+      </c>
+      <c r="AD93">
+        <v>1.33</v>
+      </c>
+      <c r="AE93">
         <v>1.06</v>
       </c>
-      <c r="X93">
-        <v>1.05</v>
-      </c>
-      <c r="Y93">
-        <v>1.27</v>
-      </c>
-      <c r="Z93">
-        <v>3.4</v>
-      </c>
-      <c r="AA93">
-        <v>1.84</v>
-      </c>
-      <c r="AB93">
-        <v>1.95</v>
-      </c>
-      <c r="AC93">
-        <v>3</v>
-      </c>
-      <c r="AD93">
+      <c r="AF93">
+        <v>1.7</v>
+      </c>
+      <c r="AG93">
+        <v>2.05</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
         <v>1.3</v>
       </c>
-      <c r="AE93">
-        <v>1.11</v>
-      </c>
-      <c r="AF93">
-        <v>1.76</v>
-      </c>
-      <c r="AG93">
-        <v>1.97</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.29</v>
-      </c>
       <c r="AK93">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,80 +15631,80 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="O94">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P94">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="Q94">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="R94">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S94">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T94">
         <v>2.75</v>
       </c>
       <c r="U94">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="V94">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W94">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
         <v>1.3</v>
       </c>
       <c r="Z94">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA94">
+        <v>2</v>
+      </c>
+      <c r="AB94">
+        <v>1.8</v>
+      </c>
+      <c r="AC94">
+        <v>3.5</v>
+      </c>
+      <c r="AD94">
+        <v>1.25</v>
+      </c>
+      <c r="AE94">
+        <v>1.1</v>
+      </c>
+      <c r="AF94">
+        <v>1.8</v>
+      </c>
+      <c r="AG94">
+        <v>1.85</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ94">
+        <v>1.29</v>
+      </c>
+      <c r="AK94">
         <v>1.95</v>
-      </c>
-      <c r="AB94">
-        <v>1.78</v>
-      </c>
-      <c r="AC94">
-        <v>3.14</v>
-      </c>
-      <c r="AD94">
-        <v>1.29</v>
-      </c>
-      <c r="AE94">
-        <v>1.11</v>
-      </c>
-      <c r="AF94">
-        <v>1.75</v>
-      </c>
-      <c r="AG94">
-        <v>2</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ94">
-        <v>1.33</v>
-      </c>
-      <c r="AK94">
-        <v>1.57</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O95">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P95">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q95">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R95">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S95">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T95">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="U95">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="V95">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W95">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Z95">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="AA95">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AB95">
+        <v>1.73</v>
+      </c>
+      <c r="AC95">
+        <v>3.5</v>
+      </c>
+      <c r="AD95">
+        <v>1.27</v>
+      </c>
+      <c r="AE95">
+        <v>1.03</v>
+      </c>
+      <c r="AF95">
         <v>1.85</v>
       </c>
-      <c r="AC95">
-        <v>3.19</v>
-      </c>
-      <c r="AD95">
-        <v>1.33</v>
-      </c>
-      <c r="AE95">
-        <v>1.06</v>
-      </c>
-      <c r="AF95">
-        <v>1.7</v>
-      </c>
       <c r="AG95">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O96">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P96">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q96">
+        <v>3.1</v>
+      </c>
+      <c r="R96">
+        <v>2.15</v>
+      </c>
+      <c r="S96">
+        <v>1.36</v>
+      </c>
+      <c r="T96">
+        <v>2.9</v>
+      </c>
+      <c r="U96">
         <v>2.88</v>
       </c>
-      <c r="R96">
-        <v>2.1</v>
-      </c>
-      <c r="S96">
-        <v>1.43</v>
-      </c>
-      <c r="T96">
-        <v>2.56</v>
-      </c>
-      <c r="U96">
-        <v>2.8</v>
-      </c>
       <c r="V96">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W96">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y96">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z96">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AA96">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AB96">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC96">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="AD96">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE96">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG96">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="O97">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="Q97">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="R97">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S97">
+        <v>1.36</v>
+      </c>
+      <c r="T97">
+        <v>3.01</v>
+      </c>
+      <c r="U97">
+        <v>2.65</v>
+      </c>
+      <c r="V97">
         <v>1.4</v>
       </c>
-      <c r="T97">
-        <v>2.8</v>
-      </c>
-      <c r="U97">
-        <v>2.95</v>
-      </c>
-      <c r="V97">
-        <v>1.34</v>
-      </c>
       <c r="W97">
+        <v>1.08</v>
+      </c>
+      <c r="X97">
         <v>1.05</v>
       </c>
-      <c r="X97">
-        <v>1.01</v>
-      </c>
       <c r="Y97">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z97">
+        <v>3.4</v>
+      </c>
+      <c r="AA97">
+        <v>1.9</v>
+      </c>
+      <c r="AB97">
+        <v>1.83</v>
+      </c>
+      <c r="AC97">
         <v>3.22</v>
       </c>
-      <c r="AA97">
-        <v>2.06</v>
-      </c>
-      <c r="AB97">
+      <c r="AD97">
+        <v>1.3</v>
+      </c>
+      <c r="AE97">
+        <v>1.1</v>
+      </c>
+      <c r="AF97">
         <v>1.73</v>
       </c>
-      <c r="AC97">
-        <v>3.5</v>
-      </c>
-      <c r="AD97">
-        <v>1.27</v>
-      </c>
-      <c r="AE97">
-        <v>1.03</v>
-      </c>
-      <c r="AF97">
-        <v>1.85</v>
-      </c>
       <c r="AG97">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.3</v>
       </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O98">
         <v>3.4</v>
       </c>
       <c r="P98">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="Q98">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="R98">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="S98">
         <v>1.36</v>
       </c>
       <c r="T98">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="U98">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="V98">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W98">
+        <v>1.04</v>
+      </c>
+      <c r="X98">
+        <v>1</v>
+      </c>
+      <c r="Y98">
+        <v>1.31</v>
+      </c>
+      <c r="Z98">
+        <v>3.07</v>
+      </c>
+      <c r="AA98">
+        <v>2.1</v>
+      </c>
+      <c r="AB98">
+        <v>1.67</v>
+      </c>
+      <c r="AC98">
+        <v>3.83</v>
+      </c>
+      <c r="AD98">
+        <v>1.24</v>
+      </c>
+      <c r="AE98">
         <v>1.08</v>
       </c>
-      <c r="X98">
-        <v>1.05</v>
-      </c>
-      <c r="Y98">
-        <v>1.29</v>
-      </c>
-      <c r="Z98">
-        <v>3.4</v>
-      </c>
-      <c r="AA98">
-        <v>1.9</v>
-      </c>
-      <c r="AB98">
+      <c r="AF98">
         <v>1.83</v>
       </c>
-      <c r="AC98">
-        <v>3.22</v>
-      </c>
-      <c r="AD98">
-        <v>1.3</v>
-      </c>
-      <c r="AE98">
-        <v>1.1</v>
-      </c>
-      <c r="AF98">
-        <v>1.73</v>
-      </c>
       <c r="AG98">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK98">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -20367,7 +20367,7 @@
         <v>6.22</v>
       </c>
       <c r="Q123">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="R123">
         <v>2.45</v>
@@ -20376,7 +20376,7 @@
         <v>1.3</v>
       </c>
       <c r="T123">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U123">
         <v>2.5</v>
@@ -20385,34 +20385,34 @@
         <v>1.5</v>
       </c>
       <c r="W123">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X123">
         <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z123">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA123">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AB123">
         <v>2.05</v>
       </c>
       <c r="AC123">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD123">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE123">
         <v>1.15</v>
       </c>
       <c r="AF123">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AG123">
         <v>1.77</v>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK123">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20524,10 +20524,10 @@
         <v>1.34</v>
       </c>
       <c r="O124">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="P124">
-        <v>8.699999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -21336,19 +21336,19 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O129">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P129">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q129">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R129">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S129">
         <v>1.3</v>
@@ -21363,19 +21363,19 @@
         <v>1.51</v>
       </c>
       <c r="W129">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X129">
         <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z129">
         <v>4.2</v>
       </c>
       <c r="AA129">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB129">
         <v>2.15</v>
@@ -21384,7 +21384,7 @@
         <v>2.65</v>
       </c>
       <c r="AD129">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE129">
         <v>1.15</v>
@@ -21828,61 +21828,61 @@
         <v>1.36</v>
       </c>
       <c r="O132">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="P132">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="Q132">
         <v>1.78</v>
       </c>
       <c r="R132">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="S132">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T132">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="U132">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="V132">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W132">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X132">
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z132">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA132">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB132">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AC132">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD132">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE132">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF132">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG132">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK132">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="O135">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P135">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="O136">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P136">
-        <v>8.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="Q136">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="R136">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S136">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T136">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U136">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V136">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W136">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X136">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z136">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AA136">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB136">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AC136">
         <v>2.38</v>
       </c>
       <c r="AD136">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE136">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF136">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AG136">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK136">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,65 +22640,65 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.87</v>
+        <v>1.3</v>
       </c>
       <c r="O137">
-        <v>3.22</v>
+        <v>4.6</v>
       </c>
       <c r="P137">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q137">
-        <v>3.82</v>
+        <v>1.8</v>
       </c>
       <c r="R137">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="S137">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="T137">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="U137">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="V137">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="W137">
+        <v>1.1</v>
+      </c>
+      <c r="X137">
         <v>1.04</v>
       </c>
-      <c r="X137">
-        <v>1.05</v>
-      </c>
       <c r="Y137">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z137">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA137">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AB137">
+        <v>2.28</v>
+      </c>
+      <c r="AC137">
+        <v>2.38</v>
+      </c>
+      <c r="AD137">
+        <v>1.55</v>
+      </c>
+      <c r="AE137">
+        <v>1.18</v>
+      </c>
+      <c r="AF137">
+        <v>1.81</v>
+      </c>
+      <c r="AG137">
         <v>1.9</v>
       </c>
-      <c r="AC137">
-        <v>3.14</v>
-      </c>
-      <c r="AD137">
-        <v>1.28</v>
-      </c>
-      <c r="AE137">
-        <v>1.06</v>
-      </c>
-      <c r="AF137">
-        <v>1.7</v>
-      </c>
-      <c r="AG137">
-        <v>2</v>
-      </c>
       <c r="AH137" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AK137">
-        <v>1.34</v>
+        <v>3</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.15</v>
+        <v>2.87</v>
       </c>
       <c r="O138">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P138">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q138">
-        <v>2.63</v>
+        <v>3.82</v>
       </c>
       <c r="R138">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="S138">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="T138">
-        <v>3.22</v>
+        <v>2.69</v>
       </c>
       <c r="U138">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="V138">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="W138">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X138">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y138">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z138">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA138">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="AB138">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AC138">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="AD138">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE138">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF138">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG138">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK138">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23627,37 +23627,37 @@
         <v>2.7</v>
       </c>
       <c r="Q143">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R143">
         <v>2</v>
       </c>
       <c r="S143">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T143">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U143">
         <v>3</v>
       </c>
       <c r="V143">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W143">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X143">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y143">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z143">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA143">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB143">
         <v>1.7</v>
@@ -23669,10 +23669,10 @@
         <v>1.22</v>
       </c>
       <c r="AE143">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF143">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG143">
         <v>1.78</v>
@@ -23691,7 +23691,7 @@
         <v>1.44</v>
       </c>
       <c r="AK143">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="O144">
         <v>5.72</v>
       </c>
       <c r="P144">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="O151">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P151">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q151">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R151">
         <v>2</v>
@@ -24940,22 +24940,22 @@
         <v>1.47</v>
       </c>
       <c r="T151">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="U151">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="V151">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W151">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X151">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y151">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z151">
         <v>2.8</v>
@@ -24964,13 +24964,13 @@
         <v>2.2</v>
       </c>
       <c r="AB151">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC151">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD151">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE151">
         <v>1.01</v>
@@ -24979,7 +24979,7 @@
         <v>1.93</v>
       </c>
       <c r="AG151">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AK151">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,80 +26389,80 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.46</v>
+        <v>3.65</v>
       </c>
       <c r="O160">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P160">
-        <v>2.87</v>
+        <v>1.87</v>
       </c>
       <c r="Q160">
-        <v>2.8</v>
+        <v>4.44</v>
       </c>
       <c r="R160">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S160">
+        <v>1.33</v>
+      </c>
+      <c r="T160">
+        <v>3.3</v>
+      </c>
+      <c r="U160">
+        <v>2.6</v>
+      </c>
+      <c r="V160">
+        <v>1.48</v>
+      </c>
+      <c r="W160">
+        <v>1.11</v>
+      </c>
+      <c r="X160">
+        <v>1.05</v>
+      </c>
+      <c r="Y160">
+        <v>1.21</v>
+      </c>
+      <c r="Z160">
+        <v>3.62</v>
+      </c>
+      <c r="AA160">
+        <v>1.83</v>
+      </c>
+      <c r="AB160">
+        <v>2.02</v>
+      </c>
+      <c r="AC160">
+        <v>2.95</v>
+      </c>
+      <c r="AD160">
         <v>1.34</v>
       </c>
-      <c r="T160">
-        <v>2.9</v>
-      </c>
-      <c r="U160">
-        <v>2.75</v>
-      </c>
-      <c r="V160">
-        <v>1.42</v>
-      </c>
-      <c r="W160">
-        <v>1.06</v>
-      </c>
-      <c r="X160">
-        <v>1.03</v>
-      </c>
-      <c r="Y160">
+      <c r="AE160">
+        <v>1.14</v>
+      </c>
+      <c r="AF160">
+        <v>1.7</v>
+      </c>
+      <c r="AG160">
+        <v>2.06</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ160">
+        <v>1.22</v>
+      </c>
+      <c r="AK160">
         <v>1.23</v>
-      </c>
-      <c r="Z160">
-        <v>3.9</v>
-      </c>
-      <c r="AA160">
-        <v>1.9</v>
-      </c>
-      <c r="AB160">
-        <v>1.99</v>
-      </c>
-      <c r="AC160">
-        <v>2.8</v>
-      </c>
-      <c r="AD160">
-        <v>1.38</v>
-      </c>
-      <c r="AE160">
-        <v>1.08</v>
-      </c>
-      <c r="AF160">
-        <v>1.64</v>
-      </c>
-      <c r="AG160">
-        <v>2.08</v>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ160">
-        <v>1.36</v>
-      </c>
-      <c r="AK160">
-        <v>1.53</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>3.65</v>
+        <v>2.46</v>
       </c>
       <c r="O161">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P161">
-        <v>1.87</v>
+        <v>2.87</v>
       </c>
       <c r="Q161">
-        <v>4.44</v>
+        <v>2.8</v>
       </c>
       <c r="R161">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S161">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T161">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U161">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V161">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W161">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X161">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y161">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z161">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AA161">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB161">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AC161">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AD161">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE161">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF161">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG161">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK161">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27539,7 +27539,7 @@
         <v>0</v>
       </c>
       <c r="Q167">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="R167">
         <v>2.1</v>
@@ -27548,25 +27548,25 @@
         <v>1.4</v>
       </c>
       <c r="T167">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U167">
         <v>2.88</v>
       </c>
       <c r="V167">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W167">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X167">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y167">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z167">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AA167">
         <v>1.98</v>
@@ -27575,7 +27575,7 @@
         <v>1.76</v>
       </c>
       <c r="AC167">
-        <v>3.28</v>
+        <v>3.39</v>
       </c>
       <c r="AD167">
         <v>1.29</v>
@@ -27584,10 +27584,10 @@
         <v>1.06</v>
       </c>
       <c r="AF167">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG167">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK167">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="O168">
         <v>3.2</v>
       </c>
       <c r="P168">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="Q168">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R168">
         <v>2.1</v>
       </c>
       <c r="S168">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T168">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="U168">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V168">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W168">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X168">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z168">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA168">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB168">
         <v>1.85</v>
       </c>
       <c r="AC168">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD168">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE168">
         <v>1.06</v>
       </c>
       <c r="AF168">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG168">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK168">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="O169">
         <v>3.2</v>
       </c>
       <c r="P169">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="Q169">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R169">
         <v>2.1</v>
       </c>
       <c r="S169">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T169">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U169">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V169">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W169">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X169">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y169">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z169">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA169">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB169">
         <v>1.85</v>
       </c>
       <c r="AC169">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD169">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE169">
         <v>1.06</v>
       </c>
       <c r="AF169">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG169">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK169">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28182,31 +28182,31 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="O171">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="P171">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q171">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R171">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="S171">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T171">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U171">
         <v>2.28</v>
       </c>
       <c r="V171">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W171">
         <v>1.09</v>
@@ -28221,16 +28221,16 @@
         <v>4.75</v>
       </c>
       <c r="AA171">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB171">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC171">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AD171">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AE171">
         <v>1.2</v>
@@ -28239,7 +28239,7 @@
         <v>1.53</v>
       </c>
       <c r="AG171">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK171">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="O172">
         <v>3.13</v>
       </c>
       <c r="P172">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O174">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="P174">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q174">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R174">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S174">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T174">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U174">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V174">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W174">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y174">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z174">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB174">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AC174">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD174">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE174">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF174">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG174">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK174">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="O175">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="P175">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA175">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB175">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -30470,7 +30470,7 @@
         <v>3.5</v>
       </c>
       <c r="P185">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="Q185">
         <v>2.25</v>
@@ -30488,13 +30488,13 @@
         <v>2.8</v>
       </c>
       <c r="V185">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W185">
         <v>1.05</v>
       </c>
       <c r="X185">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y185">
         <v>1.26</v>
@@ -30506,13 +30506,13 @@
         <v>2.05</v>
       </c>
       <c r="AB185">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC185">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="AD185">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE185">
         <v>1.07</v>
@@ -30642,10 +30642,10 @@
         <v>2.1</v>
       </c>
       <c r="S186">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T186">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="U186">
         <v>2.88</v>
@@ -30654,7 +30654,7 @@
         <v>1.36</v>
       </c>
       <c r="W186">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X186">
         <v>1.01</v>
@@ -30663,7 +30663,7 @@
         <v>1.31</v>
       </c>
       <c r="Z186">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AA186">
         <v>1.89</v>
@@ -30672,7 +30672,7 @@
         <v>1.92</v>
       </c>
       <c r="AC186">
-        <v>3.41</v>
+        <v>3.12</v>
       </c>
       <c r="AD186">
         <v>1.28</v>
@@ -30684,7 +30684,7 @@
         <v>1.75</v>
       </c>
       <c r="AG186">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>1.26</v>
       </c>
       <c r="AK186">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="O196">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="P196">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="Q196">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
       <c r="R196">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="S196">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="T196">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="U196">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="V196">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="W196">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="X196">
         <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z196">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AA196">
+        <v>1.21</v>
+      </c>
+      <c r="AB196">
+        <v>4.2</v>
+      </c>
+      <c r="AC196">
         <v>1.58</v>
       </c>
-      <c r="AB196">
-        <v>2.34</v>
-      </c>
-      <c r="AC196">
-        <v>2.45</v>
-      </c>
       <c r="AD196">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AE196">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="AF196">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AG196">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AK196">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="O197">
-        <v>11.9</v>
+        <v>4.6</v>
       </c>
       <c r="P197">
-        <v>13</v>
+        <v>6.16</v>
       </c>
       <c r="Q197">
-        <v>1.35</v>
+        <v>1.93</v>
       </c>
       <c r="R197">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="S197">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="T197">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="U197">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="V197">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="W197">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="X197">
         <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="Z197">
-        <v>9.1</v>
+        <v>4.75</v>
       </c>
       <c r="AA197">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AB197">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC197">
-        <v>1.58</v>
+        <v>2.55</v>
       </c>
       <c r="AD197">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="AE197">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="AF197">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG197">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AK197">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="O200">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="P200">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q200">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R200">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S200">
+        <v>0</v>
+      </c>
+      <c r="T200">
+        <v>0</v>
+      </c>
+      <c r="U200">
+        <v>0</v>
+      </c>
+      <c r="V200">
+        <v>0</v>
+      </c>
+      <c r="W200">
+        <v>0</v>
+      </c>
+      <c r="X200">
+        <v>0</v>
+      </c>
+      <c r="Y200">
         <v>1.66</v>
       </c>
-      <c r="T200">
-        <v>2.28</v>
-      </c>
-      <c r="U200">
-        <v>4.1</v>
-      </c>
-      <c r="V200">
-        <v>1.16</v>
-      </c>
-      <c r="W200">
-        <v>1.03</v>
-      </c>
-      <c r="X200">
-        <v>1.13</v>
-      </c>
-      <c r="Y200">
-        <v>1.61</v>
-      </c>
       <c r="Z200">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AA200">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB200">
         <v>1.33</v>
       </c>
       <c r="AC200">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="AD200">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE200">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF200">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AG200">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK200">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="O201">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="P201">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X201">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y201">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="Z201">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AA201">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB201">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G202">
@@ -33238,28 +33238,28 @@
         <v>1.88</v>
       </c>
       <c r="O202">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P202">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="Q202">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R202">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="S202">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="T202">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U202">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="V202">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W202">
         <v>1.03</v>
@@ -33268,31 +33268,31 @@
         <v>1.13</v>
       </c>
       <c r="Y202">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z202">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA202">
         <v>3.1</v>
       </c>
       <c r="AB202">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC202">
-        <v>5.45</v>
+        <v>6.09</v>
       </c>
       <c r="AD202">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE202">
         <v>1.03</v>
       </c>
       <c r="AF202">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AG202">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AK202">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O216">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P216">
-        <v>4.81</v>
+        <v>4.86</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35683,7 +35683,7 @@
         <v>7</v>
       </c>
       <c r="O217">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="P217">
         <v>1.4</v>
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O218">
         <v>3.1</v>
       </c>
       <c r="P218">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O226">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P226">
-        <v>4.26</v>
+        <v>3.6</v>
       </c>
       <c r="Q226">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R226">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S226">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T226">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="U226">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="V226">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="W226">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X226">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y226">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Z226">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AA226">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AB226">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC226">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="AD226">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE226">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF226">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AG226">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK226">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="O227">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="P227">
+        <v>4.26</v>
+      </c>
+      <c r="Q227">
+        <v>2.5</v>
+      </c>
+      <c r="R227">
+        <v>1.95</v>
+      </c>
+      <c r="S227">
+        <v>1.48</v>
+      </c>
+      <c r="T227">
+        <v>2.48</v>
+      </c>
+      <c r="U227">
         <v>3.6</v>
       </c>
-      <c r="Q227">
-        <v>3</v>
-      </c>
-      <c r="R227">
-        <v>1.85</v>
-      </c>
-      <c r="S227">
-        <v>1.55</v>
-      </c>
-      <c r="T227">
-        <v>2.25</v>
-      </c>
-      <c r="U227">
-        <v>3.8</v>
-      </c>
       <c r="V227">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W227">
         <v>1.03</v>
       </c>
       <c r="X227">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Y227">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="Z227">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="AA227">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB227">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AC227">
-        <v>6.5</v>
+        <v>4.85</v>
       </c>
       <c r="AD227">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE227">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF227">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG227">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK227">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="O228">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P228">
         <v>3.6</v>
       </c>
       <c r="Q228">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="R228">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S228">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="T228">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="U228">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="V228">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W228">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X228">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y228">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="Z228">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="AA228">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="AB228">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AC228">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AD228">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AE228">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF228">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AG228">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK228">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37962,16 +37962,16 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O231">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="P231">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="Q231">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="R231">
         <v>2.15</v>
@@ -37998,13 +37998,13 @@
         <v>1.3</v>
       </c>
       <c r="Z231">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA231">
         <v>1.95</v>
       </c>
       <c r="AB231">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC231">
         <v>2.89</v>
@@ -38019,7 +38019,7 @@
         <v>1.85</v>
       </c>
       <c r="AG231">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,65 +39918,65 @@
         </is>
       </c>
       <c r="N243">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="O243">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="P243">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q243">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R243">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S243">
+        <v>1.62</v>
+      </c>
+      <c r="T243">
+        <v>2.04</v>
+      </c>
+      <c r="U243">
+        <v>4</v>
+      </c>
+      <c r="V243">
+        <v>1.2</v>
+      </c>
+      <c r="W243">
+        <v>1.03</v>
+      </c>
+      <c r="X243">
+        <v>1.1</v>
+      </c>
+      <c r="Y243">
+        <v>1.72</v>
+      </c>
+      <c r="Z243">
+        <v>2.25</v>
+      </c>
+      <c r="AA243">
+        <v>3.08</v>
+      </c>
+      <c r="AB243">
+        <v>1.33</v>
+      </c>
+      <c r="AC243">
+        <v>5.2</v>
+      </c>
+      <c r="AD243">
+        <v>1.11</v>
+      </c>
+      <c r="AE243">
+        <v>1.02</v>
+      </c>
+      <c r="AF243">
+        <v>2.33</v>
+      </c>
+      <c r="AG243">
         <v>1.5</v>
       </c>
-      <c r="T243">
-        <v>2.52</v>
-      </c>
-      <c r="U243">
-        <v>3.32</v>
-      </c>
-      <c r="V243">
-        <v>1.26</v>
-      </c>
-      <c r="W243">
-        <v>1.05</v>
-      </c>
-      <c r="X243">
-        <v>1.03</v>
-      </c>
-      <c r="Y243">
-        <v>1.38</v>
-      </c>
-      <c r="Z243">
-        <v>2.75</v>
-      </c>
-      <c r="AA243">
-        <v>2.35</v>
-      </c>
-      <c r="AB243">
-        <v>1.55</v>
-      </c>
-      <c r="AC243">
-        <v>4.3</v>
-      </c>
-      <c r="AD243">
-        <v>1.17</v>
-      </c>
-      <c r="AE243">
-        <v>1</v>
-      </c>
-      <c r="AF243">
-        <v>2.23</v>
-      </c>
-      <c r="AG243">
-        <v>1.57</v>
-      </c>
       <c r="AH243" t="inlineStr">
         <is>
           <t>[]</t>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK243">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,80 +40081,80 @@
         </is>
       </c>
       <c r="N244">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="O244">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="P244">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q244">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R244">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S244">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="T244">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="U244">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="V244">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="W244">
+        <v>1.05</v>
+      </c>
+      <c r="X244">
         <v>1.03</v>
       </c>
-      <c r="X244">
-        <v>1.1</v>
-      </c>
       <c r="Y244">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="Z244">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA244">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="AB244">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AC244">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD244">
+        <v>1.17</v>
+      </c>
+      <c r="AE244">
+        <v>1</v>
+      </c>
+      <c r="AF244">
+        <v>2.23</v>
+      </c>
+      <c r="AG244">
+        <v>1.57</v>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ244">
         <v>1.11</v>
       </c>
-      <c r="AE244">
-        <v>1.02</v>
-      </c>
-      <c r="AF244">
-        <v>2.33</v>
-      </c>
-      <c r="AG244">
-        <v>1.5</v>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ244">
-        <v>1.13</v>
-      </c>
       <c r="AK244">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -42538,10 +42538,10 @@
         <v>2.92</v>
       </c>
       <c r="R259">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S259">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T259">
         <v>2.91</v>
@@ -42562,13 +42562,13 @@
         <v>1.23</v>
       </c>
       <c r="Z259">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA259">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB259">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC259">
         <v>2.92</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="O269">
-        <v>4.39</v>
+        <v>5.18</v>
       </c>
       <c r="P269">
-        <v>4.28</v>
+        <v>5.2</v>
       </c>
       <c r="Q269">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="R269">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="S269">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T269">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
       <c r="U269">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="V269">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="W269">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X269">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y269">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z269">
-        <v>5</v>
+        <v>5.58</v>
       </c>
       <c r="AA269">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AB269">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC269">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="AD269">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AE269">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AF269">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG269">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK269">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="O270">
-        <v>5.18</v>
+        <v>4.39</v>
       </c>
       <c r="P270">
-        <v>5.2</v>
+        <v>4.28</v>
       </c>
       <c r="Q270">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="R270">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="S270">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T270">
-        <v>4.1</v>
+        <v>3.22</v>
       </c>
       <c r="U270">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="V270">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="W270">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X270">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y270">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z270">
-        <v>5.58</v>
+        <v>5</v>
       </c>
       <c r="AA270">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AB270">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC270">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="AD270">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AE270">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AF270">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG270">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK270">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AL270">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -804,7 +804,7 @@
         <v>3.8</v>
       </c>
       <c r="P3">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q3">
         <v>2.33</v>
@@ -843,10 +843,10 @@
         <v>2.53</v>
       </c>
       <c r="AC3">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE3">
         <v>1.22</v>
@@ -855,7 +855,7 @@
         <v>1.41</v>
       </c>
       <c r="AG3">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -976,19 +976,19 @@
         <v>2.4</v>
       </c>
       <c r="S4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T4">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="U4">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
         <v>1.63</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1003,19 +1003,19 @@
         <v>1.4</v>
       </c>
       <c r="AB4">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC4">
         <v>2.1</v>
       </c>
       <c r="AD4">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE4">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG4">
         <v>2.29</v>
@@ -1034,7 +1034,7 @@
         <v>1.13</v>
       </c>
       <c r="AK4">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,65 +1124,65 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.41</v>
+        <v>4.75</v>
       </c>
       <c r="O5">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>2.62</v>
+        <v>1.52</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R5">
+        <v>2.24</v>
+      </c>
+      <c r="S5">
+        <v>1.32</v>
+      </c>
+      <c r="T5">
+        <v>3.04</v>
+      </c>
+      <c r="U5">
+        <v>2.47</v>
+      </c>
+      <c r="V5">
+        <v>1.44</v>
+      </c>
+      <c r="W5">
+        <v>1.07</v>
+      </c>
+      <c r="X5">
+        <v>1.03</v>
+      </c>
+      <c r="Y5">
+        <v>1.19</v>
+      </c>
+      <c r="Z5">
+        <v>3.85</v>
+      </c>
+      <c r="AA5">
+        <v>1.65</v>
+      </c>
+      <c r="AB5">
+        <v>2.01</v>
+      </c>
+      <c r="AC5">
+        <v>2.7</v>
+      </c>
+      <c r="AD5">
+        <v>1.36</v>
+      </c>
+      <c r="AE5">
+        <v>1.11</v>
+      </c>
+      <c r="AF5">
+        <v>1.65</v>
+      </c>
+      <c r="AG5">
         <v>2.06</v>
       </c>
-      <c r="S5">
-        <v>1.37</v>
-      </c>
-      <c r="T5">
-        <v>2.75</v>
-      </c>
-      <c r="U5">
-        <v>2.71</v>
-      </c>
-      <c r="V5">
-        <v>1.37</v>
-      </c>
-      <c r="W5">
-        <v>1.08</v>
-      </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <v>1.2</v>
-      </c>
-      <c r="Z5">
-        <v>3.7</v>
-      </c>
-      <c r="AA5">
-        <v>1.9</v>
-      </c>
-      <c r="AB5">
-        <v>1.86</v>
-      </c>
-      <c r="AC5">
-        <v>3.08</v>
-      </c>
-      <c r="AD5">
-        <v>1.28</v>
-      </c>
-      <c r="AE5">
-        <v>1.07</v>
-      </c>
-      <c r="AF5">
-        <v>1.67</v>
-      </c>
-      <c r="AG5">
-        <v>2.05</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK5">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.75</v>
+        <v>2.41</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="S6">
+        <v>1.37</v>
+      </c>
+      <c r="T6">
+        <v>2.87</v>
+      </c>
+      <c r="U6">
+        <v>2.71</v>
+      </c>
+      <c r="V6">
+        <v>1.37</v>
+      </c>
+      <c r="W6">
+        <v>1.04</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.2</v>
+      </c>
+      <c r="Z6">
+        <v>3.7</v>
+      </c>
+      <c r="AA6">
+        <v>1.68</v>
+      </c>
+      <c r="AB6">
+        <v>1.83</v>
+      </c>
+      <c r="AC6">
+        <v>3.3</v>
+      </c>
+      <c r="AD6">
         <v>1.3</v>
       </c>
-      <c r="T6">
-        <v>3.04</v>
-      </c>
-      <c r="U6">
-        <v>2.47</v>
-      </c>
-      <c r="V6">
-        <v>1.44</v>
-      </c>
-      <c r="W6">
+      <c r="AE6">
         <v>1.07</v>
       </c>
-      <c r="X6">
-        <v>1.03</v>
-      </c>
-      <c r="Y6">
-        <v>1.19</v>
-      </c>
-      <c r="Z6">
-        <v>3.85</v>
-      </c>
-      <c r="AA6">
-        <v>1.65</v>
-      </c>
-      <c r="AB6">
-        <v>2</v>
-      </c>
-      <c r="AC6">
-        <v>2.7</v>
-      </c>
-      <c r="AD6">
-        <v>1.38</v>
-      </c>
-      <c r="AE6">
-        <v>1.11</v>
-      </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>2.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q10">
         <v>3.2</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T10">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
         <v>1.04</v>
@@ -1972,19 +1972,19 @@
         <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
         <v>2.99</v>
       </c>
       <c r="AA10">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB10">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="AD10">
         <v>1.28</v>
@@ -1996,7 +1996,7 @@
         <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
         <v>1.4</v>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="Q11">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S11">
         <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
         <v>2.8</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
         <v>1.03</v>
@@ -2135,31 +2135,31 @@
         <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AA11">
         <v>1.94</v>
       </c>
       <c r="AB11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AD11">
         <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>2.9</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S13">
         <v>1.41</v>
       </c>
       <c r="T13">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="U13">
         <v>2.89</v>
@@ -2455,13 +2455,13 @@
         <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
         <v>3.18</v>
@@ -2470,16 +2470,16 @@
         <v>1.98</v>
       </c>
       <c r="AB13">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC13">
         <v>3.3</v>
       </c>
       <c r="AD13">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
         <v>1.73</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK13">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,13 +2594,13 @@
         <v>2.1</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q14">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R14">
         <v>2</v>
@@ -2609,13 +2609,13 @@
         <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="U14">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
         <v>1.01</v>
@@ -2633,13 +2633,13 @@
         <v>2.13</v>
       </c>
       <c r="AB14">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC14">
         <v>3.74</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
@@ -2648,7 +2648,7 @@
         <v>1.83</v>
       </c>
       <c r="AG14">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -3910,28 +3910,28 @@
         <v>2.05</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T22">
         <v>2.56</v>
       </c>
       <c r="U22">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="V22">
         <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z22">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AA22">
         <v>2.13</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
         <v>2.7</v>
@@ -4076,10 +4076,10 @@
         <v>1.38</v>
       </c>
       <c r="T23">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U23">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="V23">
         <v>1.37</v>
@@ -4088,28 +4088,28 @@
         <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.33</v>
       </c>
       <c r="Z23">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA23">
         <v>2</v>
       </c>
       <c r="AB23">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC23">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD23">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE23">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
         <v>1.8</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         <v>3.45</v>
       </c>
       <c r="O24">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="Q24">
         <v>4</v>
@@ -4236,34 +4236,34 @@
         <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U24">
         <v>2.75</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
         <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
         <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AA24">
         <v>1.85</v>
       </c>
       <c r="AB24">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
         <v>3.05</v>
@@ -4272,7 +4272,7 @@
         <v>1.34</v>
       </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
         <v>1.73</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AK24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="O25">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q25">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="R25">
         <v>2.02</v>
@@ -4402,16 +4402,16 @@
         <v>1.4</v>
       </c>
       <c r="T25">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U25">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4423,10 +4423,10 @@
         <v>3.16</v>
       </c>
       <c r="AA25">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB25">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC25">
         <v>3.54</v>
@@ -4435,7 +4435,7 @@
         <v>1.22</v>
       </c>
       <c r="AE25">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
         <v>1.9</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>3.25</v>
       </c>
       <c r="P26">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q26">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R26">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="S26">
         <v>1.37</v>
@@ -4568,7 +4568,7 @@
         <v>2.77</v>
       </c>
       <c r="U26">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V26">
         <v>1.42</v>
@@ -4583,16 +4583,16 @@
         <v>1.23</v>
       </c>
       <c r="Z26">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AA26">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB26">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AD26">
         <v>1.32</v>
@@ -4601,10 +4601,10 @@
         <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,65 +5525,65 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q32">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="R32">
         <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U32">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Z32">
         <v>3.4</v>
       </c>
       <c r="AA32">
+        <v>1.79</v>
+      </c>
+      <c r="AB32">
+        <v>1.84</v>
+      </c>
+      <c r="AC32">
+        <v>3.25</v>
+      </c>
+      <c r="AD32">
+        <v>1.3</v>
+      </c>
+      <c r="AE32">
+        <v>1.1</v>
+      </c>
+      <c r="AF32">
+        <v>1.67</v>
+      </c>
+      <c r="AG32">
         <v>2</v>
       </c>
-      <c r="AB32">
-        <v>1.8</v>
-      </c>
-      <c r="AC32">
-        <v>3.5</v>
-      </c>
-      <c r="AD32">
-        <v>1.25</v>
-      </c>
-      <c r="AE32">
-        <v>1.08</v>
-      </c>
-      <c r="AF32">
-        <v>1.8</v>
-      </c>
-      <c r="AG32">
-        <v>1.91</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK32">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.04</v>
+        <v>3.32</v>
       </c>
       <c r="O33">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="Q33">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>4.23</v>
+        <v>3.4</v>
       </c>
       <c r="AA33">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB33">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AC33">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD33">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="O34">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
+        <v>3.1</v>
+      </c>
+      <c r="Q34">
         <v>2.6</v>
       </c>
-      <c r="Q34">
-        <v>3</v>
-      </c>
       <c r="R34">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="V34">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>3.4</v>
+        <v>4.23</v>
       </c>
       <c r="AA34">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="AC34">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AD34">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="O201">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P201">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q201">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="R201">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="S201">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="T201">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="U201">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V201">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="W201">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X201">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y201">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Z201">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="AA201">
-        <v>2.58</v>
+        <v>2.83</v>
       </c>
       <c r="AB201">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AC201">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AD201">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE201">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF201">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AG201">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK201">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="O202">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P202">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q202">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="R202">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="S202">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="T202">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="U202">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V202">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W202">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X202">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y202">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Z202">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="AA202">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="AB202">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AC202">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AD202">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE202">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF202">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AG202">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK202">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AL202">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O27">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="Q27">
         <v>2.7</v>
@@ -4725,13 +4725,13 @@
         <v>2</v>
       </c>
       <c r="S27">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="U27">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="V27">
         <v>1.32</v>
@@ -4740,7 +4740,7 @@
         <v>1.01</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
         <v>1.33</v>
@@ -4758,10 +4758,10 @@
         <v>3.88</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
         <v>1.85</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.32</v>
+        <v>2.04</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="Q33">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.96</v>
+        <v>2.44</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.4</v>
+        <v>4.23</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB33">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AC33">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG33">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.04</v>
+        <v>3.32</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P34">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="Q34">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z34">
-        <v>4.23</v>
+        <v>3.4</v>
       </c>
       <c r="AA34">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD34">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6204,28 +6204,28 @@
         <v>1.57</v>
       </c>
       <c r="W36">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.12</v>
       </c>
       <c r="Z36">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA36">
         <v>1.57</v>
       </c>
       <c r="AB36">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC36">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AD36">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE36">
         <v>1.22</v>
@@ -6234,7 +6234,7 @@
         <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="O43">
-        <v>3.51</v>
+        <v>3.46</v>
       </c>
       <c r="P43">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q43">
         <v>3.04</v>
@@ -7339,10 +7339,10 @@
         <v>3.04</v>
       </c>
       <c r="U43">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W43">
         <v>1.09</v>
@@ -7357,16 +7357,16 @@
         <v>3.78</v>
       </c>
       <c r="AA43">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB43">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AC43">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AD43">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE43">
         <v>1.12</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AK43">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8133,34 +8133,34 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="O48">
         <v>4.1</v>
       </c>
       <c r="P48">
-        <v>5.23</v>
+        <v>5.8</v>
       </c>
       <c r="Q48">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R48">
         <v>2.45</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T48">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U48">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V48">
         <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
         <v>1.03</v>
@@ -8172,19 +8172,19 @@
         <v>4.45</v>
       </c>
       <c r="AA48">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB48">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AC48">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD48">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
         <v>1.67</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK48">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="O52">
         <v>3.75</v>
       </c>
       <c r="P52">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q52">
         <v>3.24</v>
@@ -8809,7 +8809,7 @@
         <v>2</v>
       </c>
       <c r="V52">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W52">
         <v>1.16</v>
@@ -8821,7 +8821,7 @@
         <v>1.08</v>
       </c>
       <c r="Z52">
-        <v>6.22</v>
+        <v>6.23</v>
       </c>
       <c r="AA52">
         <v>1.42</v>
@@ -8833,16 +8833,16 @@
         <v>1.95</v>
       </c>
       <c r="AD52">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AE52">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF52">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG52">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK52">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,22 +8948,22 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O53">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q53">
         <v>3.8</v>
       </c>
       <c r="R53">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S53">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
         <v>3.1</v>
@@ -8984,13 +8984,13 @@
         <v>1.25</v>
       </c>
       <c r="Z53">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA53">
         <v>1.84</v>
       </c>
       <c r="AB53">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC53">
         <v>2.78</v>
@@ -9002,10 +9002,10 @@
         <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG53">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>2.45</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S54">
         <v>1.18</v>
@@ -9135,7 +9135,7 @@
         <v>1.94</v>
       </c>
       <c r="V54">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W54">
         <v>1.2</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
         <v>1.7</v>
@@ -9286,7 +9286,7 @@
         <v>2.25</v>
       </c>
       <c r="R55">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S55">
         <v>1.2</v>
@@ -9295,10 +9295,10 @@
         <v>3.95</v>
       </c>
       <c r="U55">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="V55">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W55">
         <v>1.14</v>
@@ -9307,25 +9307,25 @@
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z55">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA55">
         <v>1.42</v>
       </c>
       <c r="AB55">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AC55">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD55">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE55">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF55">
         <v>1.41</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="O66">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P66">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="Q66">
         <v>3.1</v>
@@ -11085,7 +11085,7 @@
         <v>1.58</v>
       </c>
       <c r="T66">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="U66">
         <v>3.8</v>
@@ -11094,22 +11094,22 @@
         <v>1.22</v>
       </c>
       <c r="W66">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
         <v>1.07</v>
       </c>
       <c r="Y66">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Z66">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA66">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AB66">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC66">
         <v>4.9</v>
@@ -11121,7 +11121,7 @@
         <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AG66">
         <v>1.62</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK66">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,28 +11230,28 @@
         </is>
       </c>
       <c r="N67">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O67">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q67">
-        <v>5.29</v>
+        <v>4.8</v>
       </c>
       <c r="R67">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S67">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T67">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="U67">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V67">
         <v>1.33</v>
@@ -11260,25 +11260,25 @@
         <v>1.01</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y67">
         <v>1.4</v>
       </c>
       <c r="Z67">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA67">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB67">
         <v>1.57</v>
       </c>
       <c r="AC67">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD67">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE67">
         <v>1.06</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK67">
         <v>1.2</v>
@@ -12697,16 +12697,16 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="O76">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P76">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="Q76">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R76">
         <v>2.31</v>
@@ -12718,10 +12718,10 @@
         <v>3.02</v>
       </c>
       <c r="U76">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V76">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W76">
         <v>1.05</v>
@@ -12736,19 +12736,19 @@
         <v>3.44</v>
       </c>
       <c r="AA76">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB76">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC76">
         <v>3.2</v>
       </c>
       <c r="AD76">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE76">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF76">
         <v>2.06</v>
@@ -12770,7 +12770,7 @@
         <v>1.05</v>
       </c>
       <c r="AK76">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,58 +12860,58 @@
         </is>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O77">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P77">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q77">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="R77">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U77">
         <v>2.45</v>
       </c>
       <c r="V77">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W77">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
         <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AA77">
         <v>1.7</v>
       </c>
       <c r="AB77">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC77">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AD77">
         <v>1.4</v>
       </c>
       <c r="AE77">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
         <v>1.62</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.84</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,40 +13032,40 @@
         <v>2.4</v>
       </c>
       <c r="Q78">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R78">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.09</v>
+        <v>2.91</v>
       </c>
       <c r="U78">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="V78">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W78">
         <v>1.11</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
         <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="AA78">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB78">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC78">
         <v>2.7</v>
@@ -13077,7 +13077,7 @@
         <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG78">
         <v>2.25</v>
@@ -13096,7 +13096,7 @@
         <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,22 +13186,22 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="O79">
         <v>3.3</v>
       </c>
       <c r="P79">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q79">
         <v>2.88</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S79">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T79">
         <v>3</v>
@@ -13210,7 +13210,7 @@
         <v>2.56</v>
       </c>
       <c r="V79">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W79">
         <v>1.06</v>
@@ -13222,19 +13222,19 @@
         <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AA79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB79">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC79">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD79">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE79">
         <v>1.1</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK79">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -19552,49 +19552,49 @@
         <v>1.75</v>
       </c>
       <c r="Q118">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="R118">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S118">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T118">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U118">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V118">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W118">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X118">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z118">
         <v>4.33</v>
       </c>
       <c r="AA118">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB118">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC118">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AD118">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE118">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF118">
         <v>1.57</v>
@@ -19616,7 +19616,7 @@
         <v>1.22</v>
       </c>
       <c r="AK118">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20358,10 +20358,10 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O123">
-        <v>5.4</v>
+        <v>5.32</v>
       </c>
       <c r="P123">
         <v>8.75</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="O124">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="P124">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="Q124">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="R124">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S124">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T124">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U124">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="V124">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W124">
         <v>1.04</v>
       </c>
       <c r="X124">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y124">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z124">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA124">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AB124">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AC124">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD124">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF124">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG124">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK124">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21499,34 +21499,34 @@
         </is>
       </c>
       <c r="N130">
-        <v>4.4</v>
+        <v>4.86</v>
       </c>
       <c r="O130">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P130">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Q130">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="R130">
         <v>2.6</v>
       </c>
       <c r="S130">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T130">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U130">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V130">
         <v>1.7</v>
       </c>
       <c r="W130">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X130">
         <v>1.02</v>
@@ -21535,28 +21535,28 @@
         <v>1.13</v>
       </c>
       <c r="Z130">
-        <v>5.66</v>
+        <v>5.5</v>
       </c>
       <c r="AA130">
         <v>1.44</v>
       </c>
       <c r="AB130">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC130">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AD130">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE130">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF130">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AG130">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>1.22</v>
       </c>
       <c r="AK130">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21665,61 +21665,61 @@
         <v>1.36</v>
       </c>
       <c r="O131">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="P131">
-        <v>7.6</v>
+        <v>6.89</v>
       </c>
       <c r="Q131">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R131">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="S131">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T131">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U131">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="V131">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W131">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X131">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y131">
         <v>1.15</v>
       </c>
       <c r="Z131">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="AA131">
         <v>1.5</v>
       </c>
       <c r="AB131">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AC131">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD131">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE131">
         <v>1.22</v>
       </c>
       <c r="AF131">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG131">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK131">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="O134">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P134">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22190,10 +22190,10 @@
         <v>0</v>
       </c>
       <c r="AA134">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB134">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC134">
         <v>0</v>
@@ -23319,16 +23319,16 @@
         <v>1.39</v>
       </c>
       <c r="W141">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X141">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y141">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z141">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA141">
         <v>1.8</v>
@@ -23340,7 +23340,7 @@
         <v>2.97</v>
       </c>
       <c r="AD141">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE141">
         <v>1.08</v>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK141">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23784,28 +23784,28 @@
         <v>2.3</v>
       </c>
       <c r="O144">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P144">
         <v>3.1</v>
       </c>
       <c r="Q144">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R144">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S144">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="T144">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U144">
         <v>3.8</v>
       </c>
       <c r="V144">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W144">
         <v>1.02</v>
@@ -23832,7 +23832,7 @@
         <v>1.08</v>
       </c>
       <c r="AE144">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF144">
         <v>2.15</v>
@@ -23851,7 +23851,7 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AK144">
         <v>1.53</v>
@@ -24596,22 +24596,22 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="O149">
         <v>3.05</v>
       </c>
       <c r="P149">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q149">
         <v>2.94</v>
       </c>
       <c r="R149">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S149">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="T149">
         <v>2.33</v>
@@ -24626,34 +24626,34 @@
         <v>1.01</v>
       </c>
       <c r="X149">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y149">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Z149">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="AA149">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AB149">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC149">
         <v>4.9</v>
       </c>
       <c r="AD149">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE149">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF149">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AG149">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK149">
         <v>1.72</v>
@@ -25266,7 +25266,7 @@
         <v>1.36</v>
       </c>
       <c r="T153">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U153">
         <v>2.79</v>
@@ -25302,10 +25302,10 @@
         <v>1.05</v>
       </c>
       <c r="AF153">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG153">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>1.25</v>
       </c>
       <c r="AK153">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25426,7 +25426,7 @@
         <v>2.2</v>
       </c>
       <c r="S154">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
         <v>2.92</v>
@@ -25435,7 +25435,7 @@
         <v>2.63</v>
       </c>
       <c r="V154">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W154">
         <v>1.07</v>
@@ -25447,10 +25447,10 @@
         <v>1.22</v>
       </c>
       <c r="Z154">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AA154">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB154">
         <v>1.95</v>
@@ -25468,7 +25468,7 @@
         <v>1.64</v>
       </c>
       <c r="AG154">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK154">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25746,7 +25746,7 @@
         <v>3.11</v>
       </c>
       <c r="Q156">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="R156">
         <v>2</v>
@@ -25755,7 +25755,7 @@
         <v>1.44</v>
       </c>
       <c r="T156">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U156">
         <v>3.14</v>
@@ -25764,34 +25764,34 @@
         <v>1.28</v>
       </c>
       <c r="W156">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X156">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z156">
         <v>2.88</v>
       </c>
       <c r="AA156">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AB156">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC156">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AD156">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE156">
         <v>1.02</v>
       </c>
       <c r="AF156">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG156">
         <v>1.74</v>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK156">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25909,7 +25909,7 @@
         <v>2.88</v>
       </c>
       <c r="Q157">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="R157">
         <v>2</v>
@@ -25918,13 +25918,13 @@
         <v>1.4</v>
       </c>
       <c r="T157">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U157">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="V157">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W157">
         <v>1.06</v>
@@ -25933,22 +25933,22 @@
         <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z157">
         <v>2.92</v>
       </c>
       <c r="AA157">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AB157">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC157">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD157">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE157">
         <v>1.05</v>
@@ -25970,7 +25970,7 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK157">
         <v>1.53</v>
@@ -26078,16 +26078,16 @@
         <v>2.3</v>
       </c>
       <c r="S158">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T158">
-        <v>2.92</v>
+        <v>2.42</v>
       </c>
       <c r="U158">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="V158">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W158">
         <v>1.1</v>
@@ -26099,7 +26099,7 @@
         <v>1.19</v>
       </c>
       <c r="Z158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA158">
         <v>1.65</v>
@@ -26117,10 +26117,10 @@
         <v>1.11</v>
       </c>
       <c r="AF158">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG158">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK158">
         <v>2.04</v>
@@ -26226,22 +26226,22 @@
         </is>
       </c>
       <c r="N159">
-        <v>3.98</v>
+        <v>3.51</v>
       </c>
       <c r="O159">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P159">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q159">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="R159">
         <v>2.2</v>
       </c>
       <c r="S159">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T159">
         <v>3.3</v>
@@ -26259,22 +26259,22 @@
         <v>1.05</v>
       </c>
       <c r="Y159">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z159">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AA159">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB159">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC159">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AD159">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE159">
         <v>1.14</v>
@@ -26283,7 +26283,7 @@
         <v>1.7</v>
       </c>
       <c r="AG159">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK159">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26389,10 +26389,10 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O160">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="P160">
         <v>2.85</v>
@@ -26401,13 +26401,13 @@
         <v>2.8</v>
       </c>
       <c r="R160">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S160">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T160">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U160">
         <v>2.75</v>
@@ -26422,10 +26422,10 @@
         <v>1.05</v>
       </c>
       <c r="Y160">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z160">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA160">
         <v>1.9</v>
@@ -26437,16 +26437,16 @@
         <v>2.8</v>
       </c>
       <c r="AD160">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE160">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF160">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG160">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26887,55 +26887,55 @@
         <v>0</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O164">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P164">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="V164">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X164">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y164">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z164">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK164">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27213,55 +27213,55 @@
         <v>0</v>
       </c>
       <c r="Q165">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="R165">
         <v>2.1</v>
       </c>
       <c r="S165">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T165">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="U165">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="V165">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W165">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X165">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y165">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z165">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA165">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB165">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC165">
-        <v>3.39</v>
+        <v>3.5</v>
       </c>
       <c r="AD165">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE165">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF165">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG165">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK165">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27376,40 +27376,40 @@
         <v>2.13</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W166">
         <v>0</v>
       </c>
       <c r="X166">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC166">
         <v>0</v>
@@ -27421,10 +27421,10 @@
         <v>0</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27699,19 +27699,19 @@
         <v>3.2</v>
       </c>
       <c r="P168">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q168">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R168">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S168">
         <v>1.4</v>
       </c>
       <c r="T168">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U168">
         <v>2.86</v>
@@ -27720,28 +27720,28 @@
         <v>1.33</v>
       </c>
       <c r="W168">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X168">
         <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z168">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AA168">
         <v>2</v>
       </c>
       <c r="AB168">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC168">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD168">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE168">
         <v>1.06</v>
@@ -27763,7 +27763,7 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK168">
         <v>1.7</v>
@@ -27856,58 +27856,58 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="O169">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P169">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="Q169">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="R169">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S169">
         <v>1.36</v>
       </c>
       <c r="T169">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="U169">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V169">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W169">
         <v>1.08</v>
       </c>
       <c r="X169">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y169">
         <v>1.3</v>
       </c>
       <c r="Z169">
+        <v>3.25</v>
+      </c>
+      <c r="AA169">
+        <v>1.91</v>
+      </c>
+      <c r="AB169">
+        <v>1.78</v>
+      </c>
+      <c r="AC169">
         <v>3.2</v>
       </c>
-      <c r="AA169">
-        <v>1.95</v>
-      </c>
-      <c r="AB169">
-        <v>1.75</v>
-      </c>
-      <c r="AC169">
-        <v>3.4</v>
-      </c>
       <c r="AD169">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE169">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF169">
         <v>1.7</v>
@@ -28182,10 +28182,10 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O171">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P171">
         <v>3.8</v>
@@ -28194,19 +28194,19 @@
         <v>2.4</v>
       </c>
       <c r="R171">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="S171">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T171">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U171">
         <v>2.28</v>
       </c>
       <c r="V171">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W171">
         <v>1.09</v>
@@ -28218,7 +28218,7 @@
         <v>1.13</v>
       </c>
       <c r="Z171">
-        <v>4.75</v>
+        <v>4.58</v>
       </c>
       <c r="AA171">
         <v>1.57</v>
@@ -28227,13 +28227,13 @@
         <v>2.2</v>
       </c>
       <c r="AC171">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD171">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE171">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF171">
         <v>1.53</v>
@@ -28252,7 +28252,7 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK171">
         <v>1.85</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="O172">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="P172">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB172">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X177">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29658,40 +29658,40 @@
         <v>1.83</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W180">
         <v>0</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC180">
         <v>0</v>
@@ -29703,10 +29703,10 @@
         <v>0</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="O181">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="P181">
-        <v>10.5</v>
+        <v>10.14</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="AA181">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AB181">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC181">
         <v>0</v>
@@ -29978,10 +29978,10 @@
         <v>2.7</v>
       </c>
       <c r="O182">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P182">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="Q182">
         <v>3</v>
@@ -29993,25 +29993,25 @@
         <v>1.25</v>
       </c>
       <c r="T182">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="U182">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V182">
         <v>1.57</v>
       </c>
       <c r="W182">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X182">
         <v>1.02</v>
       </c>
       <c r="Y182">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z182">
-        <v>4.89</v>
+        <v>4.94</v>
       </c>
       <c r="AA182">
         <v>1.62</v>
@@ -30020,16 +30020,16 @@
         <v>2.36</v>
       </c>
       <c r="AC182">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AD182">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE182">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF182">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG182">
         <v>2.5</v>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AK182">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30627,19 +30627,19 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O186">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P186">
-        <v>4.33</v>
+        <v>4.78</v>
       </c>
       <c r="Q186">
         <v>2.25</v>
       </c>
       <c r="R186">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S186">
         <v>1.37</v>
@@ -30651,40 +30651,40 @@
         <v>2.8</v>
       </c>
       <c r="V186">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W186">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X186">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y186">
         <v>1.26</v>
       </c>
       <c r="Z186">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AA186">
         <v>2.05</v>
       </c>
       <c r="AB186">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC186">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AD186">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE186">
         <v>1.07</v>
       </c>
       <c r="AF186">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG186">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK186">
         <v>2.05</v>
@@ -30799,55 +30799,55 @@
         <v>0</v>
       </c>
       <c r="Q187">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R187">
         <v>2.1</v>
       </c>
       <c r="S187">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T187">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U187">
         <v>2.88</v>
       </c>
       <c r="V187">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W187">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y187">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z187">
         <v>3.35</v>
       </c>
       <c r="AA187">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB187">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AC187">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AD187">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE187">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF187">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG187">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK187">
         <v>1.8</v>
@@ -31771,10 +31771,10 @@
         <v>1.55</v>
       </c>
       <c r="O193">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="P193">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="Q193">
         <v>2.08</v>
@@ -31798,13 +31798,13 @@
         <v>1.08</v>
       </c>
       <c r="X193">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y193">
         <v>1.19</v>
       </c>
       <c r="Z193">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="AA193">
         <v>1.74</v>
@@ -31813,7 +31813,7 @@
         <v>2.1</v>
       </c>
       <c r="AC193">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="AD193">
         <v>1.39</v>
@@ -31940,34 +31940,34 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA194">
         <v>2.5</v>
@@ -31976,19 +31976,19 @@
         <v>1.5</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32103,28 +32103,28 @@
         <v>3.5</v>
       </c>
       <c r="Q195">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="R195">
         <v>1.85</v>
       </c>
       <c r="S195">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="T195">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U195">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="V195">
         <v>1.18</v>
       </c>
       <c r="W195">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X195">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y195">
         <v>1.67</v>
@@ -32142,16 +32142,16 @@
         <v>6.5</v>
       </c>
       <c r="AD195">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE195">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF195">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AG195">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32257,28 +32257,28 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="O196">
         <v>4.6</v>
       </c>
       <c r="P196">
-        <v>6.16</v>
+        <v>5.77</v>
       </c>
       <c r="Q196">
         <v>1.93</v>
       </c>
       <c r="R196">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S196">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T196">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="U196">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V196">
         <v>1.56</v>
@@ -32290,10 +32290,10 @@
         <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z196">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="AA196">
         <v>1.6</v>
@@ -32308,10 +32308,10 @@
         <v>1.53</v>
       </c>
       <c r="AE196">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF196">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG196">
         <v>1.98</v>
@@ -32330,7 +32330,7 @@
         <v>1.18</v>
       </c>
       <c r="AK196">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="O197">
         <v>10</v>
       </c>
       <c r="P197">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="Q197">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="R197">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="S197">
         <v>1.11</v>
       </c>
       <c r="T197">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="U197">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="V197">
         <v>2.05</v>
       </c>
       <c r="W197">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X197">
         <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z197">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA197">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AB197">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AC197">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AD197">
         <v>2.25</v>
       </c>
       <c r="AE197">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AF197">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG197">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK197">
         <v>6</v>
@@ -33724,16 +33724,16 @@
         </is>
       </c>
       <c r="N205">
+        <v>4.75</v>
+      </c>
+      <c r="O205">
         <v>4.5</v>
       </c>
-      <c r="O205">
-        <v>4.4</v>
-      </c>
       <c r="P205">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q205">
-        <v>4.07</v>
+        <v>4.9</v>
       </c>
       <c r="R205">
         <v>2.7</v>
@@ -33742,13 +33742,13 @@
         <v>1.19</v>
       </c>
       <c r="T205">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U205">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V205">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W205">
         <v>1.22</v>
@@ -33757,16 +33757,16 @@
         <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z205">
         <v>7</v>
       </c>
       <c r="AA205">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AB205">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AC205">
         <v>1.84</v>
@@ -33781,7 +33781,7 @@
         <v>1.4</v>
       </c>
       <c r="AG205">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33896,49 +33896,49 @@
         <v>4.24</v>
       </c>
       <c r="Q206">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="R206">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S206">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T206">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="U206">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="V206">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W206">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X206">
         <v>1.05</v>
       </c>
       <c r="Y206">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z206">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AA206">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB206">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AC206">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AD206">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE206">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF206">
         <v>1.96</v>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK206">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34382,7 +34382,7 @@
         <v>4.1</v>
       </c>
       <c r="P209">
-        <v>5.01</v>
+        <v>5.25</v>
       </c>
       <c r="Q209">
         <v>1.88</v>
@@ -34391,7 +34391,7 @@
         <v>2.4</v>
       </c>
       <c r="S209">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T209">
         <v>3.25</v>
@@ -34403,7 +34403,7 @@
         <v>1.53</v>
       </c>
       <c r="W209">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X209">
         <v>1.03</v>
@@ -34412,13 +34412,13 @@
         <v>1.18</v>
       </c>
       <c r="Z209">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA209">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB209">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="AC209">
         <v>2.49</v>
@@ -34446,7 +34446,7 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK209">
         <v>2.3</v>
@@ -34539,10 +34539,10 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="O210">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="P210">
         <v>2.55</v>
@@ -34551,49 +34551,49 @@
         <v>3</v>
       </c>
       <c r="R210">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S210">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T210">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U210">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="V210">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W210">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X210">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z210">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA210">
         <v>1.83</v>
       </c>
       <c r="AB210">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC210">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="AD210">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE210">
         <v>1.09</v>
       </c>
       <c r="AF210">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG210">
         <v>2.1</v>
@@ -34609,7 +34609,7 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AK210">
         <v>1.44</v>
@@ -34702,31 +34702,31 @@
         </is>
       </c>
       <c r="N211">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O211">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="P211">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Q211">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="R211">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S211">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T211">
         <v>3.3</v>
       </c>
       <c r="U211">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="V211">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W211">
         <v>1.08</v>
@@ -34735,31 +34735,31 @@
         <v>1.04</v>
       </c>
       <c r="Y211">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z211">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA211">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AB211">
         <v>2.14</v>
       </c>
       <c r="AC211">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AD211">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE211">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF211">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AG211">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="O213">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P213">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R213">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S213">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T213">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U213">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V213">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X213">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y213">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z213">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG213">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK213">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="O214">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P214">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O216">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P216">
-        <v>4.86</v>
+        <v>4.77</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O217">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="P217">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -36984,34 +36984,34 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="O225">
         <v>4.2</v>
       </c>
       <c r="P225">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q225">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="R225">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S225">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T225">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="U225">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="V225">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W225">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X225">
         <v>1.03</v>
@@ -37023,13 +37023,13 @@
         <v>4.95</v>
       </c>
       <c r="AA225">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB225">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AC225">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AD225">
         <v>1.6</v>
@@ -37038,10 +37038,10 @@
         <v>1.22</v>
       </c>
       <c r="AF225">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG225">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>1.2</v>
       </c>
       <c r="AK225">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37962,22 +37962,22 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O231">
-        <v>3.68</v>
+        <v>3.37</v>
       </c>
       <c r="P231">
-        <v>5.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q231">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="R231">
         <v>2.15</v>
       </c>
       <c r="S231">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T231">
         <v>2.77</v>
@@ -37992,19 +37992,19 @@
         <v>1.05</v>
       </c>
       <c r="X231">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y231">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z231">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA231">
         <v>1.95</v>
       </c>
       <c r="AB231">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC231">
         <v>2.89</v>
@@ -38016,7 +38016,7 @@
         <v>1.11</v>
       </c>
       <c r="AF231">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG231">
         <v>1.83</v>
@@ -38035,7 +38035,7 @@
         <v>1.2</v>
       </c>
       <c r="AK231">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AL231">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
+        <v>2.11</v>
+      </c>
+      <c r="O31">
         <v>3.32</v>
       </c>
-      <c r="O31">
-        <v>3.35</v>
-      </c>
       <c r="P31">
+        <v>2.8</v>
+      </c>
+      <c r="Q31">
+        <v>2.7</v>
+      </c>
+      <c r="R31">
+        <v>2.15</v>
+      </c>
+      <c r="S31">
+        <v>1.3</v>
+      </c>
+      <c r="T31">
+        <v>2.7</v>
+      </c>
+      <c r="U31">
+        <v>2.5</v>
+      </c>
+      <c r="V31">
+        <v>1.45</v>
+      </c>
+      <c r="W31">
+        <v>1.11</v>
+      </c>
+      <c r="X31">
+        <v>1.04</v>
+      </c>
+      <c r="Y31">
+        <v>1.27</v>
+      </c>
+      <c r="Z31">
+        <v>3.7</v>
+      </c>
+      <c r="AA31">
+        <v>1.81</v>
+      </c>
+      <c r="AB31">
         <v>2</v>
       </c>
-      <c r="Q31">
-        <v>3.7</v>
-      </c>
-      <c r="R31">
-        <v>2.05</v>
-      </c>
-      <c r="S31">
-        <v>1.37</v>
-      </c>
-      <c r="T31">
-        <v>2.6</v>
-      </c>
-      <c r="U31">
-        <v>2.9</v>
-      </c>
-      <c r="V31">
-        <v>1.32</v>
-      </c>
-      <c r="W31">
-        <v>1.02</v>
-      </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>1.35</v>
-      </c>
-      <c r="Z31">
-        <v>3.1</v>
-      </c>
-      <c r="AA31">
-        <v>1.95</v>
-      </c>
-      <c r="AB31">
-        <v>1.75</v>
-      </c>
       <c r="AC31">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD31">
+        <v>1.36</v>
+      </c>
+      <c r="AE31">
+        <v>1.08</v>
+      </c>
+      <c r="AF31">
+        <v>1.61</v>
+      </c>
+      <c r="AG31">
+        <v>2.1</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.25</v>
       </c>
-      <c r="AE31">
-        <v>1.03</v>
-      </c>
-      <c r="AF31">
-        <v>1.8</v>
-      </c>
-      <c r="AG31">
-        <v>1.89</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.24</v>
-      </c>
       <c r="AK31">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.4</v>
+        <v>3.32</v>
       </c>
       <c r="O32">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
+        <v>2</v>
+      </c>
+      <c r="Q32">
+        <v>3.7</v>
+      </c>
+      <c r="R32">
+        <v>2.05</v>
+      </c>
+      <c r="S32">
+        <v>1.37</v>
+      </c>
+      <c r="T32">
         <v>2.6</v>
       </c>
-      <c r="Q32">
-        <v>3</v>
-      </c>
-      <c r="R32">
-        <v>2.2</v>
-      </c>
-      <c r="S32">
-        <v>1.33</v>
-      </c>
-      <c r="T32">
-        <v>2.69</v>
-      </c>
       <c r="U32">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
+        <v>1.35</v>
+      </c>
+      <c r="Z32">
+        <v>3.1</v>
+      </c>
+      <c r="AA32">
+        <v>1.95</v>
+      </c>
+      <c r="AB32">
+        <v>1.75</v>
+      </c>
+      <c r="AC32">
+        <v>3.5</v>
+      </c>
+      <c r="AD32">
         <v>1.25</v>
       </c>
-      <c r="Z32">
-        <v>3.35</v>
-      </c>
-      <c r="AA32">
-        <v>1.79</v>
-      </c>
-      <c r="AB32">
-        <v>1.81</v>
-      </c>
-      <c r="AC32">
-        <v>3.2</v>
-      </c>
-      <c r="AD32">
-        <v>1.26</v>
-      </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="P33">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q33">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AA33">
+        <v>1.79</v>
+      </c>
+      <c r="AB33">
         <v>1.81</v>
-      </c>
-      <c r="AB33">
-        <v>2</v>
       </c>
       <c r="AC33">
         <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK33">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6343,13 +6343,13 @@
         <v>1.96</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P37">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R37">
         <v>2.5</v>
@@ -6394,7 +6394,7 @@
         <v>1.19</v>
       </c>
       <c r="AF37">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG37">
         <v>2.5</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
         <v>1.85</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>23</v>
+        <v>1.7</v>
       </c>
       <c r="O38">
-        <v>11</v>
+        <v>3.72</v>
       </c>
       <c r="P38">
-        <v>1.02</v>
+        <v>4.12</v>
       </c>
       <c r="Q38">
-        <v>17</v>
+        <v>1.95</v>
       </c>
       <c r="R38">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="S38">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="T38">
-        <v>5.5</v>
+        <v>3.28</v>
       </c>
       <c r="U38">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="V38">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="W38">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA38">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AB38">
-        <v>3.4</v>
+        <v>2.29</v>
       </c>
       <c r="AC38">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD38">
-        <v>1.84</v>
+        <v>1.48</v>
       </c>
       <c r="AE38">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>2.28</v>
+        <v>1.59</v>
       </c>
       <c r="AG38">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>7</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
+        <v>23</v>
+      </c>
+      <c r="O39">
+        <v>11</v>
+      </c>
+      <c r="P39">
+        <v>1.02</v>
+      </c>
+      <c r="Q39">
+        <v>17</v>
+      </c>
+      <c r="R39">
+        <v>3.6</v>
+      </c>
+      <c r="S39">
+        <v>1.11</v>
+      </c>
+      <c r="T39">
+        <v>5.5</v>
+      </c>
+      <c r="U39">
+        <v>1.73</v>
+      </c>
+      <c r="V39">
+        <v>1.95</v>
+      </c>
+      <c r="W39">
+        <v>1.25</v>
+      </c>
+      <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.06</v>
+      </c>
+      <c r="Z39">
+        <v>7.5</v>
+      </c>
+      <c r="AA39">
+        <v>1.25</v>
+      </c>
+      <c r="AB39">
+        <v>3.4</v>
+      </c>
+      <c r="AC39">
         <v>1.7</v>
       </c>
-      <c r="O39">
-        <v>3.72</v>
-      </c>
-      <c r="P39">
-        <v>4.12</v>
-      </c>
-      <c r="Q39">
-        <v>1.95</v>
-      </c>
-      <c r="R39">
-        <v>2.33</v>
-      </c>
-      <c r="S39">
-        <v>1.25</v>
-      </c>
-      <c r="T39">
-        <v>3.34</v>
-      </c>
-      <c r="U39">
-        <v>2.3</v>
-      </c>
-      <c r="V39">
-        <v>1.53</v>
-      </c>
-      <c r="W39">
-        <v>1.12</v>
-      </c>
-      <c r="X39">
-        <v>1.03</v>
-      </c>
-      <c r="Y39">
-        <v>1.17</v>
-      </c>
-      <c r="Z39">
-        <v>4.5</v>
-      </c>
-      <c r="AA39">
-        <v>1.58</v>
-      </c>
-      <c r="AB39">
-        <v>2.2</v>
-      </c>
-      <c r="AC39">
+      <c r="AD39">
+        <v>2.05</v>
+      </c>
+      <c r="AE39">
+        <v>1.44</v>
+      </c>
+      <c r="AF39">
         <v>2.4</v>
       </c>
-      <c r="AD39">
-        <v>1.44</v>
-      </c>
-      <c r="AE39">
-        <v>1.18</v>
-      </c>
-      <c r="AF39">
-        <v>1.59</v>
-      </c>
       <c r="AG39">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>7</v>
       </c>
       <c r="AK39">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -9953,10 +9953,10 @@
         <v>1.85</v>
       </c>
       <c r="W59">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
         <v>1.04</v>
@@ -9968,19 +9968,19 @@
         <v>1.25</v>
       </c>
       <c r="AB59">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC59">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD59">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE59">
         <v>1.41</v>
       </c>
       <c r="AF59">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG59">
         <v>2.5</v>
@@ -10104,7 +10104,7 @@
         <v>2.17</v>
       </c>
       <c r="S60">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T60">
         <v>2.39</v>
@@ -10122,7 +10122,7 @@
         <v>1</v>
       </c>
       <c r="Y60">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z60">
         <v>2.9</v>
@@ -10131,7 +10131,7 @@
         <v>1.58</v>
       </c>
       <c r="AB60">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AC60">
         <v>2.88</v>
@@ -10279,7 +10279,7 @@
         <v>1.55</v>
       </c>
       <c r="W61">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
         <v>1.04</v>
@@ -10303,10 +10303,10 @@
         <v>1.46</v>
       </c>
       <c r="AE61">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF61">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG61">
         <v>2.38</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P62">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q62">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S62">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V62">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W62">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X62">
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z62">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AC62">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AD62">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE62">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG62">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK62">
-        <v>1.19</v>
+        <v>2.26</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="O63">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>4.7</v>
+        <v>1.85</v>
       </c>
       <c r="Q63">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="R63">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U63">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V63">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W63">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z63">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA63">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB63">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="AC63">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AD63">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AE63">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF63">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK63">
-        <v>2.36</v>
+        <v>1.19</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>1.21</v>
       </c>
       <c r="Q64">
-        <v>8.15</v>
+        <v>9</v>
       </c>
       <c r="R64">
         <v>2.88</v>
@@ -10762,10 +10762,10 @@
         <v>4.5</v>
       </c>
       <c r="U64">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V64">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W64">
         <v>1.18</v>
@@ -10783,22 +10783,22 @@
         <v>1.36</v>
       </c>
       <c r="AB64">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC64">
         <v>2</v>
       </c>
       <c r="AD64">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE64">
         <v>1.28</v>
       </c>
       <c r="AF64">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG64">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="O70">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q70">
         <v>3.4</v>
@@ -11740,7 +11740,7 @@
         <v>3.25</v>
       </c>
       <c r="U70">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V70">
         <v>1.48</v>
@@ -11755,7 +11755,7 @@
         <v>1.28</v>
       </c>
       <c r="Z70">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA70">
         <v>1.74</v>
@@ -11764,7 +11764,7 @@
         <v>2.09</v>
       </c>
       <c r="AC70">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD70">
         <v>1.38</v>
@@ -11792,7 +11792,7 @@
         <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="O72">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="P72">
-        <v>10</v>
+        <v>8.82</v>
       </c>
       <c r="Q72">
         <v>1.54</v>
@@ -12099,10 +12099,10 @@
         <v>1.25</v>
       </c>
       <c r="AF72">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AG72">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="R73">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S73">
         <v>1.29</v>
@@ -12244,7 +12244,7 @@
         <v>1.18</v>
       </c>
       <c r="Z73">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="AA73">
         <v>1.71</v>
@@ -12265,7 +12265,7 @@
         <v>1.66</v>
       </c>
       <c r="AG73">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12392,16 +12392,16 @@
         <v>3.3</v>
       </c>
       <c r="U74">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V74">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W74">
         <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y74">
         <v>1.19</v>
@@ -12413,16 +12413,16 @@
         <v>1.78</v>
       </c>
       <c r="AB74">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC74">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="AD74">
         <v>1.43</v>
       </c>
       <c r="AE74">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF74">
         <v>1.6</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P77">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O78">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -13186,16 +13186,16 @@
         </is>
       </c>
       <c r="N79">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P79">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q79">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="R79">
         <v>2.3</v>
@@ -13222,7 +13222,7 @@
         <v>1.22</v>
       </c>
       <c r="Z79">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AA79">
         <v>1.7</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="O82">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="Q82">
-        <v>3.28</v>
+        <v>4.42</v>
       </c>
       <c r="R82">
+        <v>2.2</v>
+      </c>
+      <c r="S82">
+        <v>1.3</v>
+      </c>
+      <c r="T82">
+        <v>3.2</v>
+      </c>
+      <c r="U82">
         <v>2.1</v>
       </c>
-      <c r="S82">
-        <v>1.36</v>
-      </c>
-      <c r="T82">
-        <v>2.88</v>
-      </c>
-      <c r="U82">
-        <v>2.65</v>
-      </c>
       <c r="V82">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W82">
         <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z82">
-        <v>3.63</v>
+        <v>2.9</v>
       </c>
       <c r="AA82">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB82">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC82">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AD82">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE82">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG82">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="O83">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q83">
-        <v>4.42</v>
+        <v>3.4</v>
       </c>
       <c r="R83">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
         <v>1.3</v>
       </c>
       <c r="T83">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U83">
+        <v>2.44</v>
+      </c>
+      <c r="V83">
+        <v>1.46</v>
+      </c>
+      <c r="W83">
+        <v>1.1</v>
+      </c>
+      <c r="X83">
+        <v>1.03</v>
+      </c>
+      <c r="Y83">
+        <v>1.16</v>
+      </c>
+      <c r="Z83">
+        <v>4.19</v>
+      </c>
+      <c r="AA83">
+        <v>1.7</v>
+      </c>
+      <c r="AB83">
         <v>2.1</v>
       </c>
-      <c r="V83">
-        <v>1.38</v>
-      </c>
-      <c r="W83">
-        <v>1.11</v>
-      </c>
-      <c r="X83">
-        <v>1.04</v>
-      </c>
-      <c r="Y83">
+      <c r="AC83">
+        <v>2.25</v>
+      </c>
+      <c r="AD83">
+        <v>1.33</v>
+      </c>
+      <c r="AE83">
         <v>1.17</v>
       </c>
-      <c r="Z83">
-        <v>2.9</v>
-      </c>
-      <c r="AA83">
-        <v>1.76</v>
-      </c>
-      <c r="AB83">
-        <v>2</v>
-      </c>
-      <c r="AC83">
-        <v>2.9</v>
-      </c>
-      <c r="AD83">
-        <v>1.36</v>
-      </c>
-      <c r="AE83">
-        <v>1.14</v>
-      </c>
       <c r="AF83">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG83">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,65 +14001,65 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="O84">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P84">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q84">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R84">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S84">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="T84">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="U84">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="V84">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W84">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X84">
         <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z84">
-        <v>4.19</v>
+        <v>3.13</v>
       </c>
       <c r="AA84">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB84">
         <v>2.1</v>
       </c>
       <c r="AC84">
+        <v>2.5</v>
+      </c>
+      <c r="AD84">
+        <v>1.44</v>
+      </c>
+      <c r="AE84">
+        <v>1.18</v>
+      </c>
+      <c r="AF84">
+        <v>1.56</v>
+      </c>
+      <c r="AG84">
         <v>2.25</v>
       </c>
-      <c r="AD84">
-        <v>1.33</v>
-      </c>
-      <c r="AE84">
-        <v>1.17</v>
-      </c>
-      <c r="AF84">
-        <v>1.57</v>
-      </c>
-      <c r="AG84">
-        <v>2.27</v>
-      </c>
       <c r="AH84" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
+        <v>1.22</v>
+      </c>
+      <c r="AK84">
         <v>1.25</v>
-      </c>
-      <c r="AK84">
-        <v>1.31</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="O85">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
       <c r="Q85">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="R85">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="S85">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="T85">
-        <v>3.54</v>
+        <v>3</v>
       </c>
       <c r="U85">
-        <v>2.01</v>
+        <v>2.82</v>
       </c>
       <c r="V85">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z85">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="AA85">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB85">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC85">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="AD85">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE85">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF85">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG85">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,49 +14327,49 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O86">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P86">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="Q86">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="R86">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S86">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T86">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U86">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="V86">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W86">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y86">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z86">
-        <v>3.34</v>
+        <v>3.63</v>
       </c>
       <c r="AA86">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB86">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC86">
         <v>2.97</v>
@@ -14378,13 +14378,13 @@
         <v>1.3</v>
       </c>
       <c r="AE86">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG86">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="O100">
         <v>3.5</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="O111">
-        <v>3.84</v>
+        <v>3.24</v>
       </c>
       <c r="P111">
-        <v>4.68</v>
+        <v>2.48</v>
       </c>
       <c r="Q111">
-        <v>2.21</v>
+        <v>3.18</v>
       </c>
       <c r="R111">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T111">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="U111">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V111">
+        <v>1.38</v>
+      </c>
+      <c r="W111">
+        <v>1.03</v>
+      </c>
+      <c r="X111">
+        <v>1.01</v>
+      </c>
+      <c r="Y111">
+        <v>1.3</v>
+      </c>
+      <c r="Z111">
+        <v>3.1</v>
+      </c>
+      <c r="AA111">
+        <v>1.86</v>
+      </c>
+      <c r="AB111">
+        <v>1.81</v>
+      </c>
+      <c r="AC111">
+        <v>3.3</v>
+      </c>
+      <c r="AD111">
+        <v>1.27</v>
+      </c>
+      <c r="AE111">
+        <v>1.07</v>
+      </c>
+      <c r="AF111">
+        <v>1.71</v>
+      </c>
+      <c r="AG111">
+        <v>2.05</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.48</v>
+      </c>
+      <c r="AK111">
         <v>1.44</v>
-      </c>
-      <c r="W111">
-        <v>1.05</v>
-      </c>
-      <c r="X111">
-        <v>1.02</v>
-      </c>
-      <c r="Y111">
-        <v>1.25</v>
-      </c>
-      <c r="Z111">
-        <v>3.35</v>
-      </c>
-      <c r="AA111">
-        <v>1.79</v>
-      </c>
-      <c r="AB111">
-        <v>2</v>
-      </c>
-      <c r="AC111">
-        <v>2.85</v>
-      </c>
-      <c r="AD111">
-        <v>1.35</v>
-      </c>
-      <c r="AE111">
-        <v>1.14</v>
-      </c>
-      <c r="AF111">
-        <v>1.77</v>
-      </c>
-      <c r="AG111">
-        <v>2</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.13</v>
-      </c>
-      <c r="AK111">
-        <v>2.06</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,61 +18565,61 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O112">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P112">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="Q112">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="R112">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S112">
+        <v>1.35</v>
+      </c>
+      <c r="T112">
+        <v>3.1</v>
+      </c>
+      <c r="U112">
+        <v>2.88</v>
+      </c>
+      <c r="V112">
         <v>1.36</v>
       </c>
-      <c r="T112">
-        <v>2.9</v>
-      </c>
-      <c r="U112">
-        <v>2.81</v>
-      </c>
-      <c r="V112">
-        <v>1.38</v>
-      </c>
       <c r="W112">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z112">
-        <v>3.1</v>
+        <v>3.73</v>
       </c>
       <c r="AA112">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AB112">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC112">
         <v>3.3</v>
       </c>
       <c r="AD112">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE112">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF112">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG112">
         <v>2.05</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AK112">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,80 +18728,80 @@
         </is>
       </c>
       <c r="N113">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="O113">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P113">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q113">
         <v>2.55</v>
       </c>
       <c r="R113">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S113">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T113">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U113">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V113">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W113">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z113">
-        <v>3.73</v>
+        <v>4.34</v>
       </c>
       <c r="AA113">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AB113">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC113">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD113">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE113">
         <v>1.13</v>
       </c>
       <c r="AF113">
+        <v>1.6</v>
+      </c>
+      <c r="AG113">
+        <v>2.2</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
+        <v>1.35</v>
+      </c>
+      <c r="AK113">
         <v>1.69</v>
-      </c>
-      <c r="AG113">
-        <v>2.05</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>1.33</v>
-      </c>
-      <c r="AK113">
-        <v>1.67</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="O114">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P114">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q114">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="R114">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="S114">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="T114">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="U114">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="V114">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W114">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y114">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z114">
-        <v>4.34</v>
+        <v>2.66</v>
       </c>
       <c r="AA114">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB114">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC114">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD114">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE114">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AF114">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG114">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK114">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.17</v>
+        <v>1.66</v>
       </c>
       <c r="O115">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="P115">
-        <v>3</v>
+        <v>4.68</v>
       </c>
       <c r="Q115">
-        <v>2.88</v>
+        <v>2.21</v>
       </c>
       <c r="R115">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="S115">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="T115">
+        <v>2.99</v>
+      </c>
+      <c r="U115">
         <v>2.62</v>
       </c>
-      <c r="U115">
-        <v>3</v>
-      </c>
       <c r="V115">
+        <v>1.44</v>
+      </c>
+      <c r="W115">
+        <v>1.05</v>
+      </c>
+      <c r="X115">
+        <v>1.02</v>
+      </c>
+      <c r="Y115">
+        <v>1.25</v>
+      </c>
+      <c r="Z115">
+        <v>3.35</v>
+      </c>
+      <c r="AA115">
+        <v>1.79</v>
+      </c>
+      <c r="AB115">
+        <v>2</v>
+      </c>
+      <c r="AC115">
+        <v>2.85</v>
+      </c>
+      <c r="AD115">
         <v>1.35</v>
       </c>
-      <c r="W115">
-        <v>1.02</v>
-      </c>
-      <c r="X115">
-        <v>1.07</v>
-      </c>
-      <c r="Y115">
-        <v>1.4</v>
-      </c>
-      <c r="Z115">
-        <v>2.66</v>
-      </c>
-      <c r="AA115">
-        <v>2.2</v>
-      </c>
-      <c r="AB115">
-        <v>1.63</v>
-      </c>
-      <c r="AC115">
-        <v>4.2</v>
-      </c>
-      <c r="AD115">
-        <v>1.22</v>
-      </c>
       <c r="AE115">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF115">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG115">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AK115">
-        <v>1.52</v>
+        <v>2.06</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19561,7 +19561,7 @@
         <v>1.29</v>
       </c>
       <c r="T118">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U118">
         <v>2.38</v>
@@ -19582,10 +19582,10 @@
         <v>4.33</v>
       </c>
       <c r="AA118">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB118">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC118">
         <v>2.6</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O127">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P127">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -21046,7 +21046,7 @@
         <v>1.17</v>
       </c>
       <c r="Z127">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA127">
         <v>1.56</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="O128">
         <v>3.6</v>
       </c>
       <c r="P128">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q128">
         <v>3.3</v>
@@ -21194,7 +21194,7 @@
         <v>2.63</v>
       </c>
       <c r="U128">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="V128">
         <v>1.55</v>
@@ -21212,13 +21212,13 @@
         <v>4.33</v>
       </c>
       <c r="AA128">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB128">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AC128">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD128">
         <v>1.44</v>
@@ -21662,10 +21662,10 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O131">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P131">
         <v>6.89</v>
@@ -21713,13 +21713,13 @@
         <v>1.58</v>
       </c>
       <c r="AE131">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF131">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG131">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,31 +22314,31 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="P135">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="Q135">
-        <v>2.63</v>
+        <v>1.68</v>
       </c>
       <c r="R135">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S135">
         <v>1.3</v>
       </c>
       <c r="T135">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U135">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="V135">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W135">
         <v>1.1</v>
@@ -22347,31 +22347,31 @@
         <v>1.03</v>
       </c>
       <c r="Y135">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z135">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA135">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AB135">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AC135">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AD135">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE135">
         <v>1.17</v>
       </c>
       <c r="AF135">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AG135">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK135">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.35</v>
+        <v>2.98</v>
       </c>
       <c r="O136">
-        <v>4.65</v>
+        <v>3.1</v>
       </c>
       <c r="P136">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q136">
-        <v>1.68</v>
+        <v>3.82</v>
       </c>
       <c r="R136">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="S136">
+        <v>1.33</v>
+      </c>
+      <c r="T136">
+        <v>2.88</v>
+      </c>
+      <c r="U136">
+        <v>2.73</v>
+      </c>
+      <c r="V136">
+        <v>1.36</v>
+      </c>
+      <c r="W136">
+        <v>1.08</v>
+      </c>
+      <c r="X136">
+        <v>1.04</v>
+      </c>
+      <c r="Y136">
         <v>1.3</v>
       </c>
-      <c r="T136">
-        <v>3.28</v>
-      </c>
-      <c r="U136">
-        <v>2.3</v>
-      </c>
-      <c r="V136">
-        <v>1.55</v>
-      </c>
-      <c r="W136">
-        <v>1.1</v>
-      </c>
-      <c r="X136">
-        <v>1.03</v>
-      </c>
-      <c r="Y136">
-        <v>1.18</v>
-      </c>
       <c r="Z136">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA136">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AB136">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AC136">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="AD136">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE136">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF136">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AK136">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="O137">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P137">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q137">
-        <v>3.82</v>
+        <v>2.63</v>
       </c>
       <c r="R137">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="U137">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="V137">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z137">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="AA137">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AB137">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC137">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD137">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE137">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF137">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG137">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK137">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22809,13 +22809,13 @@
         <v>3.75</v>
       </c>
       <c r="P138">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="Q138">
         <v>2.25</v>
       </c>
       <c r="R138">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="S138">
         <v>1.25</v>
@@ -22857,10 +22857,10 @@
         <v>1.19</v>
       </c>
       <c r="AF138">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG138">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK138">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22966,10 +22966,10 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O139">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P139">
         <v>1.77</v>
@@ -23129,25 +23129,25 @@
         </is>
       </c>
       <c r="N140">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O140">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P140">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="Q140">
         <v>4.2</v>
       </c>
       <c r="R140">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S140">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T140">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U140">
         <v>2.77</v>
@@ -23183,7 +23183,7 @@
         <v>1.06</v>
       </c>
       <c r="AF140">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG140">
         <v>1.98</v>
@@ -23199,7 +23199,7 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK140">
         <v>1.25</v>
@@ -23295,7 +23295,7 @@
         <v>1.8</v>
       </c>
       <c r="O141">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P141">
         <v>3.8</v>
@@ -23322,7 +23322,7 @@
         <v>1.1</v>
       </c>
       <c r="X141">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y141">
         <v>1.22</v>
@@ -23334,10 +23334,10 @@
         <v>1.8</v>
       </c>
       <c r="AB141">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AC141">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AD141">
         <v>1.33</v>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK141">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -24107,16 +24107,16 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O146">
         <v>3.2</v>
       </c>
       <c r="P146">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q146">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="R146">
         <v>2.08</v>
@@ -24152,7 +24152,7 @@
         <v>1.83</v>
       </c>
       <c r="AC146">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD146">
         <v>1.26</v>
@@ -24439,7 +24439,7 @@
         <v>3.5</v>
       </c>
       <c r="P148">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q148">
         <v>2.3</v>
@@ -24460,13 +24460,13 @@
         <v>1.39</v>
       </c>
       <c r="W148">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X148">
         <v>1</v>
       </c>
       <c r="Y148">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z148">
         <v>3.6</v>
@@ -24478,13 +24478,13 @@
         <v>1.9</v>
       </c>
       <c r="AC148">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD148">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE148">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF148">
         <v>1.7</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>3.48</v>
+        <v>6.57</v>
       </c>
       <c r="O166">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="P166">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
       <c r="Q166">
-        <v>4.2</v>
+        <v>6.75</v>
       </c>
       <c r="R166">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="S166">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T166">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U166">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="V166">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W166">
         <v>0</v>
       </c>
       <c r="X166">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y166">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z166">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AA166">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AB166">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE166">
         <v>0</v>
       </c>
       <c r="AF166">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AG166">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK166">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>6.57</v>
+        <v>3.48</v>
       </c>
       <c r="O167">
-        <v>3.38</v>
+        <v>2.82</v>
       </c>
       <c r="P167">
-        <v>1.51</v>
+        <v>2.13</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T167">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U167">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V167">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W167">
         <v>0</v>
       </c>
       <c r="X167">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y167">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z167">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AD167">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE167">
         <v>0</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG167">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK167">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O168">
         <v>3.2</v>
       </c>
       <c r="P168">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q168">
         <v>2.63</v>
@@ -27747,7 +27747,7 @@
         <v>1.06</v>
       </c>
       <c r="AF168">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG168">
         <v>1.89</v>
@@ -27862,10 +27862,10 @@
         <v>3.2</v>
       </c>
       <c r="P169">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="Q169">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R169">
         <v>2.1</v>
@@ -27886,13 +27886,13 @@
         <v>1.08</v>
       </c>
       <c r="X169">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y169">
         <v>1.3</v>
       </c>
       <c r="Z169">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA169">
         <v>1.91</v>
@@ -27929,7 +27929,7 @@
         <v>1.33</v>
       </c>
       <c r="AK169">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28553,10 +28553,10 @@
         <v>2.01</v>
       </c>
       <c r="AC173">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AD173">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE173">
         <v>1.08</v>
@@ -28834,16 +28834,16 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O175">
         <v>3.8</v>
       </c>
       <c r="P175">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q175">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="R175">
         <v>2.54</v>
@@ -28855,10 +28855,10 @@
         <v>3.5</v>
       </c>
       <c r="U175">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V175">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W175">
         <v>1.12</v>
@@ -28873,10 +28873,10 @@
         <v>4.5</v>
       </c>
       <c r="AA175">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB175">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AC175">
         <v>2.55</v>
@@ -28888,7 +28888,7 @@
         <v>1.15</v>
       </c>
       <c r="AF175">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG175">
         <v>2.15</v>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK175">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>4.37</v>
+        <v>3.28</v>
       </c>
       <c r="O180">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="P180">
+        <v>2.2</v>
+      </c>
+      <c r="Q180">
+        <v>5.35</v>
+      </c>
+      <c r="R180">
         <v>1.83</v>
       </c>
-      <c r="Q180">
-        <v>4.75</v>
-      </c>
-      <c r="R180">
-        <v>1.85</v>
-      </c>
       <c r="S180">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T180">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U180">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="V180">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W180">
         <v>0</v>
       </c>
       <c r="X180">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y180">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z180">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AA180">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AB180">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE180">
         <v>0</v>
       </c>
       <c r="AF180">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AG180">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK180">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -31605,10 +31605,10 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="O192">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="P192">
         <v>4.33</v>
@@ -31626,13 +31626,13 @@
         <v>3</v>
       </c>
       <c r="U192">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V192">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W192">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X192">
         <v>1.01</v>
@@ -31662,7 +31662,7 @@
         <v>1.79</v>
       </c>
       <c r="AG192">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="O209">
         <v>4.1</v>
@@ -34406,7 +34406,7 @@
         <v>1.12</v>
       </c>
       <c r="X209">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y209">
         <v>1.18</v>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK209">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -35843,7 +35843,7 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O218">
         <v>3.25</v>
@@ -35882,10 +35882,10 @@
         <v>0</v>
       </c>
       <c r="AA218">
+        <v>1.85</v>
+      </c>
+      <c r="AB218">
         <v>1.95</v>
-      </c>
-      <c r="AB218">
-        <v>1.85</v>
       </c>
       <c r="AC218">
         <v>0</v>
@@ -36054,7 +36054,7 @@
         <v>1.98</v>
       </c>
       <c r="AD219">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE219">
         <v>1.36</v>
@@ -36076,7 +36076,7 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK219">
         <v>1.85</v>
@@ -37150,10 +37150,10 @@
         <v>1.91</v>
       </c>
       <c r="O226">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P226">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q226">
         <v>2.63</v>
@@ -37189,13 +37189,13 @@
         <v>2.25</v>
       </c>
       <c r="AB226">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC226">
         <v>4.5</v>
       </c>
       <c r="AD226">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE226">
         <v>1.04</v>
@@ -37322,13 +37322,13 @@
         <v>2.5</v>
       </c>
       <c r="R227">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S227">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T227">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="U227">
         <v>3.6</v>
@@ -37488,13 +37488,13 @@
         <v>1.85</v>
       </c>
       <c r="S228">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="T228">
         <v>2.3</v>
       </c>
       <c r="U228">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="V228">
         <v>1.2</v>
@@ -37503,7 +37503,7 @@
         <v>1.01</v>
       </c>
       <c r="X228">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y228">
         <v>1.58</v>
@@ -37521,13 +37521,13 @@
         <v>5.75</v>
       </c>
       <c r="AD228">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE228">
         <v>1.03</v>
       </c>
       <c r="AF228">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AG228">
         <v>1.6</v>
@@ -39112,22 +39112,22 @@
         <v>2.43</v>
       </c>
       <c r="Q238">
-        <v>2.91</v>
+        <v>3.32</v>
       </c>
       <c r="R238">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S238">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T238">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U238">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="V238">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W238">
         <v>1.14</v>
@@ -39136,47 +39136,47 @@
         <v>1.01</v>
       </c>
       <c r="Y238">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z238">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA238">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AB238">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AC238">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AD238">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE238">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF238">
+        <v>1.44</v>
+      </c>
+      <c r="AG238">
+        <v>2.4</v>
+      </c>
+      <c r="AH238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ238">
+        <v>1.25</v>
+      </c>
+      <c r="AK238">
         <v>1.4</v>
-      </c>
-      <c r="AG238">
-        <v>2.57</v>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ238">
-        <v>1.2</v>
-      </c>
-      <c r="AK238">
-        <v>1.47</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>5</v>
       </c>
       <c r="AA253">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB253">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC253">
         <v>2.41</v>
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,28 +42037,28 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O256">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P256">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="Q256">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R256">
         <v>2.3</v>
       </c>
       <c r="S256">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T256">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U256">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V256">
         <v>1.48</v>
@@ -42070,28 +42070,28 @@
         <v>1.02</v>
       </c>
       <c r="Y256">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z256">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="AA256">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB256">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC256">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD256">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE256">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF256">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG256">
         <v>2.25</v>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK256">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G257">
@@ -42200,28 +42200,28 @@
         </is>
       </c>
       <c r="N257">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O257">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P257">
-        <v>2.8</v>
+        <v>3.21</v>
       </c>
       <c r="Q257">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R257">
         <v>2.3</v>
       </c>
       <c r="S257">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T257">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U257">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V257">
         <v>1.48</v>
@@ -42233,28 +42233,28 @@
         <v>1.02</v>
       </c>
       <c r="Y257">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z257">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="AA257">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB257">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC257">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AD257">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE257">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF257">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG257">
         <v>2.25</v>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK257">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42529,13 +42529,13 @@
         <v>2.25</v>
       </c>
       <c r="O259">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P259">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="Q259">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="R259">
         <v>2.1</v>
@@ -42556,7 +42556,7 @@
         <v>1.05</v>
       </c>
       <c r="X259">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y259">
         <v>1.28</v>
@@ -42574,16 +42574,16 @@
         <v>3.2</v>
       </c>
       <c r="AD259">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE259">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF259">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG259">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.91</v>
+        <v>3.11</v>
       </c>
       <c r="O271">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="P271">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="Q271">
-        <v>2.45</v>
+        <v>4.48</v>
       </c>
       <c r="R271">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S271">
+        <v>1.33</v>
+      </c>
+      <c r="T271">
+        <v>2.91</v>
+      </c>
+      <c r="U271">
+        <v>2.66</v>
+      </c>
+      <c r="V271">
+        <v>1.45</v>
+      </c>
+      <c r="W271">
+        <v>1.05</v>
+      </c>
+      <c r="X271">
+        <v>1</v>
+      </c>
+      <c r="Y271">
         <v>1.24</v>
       </c>
-      <c r="T271">
-        <v>3.46</v>
-      </c>
-      <c r="U271">
-        <v>2.64</v>
-      </c>
-      <c r="V271">
-        <v>1.49</v>
-      </c>
-      <c r="W271">
-        <v>1.08</v>
-      </c>
-      <c r="X271">
-        <v>1.02</v>
-      </c>
-      <c r="Y271">
-        <v>1.23</v>
-      </c>
       <c r="Z271">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA271">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB271">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC271">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="AD271">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE271">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF271">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AG271">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK271">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>3.11</v>
+        <v>1.91</v>
       </c>
       <c r="O272">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="P272">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="Q272">
-        <v>4.48</v>
+        <v>2.45</v>
       </c>
       <c r="R272">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S272">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="T272">
-        <v>2.91</v>
+        <v>3.46</v>
       </c>
       <c r="U272">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V272">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W272">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X272">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y272">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z272">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA272">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB272">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC272">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AD272">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE272">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF272">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AG272">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK272">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="O274">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="P274">
-        <v>2.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q274">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="R274">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S274">
         <v>1.22</v>
       </c>
       <c r="T274">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="U274">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V274">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="W274">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X274">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y274">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z274">
-        <v>5</v>
+        <v>5.71</v>
       </c>
       <c r="AA274">
+        <v>1.41</v>
+      </c>
+      <c r="AB274">
+        <v>2.7</v>
+      </c>
+      <c r="AC274">
+        <v>2.05</v>
+      </c>
+      <c r="AD274">
+        <v>1.74</v>
+      </c>
+      <c r="AE274">
+        <v>1.25</v>
+      </c>
+      <c r="AF274">
         <v>1.5</v>
       </c>
-      <c r="AB274">
-        <v>2.5</v>
-      </c>
-      <c r="AC274">
-        <v>2.25</v>
-      </c>
-      <c r="AD274">
-        <v>1.68</v>
-      </c>
-      <c r="AE274">
-        <v>1.28</v>
-      </c>
-      <c r="AF274">
-        <v>1.4</v>
-      </c>
       <c r="AG274">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK274">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,80 +45134,80 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="O275">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="P275">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q275">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="R275">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S275">
         <v>1.22</v>
       </c>
       <c r="T275">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="U275">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V275">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="W275">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X275">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y275">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z275">
-        <v>5.71</v>
+        <v>5</v>
       </c>
       <c r="AA275">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB275">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AC275">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD275">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AE275">
+        <v>1.28</v>
+      </c>
+      <c r="AF275">
+        <v>1.4</v>
+      </c>
+      <c r="AG275">
+        <v>2.63</v>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ275">
         <v>1.25</v>
       </c>
-      <c r="AF275">
-        <v>1.5</v>
-      </c>
-      <c r="AG275">
-        <v>2.45</v>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ275">
-        <v>1.2</v>
-      </c>
       <c r="AK275">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AL275">
         <v>0</v>

--- a/jogos_2026-08-15.xlsx
+++ b/jogos_2026-08-15.xlsx
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -953,11 +953,11 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "34", "43"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "29", "45", "62"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1279,11 +1279,11 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "66"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="O7">
         <v>2.9</v>
       </c>
       <c r="P7">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="R7">
         <v>2</v>
@@ -1468,43 +1468,43 @@
         <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="U7">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="V7">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Z7">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA7">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB7">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC7">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="AD7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG7">
         <v>1.8</v>
@@ -1590,36 +1590,36 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="O8">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>3.67</v>
+        <v>2.89</v>
       </c>
       <c r="Q8">
         <v>2.77</v>
@@ -1631,7 +1631,7 @@
         <v>1.4</v>
       </c>
       <c r="T8">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U8">
         <v>2.95</v>
@@ -1649,22 +1649,22 @@
         <v>1.36</v>
       </c>
       <c r="Z8">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA8">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB8">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
         <v>1.83</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "30", "49", "64", "83"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1785,16 +1785,16 @@
         <v>4.78</v>
       </c>
       <c r="Q9">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="R9">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T9">
-        <v>2.53</v>
+        <v>2.76</v>
       </c>
       <c r="U9">
         <v>3.2</v>
@@ -1809,16 +1809,16 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA9">
         <v>2.16</v>
       </c>
       <c r="AB9">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
         <v>3.5</v>
@@ -1827,7 +1827,7 @@
         <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
         <v>1.95</v>
@@ -1837,46 +1837,46 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "90+3"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "67"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK9">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1942,28 +1942,28 @@
         <v>2.62</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
         <v>2.55</v>
       </c>
       <c r="Q10">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="R10">
         <v>1.99</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U10">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
         <v>1.04</v>
@@ -1990,7 +1990,7 @@
         <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2012,7 +2012,7 @@
         <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,31 +2105,31 @@
         <v>1.82</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S11">
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="U11">
         <v>2.8</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
         <v>1.06</v>
@@ -2138,25 +2138,25 @@
         <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA11">
         <v>1.93</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC11">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD11">
         <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
         <v>1.83</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="O12">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="P12">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q12">
         <v>3.5</v>
@@ -2316,7 +2316,7 @@
         <v>1.18</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
         <v>1.85</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O13">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P13">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R13">
         <v>2.1</v>
@@ -2446,10 +2446,10 @@
         <v>1.41</v>
       </c>
       <c r="T13">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U13">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="V13">
         <v>1.39</v>
@@ -2458,7 +2458,7 @@
         <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.3</v>
@@ -2467,16 +2467,16 @@
         <v>3.3</v>
       </c>
       <c r="AA13">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC13">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AD13">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE13">
         <v>1.1</v>
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="N14">
+        <v>1.8</v>
+      </c>
+      <c r="O14">
+        <v>3.25</v>
+      </c>
+      <c r="P14">
+        <v>3.9</v>
+      </c>
+      <c r="Q14">
+        <v>2.63</v>
+      </c>
+      <c r="R14">
         <v>2.1</v>
-      </c>
-      <c r="O14">
-        <v>3.1</v>
-      </c>
-      <c r="P14">
-        <v>3.1</v>
-      </c>
-      <c r="Q14">
-        <v>2.8</v>
-      </c>
-      <c r="R14">
-        <v>2</v>
       </c>
       <c r="S14">
         <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2630,16 +2630,16 @@
         <v>3</v>
       </c>
       <c r="AA14">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
         <v>1.58</v>
       </c>
       <c r="AC14">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE14">
         <v>1.07</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="P15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
         <v>2.3</v>
@@ -2778,7 +2778,7 @@
         <v>3.15</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W15">
         <v>1.06</v>
@@ -2808,7 +2808,7 @@
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG15">
         <v>1.7</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="O16">
         <v>3.2</v>
@@ -2938,10 +2938,10 @@
         <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W16">
         <v>1.04</v>
@@ -2950,16 +2950,16 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z16">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="AA16">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB16">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC16">
         <v>3.2</v>
@@ -2971,10 +2971,10 @@
         <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,28 +3083,28 @@
         <v>2</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R17">
         <v>1.92</v>
       </c>
       <c r="S17">
+        <v>1.45</v>
+      </c>
+      <c r="T17">
+        <v>2.8</v>
+      </c>
+      <c r="U17">
+        <v>2.75</v>
+      </c>
+      <c r="V17">
         <v>1.4</v>
-      </c>
-      <c r="T17">
-        <v>2.75</v>
-      </c>
-      <c r="U17">
-        <v>3</v>
-      </c>
-      <c r="V17">
-        <v>1.33</v>
       </c>
       <c r="W17">
         <v>1.05</v>
@@ -3116,22 +3116,22 @@
         <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.18</v>
+        <v>2.97</v>
       </c>
       <c r="AA17">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC17">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AD17">
         <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
         <v>1.87</v>
@@ -3264,7 +3264,7 @@
         <v>2.65</v>
       </c>
       <c r="U18">
-        <v>3.18</v>
+        <v>3.31</v>
       </c>
       <c r="V18">
         <v>1.35</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
         <v>1.36</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="Q19">
         <v>3</v>
@@ -3427,16 +3427,16 @@
         <v>2.44</v>
       </c>
       <c r="U19">
-        <v>3.14</v>
+        <v>2.96</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
         <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.32</v>
@@ -3451,10 +3451,10 @@
         <v>1.67</v>
       </c>
       <c r="AC19">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE19">
         <v>1.05</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
         <v>1.5</v>
@@ -3922,7 +3922,7 @@
         <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
         <v>1.06</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.47</v>
+        <v>4.6</v>
       </c>
       <c r="O23">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="Q23">
-        <v>3.36</v>
+        <v>5.05</v>
       </c>
       <c r="R23">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S23">
+        <v>1.4</v>
+      </c>
+      <c r="T23">
+        <v>2.88</v>
+      </c>
+      <c r="U23">
+        <v>2.9</v>
+      </c>
+      <c r="V23">
+        <v>1.33</v>
+      </c>
+      <c r="W23">
+        <v>1.05</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
         <v>1.38</v>
       </c>
-      <c r="T23">
-        <v>2.65</v>
-      </c>
-      <c r="U23">
-        <v>2.94</v>
-      </c>
-      <c r="V23">
-        <v>1.37</v>
-      </c>
-      <c r="W23">
+      <c r="Z23">
+        <v>3</v>
+      </c>
+      <c r="AA23">
+        <v>2.1</v>
+      </c>
+      <c r="AB23">
+        <v>1.66</v>
+      </c>
+      <c r="AC23">
+        <v>4.1</v>
+      </c>
+      <c r="AD23">
+        <v>1.2</v>
+      </c>
+      <c r="AE23">
         <v>1.06</v>
       </c>
-      <c r="X23">
-        <v>1.06</v>
-      </c>
-      <c r="Y23">
-        <v>1.33</v>
-      </c>
-      <c r="Z23">
-        <v>3.08</v>
-      </c>
-      <c r="AA23">
-        <v>2.02</v>
-      </c>
-      <c r="AB23">
-        <v>1.76</v>
-      </c>
-      <c r="AC23">
-        <v>3.38</v>
-      </c>
-      <c r="AD23">
-        <v>1.24</v>
-      </c>
-      <c r="AE23">
-        <v>1.05</v>
-      </c>
       <c r="AF23">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="AK23">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>3.5</v>
+      </c>
+      <c r="O24">
+        <v>3.6</v>
+      </c>
+      <c r="P24">
+        <v>1.98</v>
+      </c>
+      <c r="Q24">
         <v>4</v>
       </c>
-      <c r="O24">
-        <v>3.35</v>
-      </c>
-      <c r="P24">
-        <v>1.93</v>
-      </c>
-      <c r="Q24">
-        <v>4.75</v>
-      </c>
       <c r="R24">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
+        <v>1.37</v>
+      </c>
+      <c r="T24">
+        <v>3.07</v>
+      </c>
+      <c r="U24">
+        <v>2.75</v>
+      </c>
+      <c r="V24">
         <v>1.4</v>
-      </c>
-      <c r="T24">
-        <v>2.88</v>
-      </c>
-      <c r="U24">
-        <v>2.9</v>
-      </c>
-      <c r="V24">
-        <v>1.33</v>
       </c>
       <c r="W24">
         <v>1.05</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AA24">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AB24">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC24">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="O25">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>2.02</v>
+        <v>3.36</v>
       </c>
       <c r="Q25">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
         <v>1.37</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V25">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC25">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE25">
         <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AK25">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.16</v>
+        <v>2.47</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P26">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>2.62</v>
+        <v>3.36</v>
       </c>
       <c r="R26">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="S26">
+        <v>1.38</v>
+      </c>
+      <c r="T26">
+        <v>2.65</v>
+      </c>
+      <c r="U26">
+        <v>2.94</v>
+      </c>
+      <c r="V26">
         <v>1.37</v>
       </c>
-      <c r="T26">
-        <v>2.78</v>
-      </c>
-      <c r="U26">
-        <v>2.62</v>
-      </c>
-      <c r="V26">
-        <v>1.43</v>
-      </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.52</v>
+        <v>3.08</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB26">
-        <v>2.01</v>
+        <v>1.76</v>
       </c>
       <c r="AC26">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK26">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="O29">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.01</v>
+        <v>3.85</v>
       </c>
       <c r="Q29">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.28</v>
+        <v>2.81</v>
       </c>
       <c r="U29">
-        <v>3.48</v>
+        <v>2.69</v>
       </c>
       <c r="V29">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="Z29">
-        <v>2.48</v>
+        <v>3.78</v>
       </c>
       <c r="AA29">
-        <v>2.52</v>
+        <v>1.87</v>
       </c>
       <c r="AB29">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AC29">
-        <v>4.97</v>
+        <v>3.21</v>
       </c>
       <c r="AD29">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE29">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AG29">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>3.85</v>
+        <v>2.01</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T30">
-        <v>2.81</v>
+        <v>2.28</v>
       </c>
       <c r="U30">
-        <v>2.69</v>
+        <v>3.48</v>
       </c>
       <c r="V30">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="W30">
+        <v>1.03</v>
+      </c>
+      <c r="X30">
         <v>1.06</v>
       </c>
-      <c r="X30">
-        <v>1.05</v>
-      </c>
       <c r="Y30">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Z30">
-        <v>3.78</v>
+        <v>2.48</v>
       </c>
       <c r="AA30">
-        <v>1.87</v>
+        <v>2.52</v>
       </c>
       <c r="AB30">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AC30">
-        <v>3.21</v>
+        <v>4.97</v>
       </c>
       <c r="AD30">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF30">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG30">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,28 +5525,28 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="O32">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P32">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="Q32">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R32">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U32">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="V32">
         <v>1.4</v>
@@ -5555,34 +5555,34 @@
         <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA32">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="AB32">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AC32">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AD32">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG32">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AK32">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="O33">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>2.42</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AA33">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AB33">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AC33">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD33">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="O34">
+        <v>3.13</v>
+      </c>
+      <c r="P34">
+        <v>1.94</v>
+      </c>
+      <c r="Q34">
         <v>3.7</v>
       </c>
-      <c r="P34">
-        <v>3.25</v>
-      </c>
-      <c r="Q34">
-        <v>2.35</v>
-      </c>
       <c r="R34">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA34">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="AB34">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC34">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="AD34">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6032,7 +6032,7 @@
         <v>1.47</v>
       </c>
       <c r="T35">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="U35">
         <v>3.16</v>
@@ -6047,7 +6047,7 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z35">
         <v>2.83</v>
@@ -6056,10 +6056,10 @@
         <v>2.23</v>
       </c>
       <c r="AB35">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC35">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AD35">
         <v>1.18</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="O54">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="P54">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
       <c r="Q54">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="S54">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T54">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U54">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="V54">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W54">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z54">
-        <v>5.71</v>
+        <v>6.25</v>
       </c>
       <c r="AA54">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB54">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AC54">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD54">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AE54">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AF54">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AG54">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK54">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="O55">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="P55">
-        <v>2.52</v>
+        <v>2.95</v>
       </c>
       <c r="Q55">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="R55">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="S55">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T55">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U55">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="V55">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W55">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z55">
-        <v>6.25</v>
+        <v>5.71</v>
       </c>
       <c r="AA55">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB55">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="AC55">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD55">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AE55">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AF55">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AG55">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="O61">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="Q61">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="R61">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U61">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V61">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W61">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z61">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA61">
+        <v>1.36</v>
+      </c>
+      <c r="AB61">
+        <v>2.15</v>
+      </c>
+      <c r="AC61">
+        <v>2.17</v>
+      </c>
+      <c r="AD61">
+        <v>1.62</v>
+      </c>
+      <c r="AE61">
+        <v>1.22</v>
+      </c>
+      <c r="AF61">
         <v>1.44</v>
       </c>
-      <c r="AB61">
-        <v>2.7</v>
-      </c>
-      <c r="AC61">
-        <v>2.1</v>
-      </c>
-      <c r="AD61">
-        <v>1.7</v>
-      </c>
-      <c r="AE61">
-        <v>1.29</v>
-      </c>
-      <c r="AF61">
-        <v>1.48</v>
-      </c>
       <c r="AG61">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AK61">
-        <v>2.36</v>
+        <v>1.25</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P62">
-        <v>1.85</v>
+        <v>2.74</v>
       </c>
       <c r="Q62">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S62">
+        <v>1.29</v>
+      </c>
+      <c r="T62">
+        <v>3.25</v>
+      </c>
+      <c r="U62">
+        <v>2.3</v>
+      </c>
+      <c r="V62">
+        <v>1.5</v>
+      </c>
+      <c r="W62">
+        <v>1.08</v>
+      </c>
+      <c r="X62">
+        <v>1.04</v>
+      </c>
+      <c r="Y62">
         <v>1.18</v>
       </c>
-      <c r="T62">
-        <v>2.8</v>
-      </c>
-      <c r="U62">
-        <v>2.05</v>
-      </c>
-      <c r="V62">
-        <v>1.67</v>
-      </c>
-      <c r="W62">
-        <v>1.12</v>
-      </c>
-      <c r="X62">
-        <v>1.03</v>
-      </c>
-      <c r="Y62">
-        <v>1.09</v>
-      </c>
       <c r="Z62">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA62">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB62">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC62">
-        <v>2.17</v>
+        <v>2.52</v>
       </c>
       <c r="AD62">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AE62">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF62">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG62">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AK62">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,61 +10578,61 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="P63">
-        <v>2.74</v>
+        <v>5</v>
       </c>
       <c r="Q63">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="R63">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="S63">
+        <v>1.2</v>
+      </c>
+      <c r="T63">
+        <v>4</v>
+      </c>
+      <c r="U63">
+        <v>2.1</v>
+      </c>
+      <c r="V63">
+        <v>1.64</v>
+      </c>
+      <c r="W63">
+        <v>1.13</v>
+      </c>
+      <c r="X63">
+        <v>1.02</v>
+      </c>
+      <c r="Y63">
+        <v>1.08</v>
+      </c>
+      <c r="Z63">
+        <v>5.5</v>
+      </c>
+      <c r="AA63">
+        <v>1.44</v>
+      </c>
+      <c r="AB63">
+        <v>2.7</v>
+      </c>
+      <c r="AC63">
+        <v>2.1</v>
+      </c>
+      <c r="AD63">
+        <v>1.7</v>
+      </c>
+      <c r="AE63">
         <v>1.29</v>
       </c>
-      <c r="T63">
-        <v>3.25</v>
-      </c>
-      <c r="U63">
-        <v>2.3</v>
-      </c>
-      <c r="V63">
-        <v>1.5</v>
-      </c>
-      <c r="W63">
-        <v>1.08</v>
-      </c>
-      <c r="X63">
-        <v>1.04</v>
-      </c>
-      <c r="Y63">
-        <v>1.18</v>
-      </c>
-      <c r="Z63">
-        <v>4.4</v>
-      </c>
-      <c r="AA63">
-        <v>1.57</v>
-      </c>
-      <c r="AB63">
-        <v>2.14</v>
-      </c>
-      <c r="AC63">
-        <v>2.52</v>
-      </c>
-      <c r="AD63">
-        <v>1.46</v>
-      </c>
-      <c r="AE63">
-        <v>1.19</v>
-      </c>
       <c r="AF63">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AG63">
         <v>2.38</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>2.36</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.31</v>
+        <v>3.65</v>
       </c>
       <c r="O69">
         <v>3.25</v>
       </c>
       <c r="P69">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -11574,13 +11574,13 @@
         <v>1.45</v>
       </c>
       <c r="T69">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="U69">
         <v>3.27</v>
       </c>
       <c r="V69">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W69">
         <v>1.02</v>
@@ -11598,7 +11598,7 @@
         <v>2.21</v>
       </c>
       <c r="AB69">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC69">
         <v>4</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="O85">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P85">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q85">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="R85">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S85">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T85">
-        <v>3.54</v>
+        <v>2.88</v>
       </c>
       <c r="U85">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="V85">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y85">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="Z85">
-        <v>3.13</v>
+        <v>3.66</v>
       </c>
       <c r="AA85">
+        <v>1.83</v>
+      </c>
+      <c r="AB85">
+        <v>1.93</v>
+      </c>
+      <c r="AC85">
+        <v>2.97</v>
+      </c>
+      <c r="AD85">
+        <v>1.3</v>
+      </c>
+      <c r="AE85">
+        <v>1.06</v>
+      </c>
+      <c r="AF85">
         <v>1.62</v>
       </c>
-      <c r="AB85">
+      <c r="AG85">
         <v>2.2</v>
       </c>
-      <c r="AC85">
-        <v>2.5</v>
-      </c>
-      <c r="AD85">
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <v>1.25</v>
+      </c>
+      <c r="AK85">
         <v>1.44</v>
-      </c>
-      <c r="AE85">
-        <v>1.18</v>
-      </c>
-      <c r="AF85">
-        <v>1.6</v>
-      </c>
-      <c r="AG85">
-        <v>2.25</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.22</v>
-      </c>
-      <c r="AK85">
-        <v>1.25</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,65 +14327,65 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="O86">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P86">
+        <v>1.8</v>
+      </c>
+      <c r="Q86">
+        <v>3.75</v>
+      </c>
+      <c r="R86">
+        <v>2.3</v>
+      </c>
+      <c r="S86">
+        <v>1.23</v>
+      </c>
+      <c r="T86">
+        <v>3.54</v>
+      </c>
+      <c r="U86">
+        <v>2</v>
+      </c>
+      <c r="V86">
+        <v>1.43</v>
+      </c>
+      <c r="W86">
+        <v>1.07</v>
+      </c>
+      <c r="X86">
+        <v>1.03</v>
+      </c>
+      <c r="Y86">
+        <v>1.13</v>
+      </c>
+      <c r="Z86">
+        <v>3.13</v>
+      </c>
+      <c r="AA86">
+        <v>1.62</v>
+      </c>
+      <c r="AB86">
+        <v>2.2</v>
+      </c>
+      <c r="AC86">
+        <v>2.5</v>
+      </c>
+      <c r="AD86">
+        <v>1.44</v>
+      </c>
+      <c r="AE86">
+        <v>1.18</v>
+      </c>
+      <c r="AF86">
+        <v>1.6</v>
+      </c>
+      <c r="AG86">
         <v>2.25</v>
       </c>
-      <c r="Q86">
-        <v>3.45</v>
-      </c>
-      <c r="R86">
-        <v>2.2</v>
-      </c>
-      <c r="S86">
-        <v>1.33</v>
-      </c>
-      <c r="T86">
-        <v>3</v>
-      </c>
-      <c r="U86">
-        <v>2.84</v>
-      </c>
-      <c r="V86">
-        <v>1.42</v>
-      </c>
-      <c r="W86">
-        <v>1.1</v>
-      </c>
-      <c r="X86">
-        <v>1.01</v>
-      </c>
-      <c r="Y86">
-        <v>1.24</v>
-      </c>
-      <c r="Z86">
-        <v>3.34</v>
-      </c>
-      <c r="AA86">
-        <v>1.9</v>
-      </c>
-      <c r="AB86">
-        <v>1.9</v>
-      </c>
-      <c r="AC86">
-        <v>2.97</v>
-      </c>
-      <c r="AD86">
-        <v>1.33</v>
-      </c>
-      <c r="AE86">
-        <v>1.11</v>
-      </c>
-      <c r="AF86">
-        <v>1.53</v>
-      </c>
-      <c r="AG86">
-        <v>2.04</v>
-      </c>
       <c r="AH86" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
+        <v>1.22</v>
+      </c>
+      <c r="AK86">
         <v>1.25</v>
-      </c>
-      <c r="AK86">
-        <v>1.36</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O87">
         <v>3.25</v>
       </c>
       <c r="P87">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q87">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="R87">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T87">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U87">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="V87">
         <v>1.42</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z87">
-        <v>3.66</v>
+        <v>3.34</v>
       </c>
       <c r="AA87">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB87">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC87">
         <v>2.97</v>
       </c>
       <c r="AD87">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE87">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF87">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG87">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,37 +14653,37 @@
         </is>
       </c>
       <c r="N88">
-        <v>6.85</v>
+        <v>6.95</v>
       </c>
       <c r="O88">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P88">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q88">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="R88">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S88">
         <v>1.36</v>
       </c>
       <c r="T88">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U88">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="V88">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W88">
         <v>1.05</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
         <v>1.3</v>
@@ -14692,7 +14692,7 @@
         <v>3.37</v>
       </c>
       <c r="AA88">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB88">
         <v>1.88</v>
@@ -14707,10 +14707,10 @@
         <v>1.07</v>
       </c>
       <c r="AF88">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG88">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="AK88">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O96">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P96">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q96">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R96">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S96">
         <v>1.36</v>
       </c>
       <c r="T96">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="U96">
+        <v>2.82</v>
+      </c>
+      <c r="V96">
+        <v>1.42</v>
+      </c>
+      <c r="W96">
+        <v>1.06</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
+        <v>1.29</v>
+      </c>
+      <c r="Z96">
+        <v>3.5</v>
+      </c>
+      <c r="AA96">
+        <v>1.88</v>
+      </c>
+      <c r="AB96">
+        <v>1.87</v>
+      </c>
+      <c r="AC96">
         <v>3</v>
       </c>
-      <c r="V96">
-        <v>1.33</v>
-      </c>
-      <c r="W96">
-        <v>1.02</v>
-      </c>
-      <c r="X96">
+      <c r="AD96">
+        <v>1.28</v>
+      </c>
+      <c r="AE96">
         <v>1.06</v>
       </c>
-      <c r="Y96">
-        <v>1.31</v>
-      </c>
-      <c r="Z96">
-        <v>2.92</v>
-      </c>
-      <c r="AA96">
-        <v>2</v>
-      </c>
-      <c r="AB96">
-        <v>1.69</v>
-      </c>
-      <c r="AC96">
-        <v>3.85</v>
-      </c>
-      <c r="AD96">
-        <v>1.19</v>
-      </c>
-      <c r="AE96">
-        <v>1.08</v>
-      </c>
       <c r="AF96">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG96">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AK96">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O97">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P97">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q97">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="R97">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S97">
         <v>1.36</v>
       </c>
       <c r="T97">
+        <v>2.66</v>
+      </c>
+      <c r="U97">
         <v>3</v>
       </c>
-      <c r="U97">
-        <v>2.82</v>
-      </c>
       <c r="V97">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W97">
+        <v>1.02</v>
+      </c>
+      <c r="X97">
         <v>1.06</v>
       </c>
-      <c r="X97">
-        <v>1.01</v>
-      </c>
       <c r="Y97">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z97">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA97">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB97">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AC97">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="AD97">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE97">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG97">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="O106">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P106">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="Q106">
+        <v>2.38</v>
+      </c>
+      <c r="R106">
+        <v>2.15</v>
+      </c>
+      <c r="S106">
+        <v>1.36</v>
+      </c>
+      <c r="T106">
+        <v>2.88</v>
+      </c>
+      <c r="U106">
         <v>2.75</v>
       </c>
-      <c r="R106">
-        <v>2.24</v>
-      </c>
-      <c r="S106">
-        <v>1.4</v>
-      </c>
-      <c r="T106">
-        <v>2.75</v>
-      </c>
-      <c r="U106">
-        <v>2.8</v>
-      </c>
       <c r="V106">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W106">
         <v>1.06</v>
       </c>
       <c r="X106">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y106">
         <v>1.3</v>
       </c>
       <c r="Z106">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AA106">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB106">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AC106">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AD106">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE106">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF106">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O107">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P107">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="Q107">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R107">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="S107">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T107">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U107">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V107">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W107">
         <v>1.06</v>
       </c>
       <c r="X107">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y107">
         <v>1.3</v>
       </c>
       <c r="Z107">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="AA107">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB107">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AC107">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD107">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG107">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK107">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.54</v>
+        <v>1.7</v>
       </c>
       <c r="O113">
-        <v>3.24</v>
+        <v>3.9</v>
       </c>
       <c r="P113">
-        <v>2.6</v>
+        <v>3.88</v>
       </c>
       <c r="Q113">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="R113">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S113">
+        <v>1.37</v>
+      </c>
+      <c r="T113">
+        <v>3.02</v>
+      </c>
+      <c r="U113">
+        <v>2.62</v>
+      </c>
+      <c r="V113">
+        <v>1.44</v>
+      </c>
+      <c r="W113">
+        <v>1.05</v>
+      </c>
+      <c r="X113">
+        <v>1.02</v>
+      </c>
+      <c r="Y113">
+        <v>1.25</v>
+      </c>
+      <c r="Z113">
+        <v>3.4</v>
+      </c>
+      <c r="AA113">
+        <v>1.78</v>
+      </c>
+      <c r="AB113">
+        <v>2</v>
+      </c>
+      <c r="AC113">
+        <v>2.83</v>
+      </c>
+      <c r="AD113">
         <v>1.36</v>
       </c>
-      <c r="T113">
-        <v>2.9</v>
-      </c>
-      <c r="U113">
-        <v>2.75</v>
-      </c>
-      <c r="V113">
-        <v>1.4</v>
-      </c>
-      <c r="W113">
-        <v>1.03</v>
-      </c>
-      <c r="X113">
-        <v>1.01</v>
-      </c>
-      <c r="Y113">
-        <v>1.31</v>
-      </c>
-      <c r="Z113">
-        <v>3.05</v>
-      </c>
-      <c r="AA113">
-        <v>1.94</v>
-      </c>
-      <c r="AB113">
-        <v>1.83</v>
-      </c>
-      <c r="AC113">
-        <v>3.3</v>
-      </c>
-      <c r="AD113">
-        <v>1.26</v>
-      </c>
       <c r="AE113">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF113">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG113">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AK113">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="O114">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P114">
+        <v>3</v>
+      </c>
+      <c r="Q114">
+        <v>2.88</v>
+      </c>
+      <c r="R114">
+        <v>1.92</v>
+      </c>
+      <c r="S114">
+        <v>1.48</v>
+      </c>
+      <c r="T114">
+        <v>2.62</v>
+      </c>
+      <c r="U114">
         <v>3.1</v>
       </c>
-      <c r="Q114">
-        <v>2.5</v>
-      </c>
-      <c r="R114">
-        <v>2.3</v>
-      </c>
-      <c r="S114">
-        <v>1.3</v>
-      </c>
-      <c r="T114">
-        <v>3.3</v>
-      </c>
-      <c r="U114">
-        <v>2.55</v>
-      </c>
       <c r="V114">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W114">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y114">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z114">
-        <v>4.38</v>
+        <v>2.66</v>
       </c>
       <c r="AA114">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB114">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AC114">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD114">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE114">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF114">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AG114">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK114">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,80 +19054,80 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="O115">
+        <v>3.24</v>
+      </c>
+      <c r="P115">
+        <v>2.6</v>
+      </c>
+      <c r="Q115">
+        <v>3.1</v>
+      </c>
+      <c r="R115">
+        <v>2.1</v>
+      </c>
+      <c r="S115">
+        <v>1.36</v>
+      </c>
+      <c r="T115">
+        <v>2.9</v>
+      </c>
+      <c r="U115">
+        <v>2.75</v>
+      </c>
+      <c r="V115">
+        <v>1.4</v>
+      </c>
+      <c r="W115">
+        <v>1.03</v>
+      </c>
+      <c r="X115">
+        <v>1.01</v>
+      </c>
+      <c r="Y115">
+        <v>1.31</v>
+      </c>
+      <c r="Z115">
+        <v>3.05</v>
+      </c>
+      <c r="AA115">
+        <v>1.94</v>
+      </c>
+      <c r="AB115">
+        <v>1.83</v>
+      </c>
+      <c r="AC115">
         <v>3.3</v>
       </c>
-      <c r="P115">
-        <v>3</v>
-      </c>
-      <c r="Q115">
-        <v>2.88</v>
-      </c>
-      <c r="R115">
-        <v>1.92</v>
-      </c>
-      <c r="S115">
+      <c r="AD115">
+        <v>1.26</v>
+      </c>
+      <c r="AE115">
+        <v>1.07</v>
+      </c>
+      <c r="AF115">
+        <v>1.7</v>
+      </c>
+      <c r="AG115">
+        <v>2.05</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ115">
         <v>1.48</v>
       </c>
-      <c r="T115">
-        <v>2.62</v>
-      </c>
-      <c r="U115">
-        <v>3.1</v>
-      </c>
-      <c r="V115">
-        <v>1.33</v>
-      </c>
-      <c r="W115">
-        <v>1.02</v>
-      </c>
-      <c r="X115">
-        <v>1.07</v>
-      </c>
-      <c r="Y115">
-        <v>1.4</v>
-      </c>
-      <c r="Z115">
-        <v>2.66</v>
-      </c>
-      <c r="AA115">
-        <v>2.2</v>
-      </c>
-      <c r="AB115">
-        <v>1.61</v>
-      </c>
-      <c r="AC115">
-        <v>4.2</v>
-      </c>
-      <c r="AD115">
-        <v>1.22</v>
-      </c>
-      <c r="AE115">
-        <v>1.04</v>
-      </c>
-      <c r="AF115">
-        <v>1.87</v>
-      </c>
-      <c r="AG115">
-        <v>1.85</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>1.36</v>
-      </c>
       <c r="AK115">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
+        <v>2.07</v>
+      </c>
+      <c r="O116">
+        <v>3.5</v>
+      </c>
+      <c r="P116">
+        <v>3.1</v>
+      </c>
+      <c r="Q116">
+        <v>2.5</v>
+      </c>
+      <c r="R116">
+        <v>2.3</v>
+      </c>
+      <c r="S116">
+        <v>1.3</v>
+      </c>
+      <c r="T116">
+        <v>3.3</v>
+      </c>
+      <c r="U116">
+        <v>2.55</v>
+      </c>
+      <c r="V116">
+        <v>1.5</v>
+      </c>
+      <c r="W116">
+        <v>1.12</v>
+      </c>
+      <c r="X116">
+        <v>1.01</v>
+      </c>
+      <c r="Y116">
+        <v>1.2</v>
+      </c>
+      <c r="Z116">
+        <v>4.38</v>
+      </c>
+      <c r="AA116">
         <v>1.7</v>
       </c>
-      <c r="O116">
-        <v>3.9</v>
-      </c>
-      <c r="P116">
-        <v>3.88</v>
-      </c>
-      <c r="Q116">
-        <v>2.15</v>
-      </c>
-      <c r="R116">
-        <v>2.25</v>
-      </c>
-      <c r="S116">
-        <v>1.37</v>
-      </c>
-      <c r="T116">
-        <v>3.02</v>
-      </c>
-      <c r="U116">
-        <v>2.62</v>
-      </c>
-      <c r="V116">
-        <v>1.44</v>
-      </c>
-      <c r="W116">
-        <v>1.05</v>
-      </c>
-      <c r="X116">
-        <v>1.02</v>
-      </c>
-      <c r="Y116">
-        <v>1.25</v>
-      </c>
-      <c r="Z116">
-        <v>3.4</v>
-      </c>
-      <c r="AA116">
-        <v>1.78</v>
-      </c>
       <c r="AB116">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC116">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD116">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE116">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF116">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AG116">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AK116">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -22009,7 +22009,7 @@
         <v>3.2</v>
       </c>
       <c r="U133">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="V133">
         <v>1.42</v>
@@ -22027,10 +22027,10 @@
         <v>3.7</v>
       </c>
       <c r="AA133">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB133">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AC133">
         <v>2.88</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O135">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P135">
-        <v>7</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Q135">
         <v>1.75</v>
@@ -22329,7 +22329,7 @@
         <v>2.45</v>
       </c>
       <c r="S135">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T135">
         <v>3.28</v>
@@ -22344,7 +22344,7 @@
         <v>1.1</v>
       </c>
       <c r="X135">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
         <v>1.18</v>
@@ -22365,7 +22365,7 @@
         <v>1.38</v>
       </c>
       <c r="AE135">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF135">
         <v>1.85</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O136">
         <v>3.65</v>
       </c>
       <c r="P136">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q136">
         <v>2.63</v>
@@ -22492,7 +22492,7 @@
         <v>2.3</v>
       </c>
       <c r="S136">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T136">
         <v>3.22</v>
@@ -22504,7 +22504,7 @@
         <v>1.53</v>
       </c>
       <c r="W136">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X136">
         <v>1.03</v>
@@ -22516,7 +22516,7 @@
         <v>4.2</v>
       </c>
       <c r="AA136">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB136">
         <v>2.15</v>
@@ -22525,10 +22525,10 @@
         <v>2.63</v>
       </c>
       <c r="AD136">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE136">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF136">
         <v>1.57</v>
@@ -22550,7 +22550,7 @@
         <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22649,7 +22649,7 @@
         <v>2.3</v>
       </c>
       <c r="Q137">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="R137">
         <v>2</v>
@@ -22661,7 +22661,7 @@
         <v>2.88</v>
       </c>
       <c r="U137">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="V137">
         <v>1.38</v>
@@ -22676,7 +22676,7 @@
         <v>1.3</v>
       </c>
       <c r="Z137">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA137">
         <v>2.06</v>
@@ -22685,7 +22685,7 @@
         <v>1.84</v>
       </c>
       <c r="AC137">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AD137">
         <v>1.3</v>
@@ -22694,7 +22694,7 @@
         <v>1.06</v>
       </c>
       <c r="AF137">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG137">
         <v>2</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O194">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P194">
+        <v>0</v>
+      </c>
+      <c r="Q194">
+        <v>2.43</v>
+      </c>
+      <c r="R194">
+        <v>1.82</v>
+      </c>
+      <c r="S194">
+        <v>1.5</v>
+      </c>
+      <c r="T194">
+        <v>2.18</v>
+      </c>
+      <c r="U194">
         <v>3.8</v>
       </c>
-      <c r="Q194">
-        <v>2.8</v>
-      </c>
-      <c r="R194">
-        <v>1.85</v>
-      </c>
-      <c r="S194">
-        <v>1.6</v>
-      </c>
-      <c r="T194">
-        <v>2.2</v>
-      </c>
-      <c r="U194">
-        <v>3.9</v>
-      </c>
       <c r="V194">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W194">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X194">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y194">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="Z194">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AA194">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AB194">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC194">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AD194">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE194">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF194">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AG194">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK194">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,80 +32094,80 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q195">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="R195">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="S195">
+        <v>1.6</v>
+      </c>
+      <c r="T195">
+        <v>2.2</v>
+      </c>
+      <c r="U195">
+        <v>3.9</v>
+      </c>
+      <c r="V195">
+        <v>1.18</v>
+      </c>
+      <c r="W195">
+        <v>1.02</v>
+      </c>
+      <c r="X195">
+        <v>1.1</v>
+      </c>
+      <c r="Y195">
+        <v>1.62</v>
+      </c>
+      <c r="Z195">
+        <v>2.3</v>
+      </c>
+      <c r="AA195">
+        <v>2.88</v>
+      </c>
+      <c r="AB195">
+        <v>1.35</v>
+      </c>
+      <c r="AC195">
+        <v>7</v>
+      </c>
+      <c r="AD195">
+        <v>1.08</v>
+      </c>
+      <c r="AE195">
+        <v>1.01</v>
+      </c>
+      <c r="AF195">
+        <v>2.33</v>
+      </c>
+      <c r="AG195">
         <v>1.5</v>
       </c>
-      <c r="T195">
-        <v>2.18</v>
-      </c>
-      <c r="U195">
-        <v>3.8</v>
-      </c>
-      <c r="V195">
-        <v>1.2</v>
-      </c>
-      <c r="W195">
-        <v>1.04</v>
-      </c>
-      <c r="X195">
-        <v>1.07</v>
-      </c>
-      <c r="Y195">
-        <v>1.52</v>
-      </c>
-      <c r="Z195">
-        <v>2.33</v>
-      </c>
-      <c r="AA195">
-        <v>2.62</v>
-      </c>
-      <c r="AB195">
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ195">
         <v>1.44</v>
       </c>
-      <c r="AC195">
-        <v>5.25</v>
-      </c>
-      <c r="AD195">
-        <v>1.13</v>
-      </c>
-      <c r="AE195">
-        <v>1.03</v>
-      </c>
-      <c r="AF195">
-        <v>2.21</v>
-      </c>
-      <c r="AG195">
-        <v>1.58</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ195">
-        <v>1.33</v>
-      </c>
       <c r="AK195">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32579,7 +32579,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N198">
@@ -33410,7 +33410,7 @@
         <v>1.65</v>
       </c>
       <c r="R203">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="S203">
         <v>1.25</v>
@@ -33422,16 +33422,16 @@
         <v>2.24</v>
       </c>
       <c r="V203">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W203">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X203">
         <v>1.02</v>
       </c>
       <c r="Y203">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z203">
         <v>4.85</v>
@@ -33452,7 +33452,7 @@
         <v>1.17</v>
       </c>
       <c r="AF203">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG203">
         <v>1.69</v>
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,80 +42037,80 @@
         </is>
       </c>
       <c r="N256">
+        <v>2.11</v>
+      </c>
+      <c r="O256">
+        <v>3.31</v>
+      </c>
+      <c r="P256">
+        <v>2.98</v>
+      </c>
+      <c r="Q256">
+        <v>2.6</v>
+      </c>
+      <c r="R256">
+        <v>2.3</v>
+      </c>
+      <c r="S256">
+        <v>1.29</v>
+      </c>
+      <c r="T256">
+        <v>3.4</v>
+      </c>
+      <c r="U256">
+        <v>2.53</v>
+      </c>
+      <c r="V256">
+        <v>1.47</v>
+      </c>
+      <c r="W256">
+        <v>1.08</v>
+      </c>
+      <c r="X256">
+        <v>1.02</v>
+      </c>
+      <c r="Y256">
+        <v>1.2</v>
+      </c>
+      <c r="Z256">
+        <v>4.39</v>
+      </c>
+      <c r="AA256">
+        <v>1.65</v>
+      </c>
+      <c r="AB256">
         <v>2.07</v>
       </c>
-      <c r="O256">
-        <v>4.46</v>
-      </c>
-      <c r="P256">
-        <v>3</v>
-      </c>
-      <c r="Q256">
-        <v>2.49</v>
-      </c>
-      <c r="R256">
-        <v>2.5</v>
-      </c>
-      <c r="S256">
-        <v>1.17</v>
-      </c>
-      <c r="T256">
-        <v>4</v>
-      </c>
-      <c r="U256">
-        <v>2.01</v>
-      </c>
-      <c r="V256">
-        <v>1.75</v>
-      </c>
-      <c r="W256">
-        <v>1.18</v>
-      </c>
-      <c r="X256">
-        <v>1.01</v>
-      </c>
-      <c r="Y256">
-        <v>1.11</v>
-      </c>
-      <c r="Z256">
-        <v>7</v>
-      </c>
-      <c r="AA256">
-        <v>1.36</v>
-      </c>
-      <c r="AB256">
-        <v>2.88</v>
-      </c>
       <c r="AC256">
-        <v>1.98</v>
+        <v>2.74</v>
       </c>
       <c r="AD256">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="AE256">
+        <v>1.13</v>
+      </c>
+      <c r="AF256">
+        <v>1.57</v>
+      </c>
+      <c r="AG256">
+        <v>2.25</v>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ256">
         <v>1.3</v>
       </c>
-      <c r="AF256">
-        <v>1.34</v>
-      </c>
-      <c r="AG256">
-        <v>2.9</v>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ256">
-        <v>1.17</v>
-      </c>
       <c r="AK256">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G257">
@@ -42200,16 +42200,16 @@
         </is>
       </c>
       <c r="N257">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="O257">
-        <v>3.31</v>
+        <v>3.97</v>
       </c>
       <c r="P257">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="Q257">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R257">
         <v>2.3</v>
@@ -42218,43 +42218,43 @@
         <v>1.29</v>
       </c>
       <c r="T257">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U257">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V257">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W257">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X257">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y257">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z257">
-        <v>4.39</v>
+        <v>4.28</v>
       </c>
       <c r="AA257">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AB257">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AC257">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD257">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE257">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF257">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG257">
         <v>2.25</v>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK257">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,64 +42363,64 @@
         </is>
       </c>
       <c r="N258">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="O258">
-        <v>3.97</v>
+        <v>4.46</v>
       </c>
       <c r="P258">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q258">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="R258">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S258">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T258">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U258">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="V258">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W258">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X258">
         <v>1.01</v>
       </c>
       <c r="Y258">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z258">
-        <v>4.28</v>
+        <v>7</v>
       </c>
       <c r="AA258">
+        <v>1.36</v>
+      </c>
+      <c r="AB258">
+        <v>2.88</v>
+      </c>
+      <c r="AC258">
+        <v>1.98</v>
+      </c>
+      <c r="AD258">
         <v>1.74</v>
       </c>
-      <c r="AB258">
-        <v>2.17</v>
-      </c>
-      <c r="AC258">
-        <v>2.8</v>
-      </c>
-      <c r="AD258">
-        <v>1.45</v>
-      </c>
       <c r="AE258">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AF258">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="AG258">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK258">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,65 +44156,65 @@
         </is>
       </c>
       <c r="N269">
+        <v>1.49</v>
+      </c>
+      <c r="O269">
+        <v>4.4</v>
+      </c>
+      <c r="P269">
+        <v>5.2</v>
+      </c>
+      <c r="Q269">
+        <v>1.85</v>
+      </c>
+      <c r="R269">
+        <v>2.63</v>
+      </c>
+      <c r="S269">
+        <v>1.2</v>
+      </c>
+      <c r="T269">
+        <v>4.1</v>
+      </c>
+      <c r="U269">
+        <v>2.05</v>
+      </c>
+      <c r="V269">
         <v>1.73</v>
       </c>
-      <c r="O269">
-        <v>4.47</v>
-      </c>
-      <c r="P269">
-        <v>4.5</v>
-      </c>
-      <c r="Q269">
-        <v>2.15</v>
-      </c>
-      <c r="R269">
-        <v>2.56</v>
-      </c>
-      <c r="S269">
-        <v>1.25</v>
-      </c>
-      <c r="T269">
-        <v>3.6</v>
-      </c>
-      <c r="U269">
-        <v>2.27</v>
-      </c>
-      <c r="V269">
-        <v>1.56</v>
-      </c>
       <c r="W269">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X269">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y269">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z269">
-        <v>5</v>
+        <v>5.64</v>
       </c>
       <c r="AA269">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB269">
+        <v>2.63</v>
+      </c>
+      <c r="AC269">
+        <v>2.07</v>
+      </c>
+      <c r="AD269">
+        <v>1.7</v>
+      </c>
+      <c r="AE269">
+        <v>1.3</v>
+      </c>
+      <c r="AF269">
+        <v>1.55</v>
+      </c>
+      <c r="AG269">
         <v>2.3</v>
       </c>
-      <c r="AC269">
-        <v>2.44</v>
-      </c>
-      <c r="AD269">
-        <v>1.57</v>
-      </c>
-      <c r="AE269">
-        <v>1.22</v>
-      </c>
-      <c r="AF269">
-        <v>1.53</v>
-      </c>
-      <c r="AG269">
-        <v>2.38</v>
-      </c>
       <c r="AH269" t="inlineStr">
         <is>
           <t>[]</t>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK269">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,80 +44319,80 @@
         </is>
       </c>
       <c r="N270">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="O270">
-        <v>4.4</v>
+        <v>4.47</v>
       </c>
       <c r="P270">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q270">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="R270">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S270">
+        <v>1.25</v>
+      </c>
+      <c r="T270">
+        <v>3.6</v>
+      </c>
+      <c r="U270">
+        <v>2.27</v>
+      </c>
+      <c r="V270">
+        <v>1.56</v>
+      </c>
+      <c r="W270">
+        <v>1.14</v>
+      </c>
+      <c r="X270">
+        <v>1.03</v>
+      </c>
+      <c r="Y270">
+        <v>1.17</v>
+      </c>
+      <c r="Z270">
+        <v>5</v>
+      </c>
+      <c r="AA270">
+        <v>1.57</v>
+      </c>
+      <c r="AB270">
+        <v>2.3</v>
+      </c>
+      <c r="AC270">
+        <v>2.44</v>
+      </c>
+      <c r="AD270">
+        <v>1.57</v>
+      </c>
+      <c r="AE270">
+        <v>1.22</v>
+      </c>
+      <c r="AF270">
+        <v>1.53</v>
+      </c>
+      <c r="AG270">
+        <v>2.38</v>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ270">
         <v>1.2</v>
       </c>
-      <c r="T270">
-        <v>4.1</v>
-      </c>
-      <c r="U270">
+      <c r="AK270">
         <v>2.05</v>
-      </c>
-      <c r="V270">
-        <v>1.73</v>
-      </c>
-      <c r="W270">
-        <v>1.17</v>
-      </c>
-      <c r="X270">
-        <v>1.02</v>
-      </c>
-      <c r="Y270">
-        <v>1.13</v>
-      </c>
-      <c r="Z270">
-        <v>5.64</v>
-      </c>
-      <c r="AA270">
-        <v>1.47</v>
-      </c>
-      <c r="AB270">
-        <v>2.63</v>
-      </c>
-      <c r="AC270">
-        <v>2.07</v>
-      </c>
-      <c r="AD270">
-        <v>1.7</v>
-      </c>
-      <c r="AE270">
-        <v>1.3</v>
-      </c>
-      <c r="AF270">
-        <v>1.55</v>
-      </c>
-      <c r="AG270">
-        <v>2.3</v>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ270">
-        <v>1.18</v>
-      </c>
-      <c r="AK270">
-        <v>2.48</v>
       </c>
       <c r="AL270">
         <v>0</v>
